--- a/Results/Hydrogen/hydrogen resource use mineral and metals results.xlsx
+++ b/Results/Hydrogen/hydrogen resource use mineral and metals results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001935735589870231</v>
+        <v>0.0001935735589870597</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002040040674436334</v>
+        <v>0.0002040040674436352</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002000800157511692</v>
+        <v>0.0002000800157511673</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002040040674436334</v>
+        <v>0.0002040040674436352</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002040040674436334</v>
+        <v>0.0002040040674436352</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001933283329191129</v>
+        <v>0.0001933283329190958</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002123147444838578</v>
+        <v>0.0002123147444838203</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002040040674436334</v>
+        <v>0.0002040040674436352</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002051859758543356</v>
+        <v>0.0002051859758543249</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001880522325361822</v>
+        <v>0.0001880522325361677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002189112198376806</v>
+        <v>0.0001830942685195616</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.00919524356223e-06</v>
+        <v>7.009195243562171e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.237164548629538e-06</v>
+        <v>6.237164548629607e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.00919524356223e-06</v>
+        <v>7.009195243562171e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.290240984330765e-06</v>
+        <v>6.290240984330954e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.290240984330754e-06</v>
+        <v>6.290240984330901e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.944075853536408e-06</v>
+        <v>6.944075853536611e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.00919524356223e-06</v>
+        <v>7.009195243562171e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.736972321668162e-06</v>
+        <v>6.736972321668502e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.00919524356223e-06</v>
+        <v>7.009195243562171e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.00919524356223e-06</v>
+        <v>7.009195243562171e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.00919524356223e-06</v>
+        <v>7.009195243562171e-06</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.380729046491329e-05</v>
+        <v>1.497604381613681e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.468345985084644e-05</v>
+        <v>1.468345985084661e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.501756062443492e-05</v>
+        <v>1.501760574022107e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.446150067815847e-05</v>
+        <v>1.446150067815858e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.471482014424983e-05</v>
+        <v>1.471482014425002e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.374217107488736e-05</v>
+        <v>3.374217107488779e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.389714753427709e-05</v>
+        <v>3.389714753427673e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.353506754301934e-05</v>
+        <v>1.470382089424315e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.549016207442153e-05</v>
+        <v>1.549016207442176e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.500520413419427e-05</v>
+        <v>1.500520413419421e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.499162606565578e-05</v>
+        <v>1.499162606565577e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.871822997695735e-05</v>
+        <v>5.871822997695725e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.844600705506381e-05</v>
+        <v>5.844600705506368e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.871807095055616e-05</v>
+        <v>5.871807095055649e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.844522827023926e-05</v>
+        <v>5.844522827023941e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.844522827023926e-05</v>
+        <v>5.844522827023941e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.865311058693174e-05</v>
+        <v>5.865311058693171e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.871822997695735e-05</v>
+        <v>5.871822997695725e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.844600705506381e-05</v>
+        <v>5.844600705506368e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.871822997695735e-05</v>
+        <v>5.871822997695725e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.871822997695735e-05</v>
+        <v>5.871822997695725e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.871822997695735e-05</v>
+        <v>5.871822997695725e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002636158199084481</v>
+        <v>0.0002636158199084478</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004275866290765117</v>
+        <v>0.0004275866290765122</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004618773946628716</v>
+        <v>0.0004618773946628727</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003826729381143053</v>
+        <v>0.0003826729381143049</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002685484716929765</v>
+        <v>0.000268548471692977</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004277619938594056</v>
+        <v>0.000427761993859406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004278271132494303</v>
+        <v>0.0004278271132494315</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004275548903275379</v>
+        <v>0.0004275548903275382</v>
       </c>
       <c r="J6" t="n">
         <v>0.0004278593855037424</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002605655108261056</v>
+        <v>0.0002605655108261053</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005993595402965966</v>
+        <v>0.000599359540296598</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001719121541572031</v>
+        <v>0.0001719121541572034</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002177523652065946</v>
+        <v>0.000217752365206595</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002180245894140147</v>
+        <v>0.0002180245894140145</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002709651271567181</v>
+        <v>0.0002709651271567176</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002177523569879756</v>
+        <v>0.0002177523569879734</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002179594687384626</v>
+        <v>0.000217959468738463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002180245881284873</v>
+        <v>0.0002180245881284885</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002177523652065946</v>
+        <v>0.000217752365206595</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002180245881284873</v>
+        <v>0.0002180245881284885</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001599608023851114</v>
+        <v>0.0001913068633287065</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002180245881284873</v>
+        <v>0.0002180245881284885</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.38557386265107e-05</v>
+        <v>2.385573862651478e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.432162270134186e-05</v>
+        <v>2.432162270134178e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.354132960877261e-05</v>
+        <v>2.354132960877268e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.432162270134186e-05</v>
+        <v>2.432162270134178e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.432162270134186e-05</v>
+        <v>2.432162270134178e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.370689737389565e-05</v>
+        <v>2.370689737389612e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.364781919033464e-05</v>
+        <v>2.364781919033465e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.432162270134186e-05</v>
+        <v>2.432162270134178e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.350067514567032e-05</v>
+        <v>2.350067514567043e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.380481646432626e-05</v>
+        <v>2.380481646432656e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.403174743013523e-05</v>
+        <v>2.403174743013526e-05</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.410301955484871e-05</v>
+        <v>2.410301955484857e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.461411604961569e-05</v>
+        <v>2.461411604961561e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.397498916625843e-05</v>
+        <v>2.39749891662585e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.461411604961569e-05</v>
+        <v>2.461411604961561e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.461411604961569e-05</v>
+        <v>2.461411604961561e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.401957877997251e-05</v>
+        <v>2.401957877997261e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.401913203430039e-05</v>
+        <v>2.40191320343004e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.461411604961569e-05</v>
+        <v>2.461411604961561e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.395878627148899e-05</v>
+        <v>2.395878627148911e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.408231691073686e-05</v>
+        <v>2.408231691073683e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.417505912334383e-05</v>
+        <v>2.41750591233439e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002026894475674556</v>
+        <v>0.0002026894475674547</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002242094844414581</v>
+        <v>0.000224209484441457</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002509936864833097</v>
+        <v>0.0002509936864833091</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002242094844414581</v>
+        <v>0.000224209484441457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002242094844414581</v>
+        <v>0.000224209484441457</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002169713003079561</v>
+        <v>0.0002169713003079466</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002608802603758056</v>
+        <v>0.0002608802603758049</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002242094844414581</v>
+        <v>0.000224209484441457</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002420478535739988</v>
+        <v>0.0002420478535739981</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002127730768727174</v>
+        <v>0.0002127730768727177</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002464416319572976</v>
+        <v>0.0002478418725875164</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.373115638524973e-06</v>
+        <v>7.373115638524916e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.674192023509074e-06</v>
+        <v>6.674192023508942e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.373115638524973e-06</v>
+        <v>7.373115638524916e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.732292372054162e-06</v>
+        <v>6.732292372054028e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.732292372054159e-06</v>
+        <v>6.732292372054033e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.308014120495976e-06</v>
+        <v>7.308014120495858e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.373115638524973e-06</v>
+        <v>7.373115638524916e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.101096945604978e-06</v>
+        <v>7.101096945604866e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.373115638524973e-06</v>
+        <v>7.373115638524916e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.373115638524973e-06</v>
+        <v>7.373115638524916e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.373115638524973e-06</v>
+        <v>7.373115638524916e-06</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.128834242931024e-05</v>
+        <v>3.128834242931006e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.419750503446352e-05</v>
+        <v>1.419750503446338e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.456532646504891e-05</v>
+        <v>3.153875109644862e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.399370246527446e-05</v>
+        <v>1.399370246527434e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.422951514774218e-05</v>
+        <v>1.422951514774204e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.122324091128101e-05</v>
+        <v>1.442174671331719e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15018521254142e-05</v>
+        <v>3.150185212541411e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.421482953842627e-05</v>
+        <v>1.421482953842615e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.135013345722595e-05</v>
+        <v>3.135013345722578e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.449830216340396e-05</v>
+        <v>1.449830216340387e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.450863744538357e-05</v>
+        <v>1.450863744538355e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.264659396673006e-05</v>
+        <v>5.264659396672982e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.237457527381011e-05</v>
+        <v>5.237457527380983e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.264641483547746e-05</v>
+        <v>5.264641483547723e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.237887593478689e-05</v>
+        <v>5.237887593478664e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.237887593478689e-05</v>
+        <v>5.237887593478664e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.25814924487011e-05</v>
+        <v>5.258149244870087e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.264659396673006e-05</v>
+        <v>5.264659396672982e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.237457527381011e-05</v>
+        <v>5.237457527380983e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.264659396673006e-05</v>
+        <v>5.264659396672982e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.264659396673006e-05</v>
+        <v>5.264659396672982e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.264659396673006e-05</v>
+        <v>5.264659396672982e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002316358188573543</v>
+        <v>0.0002316358188573536</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003749825714244237</v>
+        <v>0.0003749825714244227</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000404995541166878</v>
+        <v>0.0004049955411668773</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003357095489115582</v>
+        <v>0.0003357095489115571</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002359179330855704</v>
+        <v>0.0002359179330855697</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003751569076989224</v>
+        <v>0.0003751569076989212</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003752220092169499</v>
+        <v>0.0003752220092169493</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000374949990524031</v>
+        <v>0.0003749499905240302</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003752502280430834</v>
+        <v>0.0003752502280430826</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002289686316520699</v>
+        <v>0.0002289686316520694</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005252097915530955</v>
+        <v>0.0005252097915530941</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001283129392820633</v>
+        <v>0.0001283129392820626</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001619628525312572</v>
+        <v>0.0001619628525312568</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001622348725261564</v>
+        <v>0.0001622348725261557</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002011080342756393</v>
+        <v>0.0002011080342756389</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001619628448251552</v>
+        <v>0.0001619628448251548</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001621697697061484</v>
+        <v>0.0001621697697061477</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001622348712241771</v>
+        <v>0.0001622348712241769</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001619628525312572</v>
+        <v>0.0001619628525312568</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001622348712241771</v>
+        <v>0.0001622348712241769</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001425803711828143</v>
+        <v>0.0001425803711828134</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001622348712241771</v>
+        <v>0.0001622348712241769</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.347016982471883e-05</v>
+        <v>2.347016982471871e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.396737767583459e-05</v>
+        <v>2.396737767583452e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.268968697791878e-05</v>
+        <v>2.268968697791862e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.396737767583459e-05</v>
+        <v>2.396737767583452e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.396737767583459e-05</v>
+        <v>2.396737767583452e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33281585008095e-05</v>
+        <v>2.332815850080948e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.279181874624599e-05</v>
+        <v>2.279181874624596e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.396737767583459e-05</v>
+        <v>2.396737767583452e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.243854172357477e-05</v>
+        <v>2.24385417235747e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.358843971508086e-05</v>
+        <v>2.358843971508075e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.296532989999152e-05</v>
+        <v>2.285449295959983e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.41338865755597e-05</v>
+        <v>2.413388657555966e-05</v>
       </c>
       <c r="C9" t="n">
         <v>2.468514655100236e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.381605844790887e-05</v>
+        <v>2.381605844790877e-05</v>
       </c>
       <c r="E9" t="n">
         <v>2.468514655100236e-05</v>
@@ -1206,22 +1206,22 @@
         <v>2.468514655100236e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.405328875620393e-05</v>
+        <v>2.405328875620381e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.38594928547574e-05</v>
+        <v>2.385949285475735e-05</v>
       </c>
       <c r="I9" t="n">
         <v>2.468514655100236e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.371462127959994e-05</v>
+        <v>2.371462127959986e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.418212331498687e-05</v>
+        <v>2.418212331498682e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.392965784122468e-05</v>
+        <v>2.39296578412246e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.487374384631373e-05</v>
+        <v>5.487374384631378e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001837381753976419</v>
+        <v>0.0001837381753976421</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002103634245795208</v>
+        <v>0.0002103634245795215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001996662267368512</v>
+        <v>0.0001996662267368513</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001996662267368512</v>
+        <v>0.0001996662267368513</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001950318933652947</v>
+        <v>0.0001950318933652942</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002488412807092175</v>
+        <v>0.0002488412807092181</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001996662267368512</v>
+        <v>0.0001996662267368513</v>
       </c>
       <c r="J2" t="n">
         <v>0.0001804002696949416</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001857923905799876</v>
+        <v>0.0001857923905799877</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002059483571032893</v>
+        <v>0.000205948357103289</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.772792968808232e-06</v>
+        <v>7.772792968808202e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.717567924689475e-06</v>
+        <v>6.717567924689478e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.772792968808232e-06</v>
+        <v>7.772792968808204e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.012422048455654e-06</v>
+        <v>7.012422048455135e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.012422048455655e-06</v>
+        <v>7.012422048455147e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.706586888088995e-06</v>
+        <v>7.706586888088948e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.772792968808232e-06</v>
+        <v>7.772792968808204e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.494319255459766e-06</v>
+        <v>7.494319255459681e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.772792968808231e-06</v>
+        <v>7.772792968808204e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.772792968808232e-06</v>
+        <v>7.772792968808204e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.772792968808232e-06</v>
+        <v>7.772792968808204e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.297101029389276e-05</v>
+        <v>1.498613777198976e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.460911138497512e-05</v>
+        <v>1.460911138497509e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.503052610080566e-05</v>
+        <v>1.50305499898147e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.447375519395878e-05</v>
+        <v>1.447375519395881e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.472259446570153e-05</v>
+        <v>1.472259446570155e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.29048042131736e-05</v>
+        <v>3.29048042131735e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.417369431215748e-05</v>
+        <v>3.417369431215746e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.269253658054428e-05</v>
+        <v>3.269253658054426e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.327869733207867e-05</v>
+        <v>3.327869733207848e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.499690876896675e-05</v>
+        <v>1.499690876896671e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.499980339580083e-05</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.612545906410929e-05</v>
+        <v>5.612545906410925e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.583905353821121e-05</v>
+        <v>5.583905353821118e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.612543033442475e-05</v>
+        <v>5.612543033442471e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.584721932500768e-05</v>
+        <v>5.584721932500763e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.584721932500768e-05</v>
+        <v>5.584721932500763e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.605925298339003e-05</v>
+        <v>5.605925298338998e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.612545906410929e-05</v>
+        <v>5.612545906410925e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.584698535076075e-05</v>
+        <v>5.584698535076067e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.612545906410929e-05</v>
+        <v>5.612545906410925e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.612545906410929e-05</v>
+        <v>5.612545906410925e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.612545906410929e-05</v>
+        <v>5.612545906410925e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457835089929884</v>
+        <v>0.0002457835089929885</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003981316985767593</v>
+        <v>0.0003981316985769989</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004300313017741977</v>
+        <v>0.0004300313017741971</v>
       </c>
       <c r="E6" t="n">
         <v>0.000356400501888275</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002503425125749642</v>
+        <v>0.0002503425125749641</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003983216004685029</v>
+        <v>0.000398321600468503</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003983878065492784</v>
+        <v>0.0003983878065492782</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003981093328358738</v>
+        <v>0.0003981093328358732</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003984177976934832</v>
+        <v>0.0003984177976934831</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002429488058164024</v>
+        <v>0.0002429488058164022</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005577957559360677</v>
+        <v>0.0005577957559360675</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001504740734113481</v>
+        <v>0.0001504740734113479</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001902509210503251</v>
+        <v>0.0001902509210503248</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001905373285113468</v>
+        <v>0.0001905373285113467</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002364909897675134</v>
+        <v>0.0002364909897675137</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001902588452478825</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001904711204955038</v>
+        <v>0.0001904711204955037</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001905373265762233</v>
+        <v>0.0001905373265762229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001902588528628747</v>
+        <v>0.0001902588528628745</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001905373265762233</v>
+        <v>0.0001905373265762229</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001400905390747087</v>
+        <v>0.0001673245211658601</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001905373265762233</v>
+        <v>0.0001905373265762229</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.247154246741568e-05</v>
+        <v>2.247154246741567e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.328514793911325e-05</v>
+        <v>2.328514793911324e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.313359994991287e-05</v>
+        <v>2.313359994991288e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.399793153413445e-05</v>
+        <v>2.399793153413446e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.399793153413445e-05</v>
+        <v>2.399793153413446e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42596283464351e-05</v>
+        <v>2.425962834643511e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.272535501200993e-05</v>
+        <v>2.272535501200992e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.399793153413445e-05</v>
+        <v>2.399793153413446e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.509917192149555e-05</v>
+        <v>2.509917192149554e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.48506765594761e-05</v>
+        <v>2.485067655947613e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.421399040944305e-05</v>
+        <v>2.421399040944306e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1587,28 +1587,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.283322846787494e-05</v>
+        <v>2.283322846787493e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.370824170256379e-05</v>
+        <v>2.370824170256375e-05</v>
       </c>
       <c r="D9" t="n">
         <v>2.396033189640638e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.465248614438862e-05</v>
+        <v>2.465248614438861e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.465248614438862e-05</v>
+        <v>2.46524861443886e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.484400454485888e-05</v>
+        <v>2.484400454485887e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.379591219041643e-05</v>
+        <v>2.379591219041644e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.465248614438862e-05</v>
+        <v>2.46524861443886e-05</v>
       </c>
       <c r="J9" t="n">
         <v>2.542337093625876e-05</v>
@@ -1617,7 +1617,7 @@
         <v>2.53165107642487e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.471835643339087e-05</v>
+        <v>2.471835643339086e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.441859923284911e-05</v>
+        <v>6.441859923284876e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.0001914971352138083</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000214424032941487</v>
+        <v>0.0002144240329414868</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002063480669593086</v>
+        <v>0.000206348066959308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002063480669593086</v>
+        <v>0.000206348066959308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002002365037494176</v>
+        <v>0.0002002365037494075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002553818069768235</v>
+        <v>0.0002553818069768233</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002063480669593086</v>
+        <v>0.000206348066959308</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001739040493052598</v>
+        <v>0.0001739040493052595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001887912903729796</v>
+        <v>0.0001887912903729794</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002107352647795447</v>
+        <v>0.0002107352647795442</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.989837725524061e-06</v>
+        <v>7.989837725523818e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.916706306901393e-06</v>
+        <v>6.916706306901309e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.989837725524061e-06</v>
+        <v>7.989837725523818e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.263185167352253e-06</v>
+        <v>7.263185167352093e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.263185167352248e-06</v>
+        <v>7.263185167352161e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.923530598183082e-06</v>
+        <v>7.923530598182897e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.989837725524061e-06</v>
+        <v>7.989837725523818e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.710885607556801e-06</v>
+        <v>7.710885607556675e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.989837725524061e-06</v>
+        <v>7.989837725523818e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.989837725524061e-06</v>
+        <v>7.989837725523818e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.989837725524061e-06</v>
+        <v>7.989837725523818e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.217663676942665e-05</v>
+        <v>3.217663676942644e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.455718405518787e-05</v>
+        <v>1.45571840551879e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.498019920872318e-05</v>
+        <v>3.273208706570811e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.443406995913413e-05</v>
+        <v>1.443406995913399e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.468164059692763e-05</v>
+        <v>1.468164059692736e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.487707306673419e-05</v>
+        <v>1.487707306673396e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.38050833066426e-05</v>
+        <v>3.380508330664217e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.466442807610766e-05</v>
+        <v>1.466442807610769e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.540836900313159e-05</v>
+        <v>1.540836900313111e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.494534434225295e-05</v>
+        <v>1.494534434225287e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.495591713966433e-05</v>
+        <v>1.495591713966414e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.385103823788071e-05</v>
+        <v>5.385103823788062e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.356408053197636e-05</v>
+        <v>5.35640805319763e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.385102508882493e-05</v>
+        <v>5.385102508882479e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.35780506166802e-05</v>
+        <v>5.357805061668015e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.35780506166802e-05</v>
+        <v>5.357805061668015e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.378473111053976e-05</v>
+        <v>5.378473111053967e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.385103823788071e-05</v>
+        <v>5.385103823788062e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.357208611991345e-05</v>
+        <v>5.357208611991338e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.385103823788071e-05</v>
+        <v>5.385103823788062e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.385103823788071e-05</v>
+        <v>5.385103823788062e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.385103823788071e-05</v>
+        <v>5.385103823788062e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002337983606782208</v>
+        <v>0.0002337983606782207</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003783661378741203</v>
+        <v>0.0003783661378744207</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00040864833940836</v>
+        <v>0.0004086483394083594</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003387633946298117</v>
+        <v>0.0003387633946298116</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002381135608550359</v>
+        <v>0.0002381135608550356</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003785525573901409</v>
+        <v>0.0003785525573901408</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000378618864517648</v>
+        <v>0.0003786188645176478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003783399123995145</v>
+        <v>0.0003783399123995144</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003786473259211815</v>
+        <v>0.0003786473259211811</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002311082454662114</v>
+        <v>0.0002311082454662111</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000529895990495156</v>
+        <v>0.0005298959904951555</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001358654933365097</v>
+        <v>0.0001358654933365094</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001715283412897268</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001718153011602754</v>
+        <v>0.000171815301160275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002130216532042643</v>
+        <v>0.0002130216532042642</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001715363395962256</v>
+        <v>0.0001715363395962254</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001717489918682903</v>
+        <v>0.0001717489918682899</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001718152989956313</v>
+        <v>0.0001718152989956308</v>
       </c>
       <c r="I7" t="n">
         <v>0.0001715363468776639</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001718152989956313</v>
+        <v>0.0001718152989956308</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001509858413213928</v>
+        <v>0.0001509858413213925</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001718152989956313</v>
+        <v>0.0001718152989956308</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.228276766715804e-05</v>
+        <v>2.228276766715809e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.297969864705029e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.298817098237008e-05</v>
+        <v>2.298817098237004e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.376664638398823e-05</v>
+        <v>2.376664638398829e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.376664638398823e-05</v>
+        <v>2.376664638398829e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.396246766598495e-05</v>
+        <v>2.39624676659849e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.252485794675115e-05</v>
+        <v>2.252485794675109e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.376664638398823e-05</v>
+        <v>2.376664638398829e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.52618540768377e-05</v>
+        <v>2.526185407683759e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.462794024727055e-05</v>
+        <v>2.462794024727053e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.400886845866936e-05</v>
+        <v>2.400886845866932e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.280976987009757e-05</v>
+        <v>2.280976987009752e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.363948088727785e-05</v>
+        <v>2.363948088727784e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.402298141247174e-05</v>
+        <v>2.402298141247171e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.465741721863749e-05</v>
+        <v>2.465741721863756e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.465741721863749e-05</v>
+        <v>2.465741721863756e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.475595241867497e-05</v>
+        <v>2.475595241867486e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.383650637053434e-05</v>
+        <v>2.383650637053422e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.465741721863749e-05</v>
+        <v>2.465741721863756e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.561665729071066e-05</v>
+        <v>2.56166572907106e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.526912387183547e-05</v>
+        <v>2.526912387183542e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.470065305263965e-05</v>
+        <v>2.470065305263963e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.070180831158738e-05</v>
+        <v>7.070180831158737e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002019928830689153</v>
+        <v>0.0002019928830689156</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002230597720151997</v>
+        <v>0.0002230597720151999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000213265247968494</v>
+        <v>0.0002132652479684897</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000213265247968494</v>
+        <v>0.0002132652479684897</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002093530857427004</v>
+        <v>0.0002093530857426922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002618203328689716</v>
+        <v>0.0002618203328689703</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000213265247968494</v>
+        <v>0.0002132652479684897</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001797530578559329</v>
+        <v>0.0001797530578559325</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001953606309691963</v>
+        <v>0.0001953606309691964</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002264338492188939</v>
+        <v>0.000226433849218894</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.462572046443156e-06</v>
+        <v>8.462572046443285e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.318217761990383e-06</v>
+        <v>7.318217761990423e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.462572046443156e-06</v>
+        <v>8.462572046443285e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.73630582680714e-06</v>
+        <v>7.736305826807106e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.73630582680714e-06</v>
+        <v>7.736305826807108e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.396031998872733e-06</v>
+        <v>8.396031998872836e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.462572046443156e-06</v>
+        <v>8.462572046443285e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.182320976082384e-06</v>
+        <v>8.182320976082519e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.462572046443156e-06</v>
+        <v>8.462572046443285e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.462572046443156e-06</v>
+        <v>8.462572046443285e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.462572046443156e-06</v>
+        <v>8.462572046443285e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.296993772126045e-05</v>
+        <v>1.545931168409722e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.505655270405676e-05</v>
+        <v>1.505655270402011e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.549387292255193e-05</v>
+        <v>1.549387292255058e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.493129140382042e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.519702450936243e-05</v>
+        <v>1.519702450936246e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.539277163652685e-05</v>
+        <v>3.290339767369005e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.50775579038304e-05</v>
+        <v>3.507755790383042e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.517906061373649e-05</v>
+        <v>3.268968665089974e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.593447776576737e-05</v>
+        <v>3.340316363659437e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.545376441671986e-05</v>
+        <v>1.545376441671985e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.547331314667228e-05</v>
+        <v>1.547331314667231e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.456736747643036e-05</v>
+        <v>5.456736747643028e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.427978421170296e-05</v>
+        <v>5.427978421170291e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.456735859554197e-05</v>
+        <v>5.456735859554198e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.429756875587593e-05</v>
+        <v>5.42975687558759e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.429756875587593e-05</v>
+        <v>5.42975687558759e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.450082742886006e-05</v>
+        <v>5.450082742885991e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.456736747643036e-05</v>
+        <v>5.456736747643028e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.428711640606973e-05</v>
+        <v>5.428711640606963e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.456736747643036e-05</v>
+        <v>5.456736747643028e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.456736747643036e-05</v>
+        <v>5.456736747643028e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.456736747643036e-05</v>
+        <v>5.456736747643028e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002349019307757339</v>
+        <v>0.0002349019307757335</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000379972510680222</v>
+        <v>0.0003799725106798093</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004103544203820691</v>
+        <v>0.0004103544203820695</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003402321380684162</v>
+        <v>0.0003402321380684161</v>
       </c>
       <c r="F6" t="n">
         <v>0.0002392343252554366</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003801549276774697</v>
+        <v>0.0003801549276774692</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003802214677252963</v>
+        <v>0.0003802214677252961</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003799412166546791</v>
+        <v>0.0003799412166546789</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000380250027202277</v>
+        <v>0.0003802500272022767</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002322025457674284</v>
+        <v>0.0002322025457674285</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000532019875514349</v>
+        <v>0.0005320198755143491</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001305205635803972</v>
+        <v>0.0001305205635803969</v>
       </c>
       <c r="C7" t="n">
         <v>0.000164616626149889</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000164904211968762</v>
+        <v>0.0001649042119687618</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002043019498310499</v>
+        <v>0.0002043019498310497</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000164623951093279</v>
+        <v>0.0001646239510932788</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001648376693670462</v>
+        <v>0.000164837669367046</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001649042094146163</v>
+        <v>0.0001649042094146162</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001646239583442557</v>
+        <v>0.0001646239583442554</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001649042094146163</v>
+        <v>0.0001649042094146162</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000144173929503886</v>
+        <v>0.0001216090611882833</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001649042094146163</v>
+        <v>0.0001649042094146162</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.225131904037639e-05</v>
+        <v>2.225131904037646e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.285731098958348e-05</v>
+        <v>2.285731098958352e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.304361864344329e-05</v>
+        <v>2.304361864344337e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.379901718290992e-05</v>
+        <v>2.379901718291023e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.379901718290992e-05</v>
+        <v>2.379901718291023e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.382309349740353e-05</v>
+        <v>2.382309349740377e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.265147194069709e-05</v>
+        <v>2.265147194069727e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.379901718290992e-05</v>
+        <v>2.379901718291023e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.54867107733142e-05</v>
+        <v>2.548671077331439e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.443109674420172e-05</v>
+        <v>2.443109674420187e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.387863418888502e-05</v>
+        <v>2.387863418888508e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.286061262381629e-05</v>
+        <v>2.286061262381635e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.365874962303298e-05</v>
+        <v>2.365874962303301e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4194884564062e-05</v>
+        <v>2.41948845640621e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.478144618268804e-05</v>
+        <v>2.478144618268815e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.478144618268804e-05</v>
+        <v>2.478144618268815e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.473926188024866e-05</v>
+        <v>2.473926188024883e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.403751173090854e-05</v>
+        <v>2.403751173090862e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.478144618268804e-05</v>
+        <v>2.478144618268815e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.591220380027322e-05</v>
+        <v>2.591220380027333e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.516322581107675e-05</v>
+        <v>2.516322581107698e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.47601717872257e-05</v>
+        <v>2.476017178722573e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.904731031296658e-05</v>
+        <v>6.904731031296648e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.0001973139772697763</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000235339872977358</v>
+        <v>0.0002353398729773577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002140535341067193</v>
+        <v>0.0002140535341067191</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002140535341067193</v>
+        <v>0.0002140535341067191</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002110948963313853</v>
+        <v>0.0002110948963313763</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000259783094598563</v>
+        <v>0.0002597830945985628</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002140535341067193</v>
+        <v>0.0002140535341067191</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002001576616681825</v>
+        <v>0.0002001576616681813</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000193906955409505</v>
+        <v>0.0001939069554095048</v>
       </c>
       <c r="L2" t="n">
         <v>0.0002229212460156785</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.777053384210198e-06</v>
+        <v>7.777053384210193e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.727691656801596e-06</v>
+        <v>6.7276916568016e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.777053384210198e-06</v>
+        <v>7.777053384210193e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.04857322554944e-06</v>
+        <v>7.048573225549333e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.048573225549388e-06</v>
+        <v>7.048573225549337e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.710666395539186e-06</v>
+        <v>7.710666395539195e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.777053384210198e-06</v>
+        <v>7.777053384210193e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.49735973688856e-06</v>
+        <v>7.497359736888524e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.777053384210198e-06</v>
+        <v>7.777053384210193e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.777053384210198e-06</v>
+        <v>7.777053384210193e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.777053384210198e-06</v>
+        <v>7.777053384210193e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.310567475277556e-05</v>
+        <v>1.509762386104534e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.471846729238235e-05</v>
+        <v>1.47184672923823e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.516195005831334e-05</v>
+        <v>1.516195005831339e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458637758947256e-05</v>
+        <v>1.458637758947246e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.483480461677757e-05</v>
+        <v>1.483480461677747e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.503123687237439e-05</v>
+        <v>1.50312368723743e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.42984303595724e-05</v>
+        <v>3.429843035957228e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.282598110545384e-05</v>
+        <v>1.481793021372367e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.341517025565657e-05</v>
+        <v>3.341517025565642e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.509310060115632e-05</v>
+        <v>1.509310060115627e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.511161695920534e-05</v>
+        <v>1.511161695920529e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.604578562860045e-05</v>
+        <v>5.604578562860038e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.575924644451264e-05</v>
+        <v>5.575924644451252e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.604575559153619e-05</v>
+        <v>5.604575559153605e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.577552232021455e-05</v>
+        <v>5.577552232021442e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.577552232021455e-05</v>
+        <v>5.577552232021442e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.597939863992944e-05</v>
+        <v>5.597939863992931e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.604578562860045e-05</v>
+        <v>5.604578562860038e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.576609198127876e-05</v>
+        <v>5.576609198127869e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.604578562860045e-05</v>
+        <v>5.604578562860038e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.604578562860045e-05</v>
+        <v>5.604578562860038e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.604578562860045e-05</v>
+        <v>5.604578562860038e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457295894786856</v>
+        <v>0.000245729589478685</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003980159365107927</v>
+        <v>0.0003980159365107918</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004298922814344922</v>
+        <v>0.0004298922814344911</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003563020038142287</v>
+        <v>0.0003563020038142282</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002502906257109221</v>
+        <v>0.0002502906257109214</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003981970147965395</v>
+        <v>0.0003981970147965393</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003982634017852649</v>
+        <v>0.0003982634017852639</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003979837081378885</v>
+        <v>0.0003979837081378881</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003982933790771435</v>
+        <v>0.000398293379077143</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002428961956017974</v>
+        <v>0.000242896195601797</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005575977234348919</v>
+        <v>0.0005575977234348904</v>
       </c>
     </row>
     <row r="7">
@@ -2707,25 +2707,25 @@
         <v>0.0002370685124299286</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001907320220146185</v>
+        <v>0.0001907320220146186</v>
       </c>
       <c r="G7" t="n">
         <v>0.000190945336345356</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001910117233340271</v>
+        <v>0.0001910117233340269</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001907320296867054</v>
+        <v>0.0001907320296867051</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001910117233340271</v>
+        <v>0.0001910117233340269</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000140451077673708</v>
+        <v>0.0001404510776737082</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001910117233340271</v>
+        <v>0.0001910117233340269</v>
       </c>
     </row>
     <row r="8">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.470317080570988e-05</v>
+        <v>2.470317080570983e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.302162718945216e-05</v>
+        <v>2.302162718945213e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.259543214190582e-05</v>
+        <v>2.259543214190577e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.370279827026794e-05</v>
@@ -2750,10 +2750,10 @@
         <v>2.370279827026794e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.416662044128448e-05</v>
+        <v>2.416662044128444e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.254121834259023e-05</v>
+        <v>2.254121834259018e-05</v>
       </c>
       <c r="I8" t="n">
         <v>2.370279827026794e-05</v>
@@ -2762,10 +2762,10 @@
         <v>2.465218969266413e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.478701097910018e-05</v>
+        <v>2.47870109791e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3868102388617e-05</v>
+        <v>2.386810238861697e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.521239825552129e-05</v>
+        <v>2.521239825552124e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.362420400032434e-05</v>
+        <v>2.362420400032431e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.376287170615982e-05</v>
+        <v>2.376287170615981e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.455112384681279e-05</v>
+        <v>2.45511238468128e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.455112384681279e-05</v>
+        <v>2.45511238468128e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.495966812416228e-05</v>
+        <v>2.495966812416227e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.374283912791649e-05</v>
+        <v>2.374283912791648e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.455112384681279e-05</v>
+        <v>2.45511238468128e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.52329285806089e-05</v>
+        <v>2.523292858060891e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.536080077299507e-05</v>
+        <v>2.536080077299487e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.457312165719678e-05</v>
+        <v>2.457312165719672e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.881951424520644e-05</v>
+        <v>7.881951424520655e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002064834359259809</v>
+        <v>0.0002064834359259811</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002539331552619357</v>
+        <v>0.0002539331552619358</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002183132195402448</v>
+        <v>0.0002183132195402463</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002183132195402448</v>
+        <v>0.0002183132195402463</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002224531614704944</v>
+        <v>0.0002224531614704987</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002656626302862933</v>
+        <v>0.0002656626302862936</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002183132195402448</v>
+        <v>0.0002183132195402463</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002277509741660672</v>
+        <v>0.0002277509741660675</v>
       </c>
       <c r="K2" t="n">
         <v>0.0001987206311797725</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002362506963759094</v>
+        <v>0.0002362506963759098</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.033137865801146e-06</v>
+        <v>8.033137865801241e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.973164309892491e-06</v>
+        <v>6.973164309892548e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.033137865801146e-06</v>
+        <v>8.033137865801241e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.320163517487555e-06</v>
+        <v>7.320163517487637e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.320163517487591e-06</v>
+        <v>7.320163517487636e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.96626178855278e-06</v>
+        <v>7.966261788552815e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.033137865801146e-06</v>
+        <v>8.033137865801241e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.750490322695027e-06</v>
+        <v>7.750490322695071e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.033137865801146e-06</v>
+        <v>8.033137865801241e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.033137865801146e-06</v>
+        <v>8.033137865801241e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.033137865801146e-06</v>
+        <v>8.033137865801241e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.511299145321697e-05</v>
+        <v>1.511299145321708e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.471992429429989e-05</v>
+        <v>1.471992429430005e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.296417044345342e-05</v>
+        <v>1.518676824863586e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458577436072938e-05</v>
+        <v>1.458577436072934e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484677414433513e-05</v>
+        <v>1.484677414433514e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.504611537596864e-05</v>
+        <v>3.232943113970086e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.408614472446382e-05</v>
+        <v>3.408614472446407e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.483034391011095e-05</v>
+        <v>3.211365967384319e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.559207877921154e-05</v>
+        <v>1.559207877921165e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.508972469323912e-05</v>
+        <v>1.508972469323926e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.512820896449271e-05</v>
+        <v>1.512820896449283e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.382360445755467e-05</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.353618213007901e-05</v>
+        <v>5.35361821300792e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.382358687963028e-05</v>
+        <v>5.382358687963056e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.355339273686678e-05</v>
+        <v>5.355339273686708e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.355339273686678e-05</v>
+        <v>5.355339273686708e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.375672838030632e-05</v>
+        <v>5.375672838030649e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.382360445755467e-05</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.354095691444842e-05</v>
+        <v>5.354095691444871e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.382360445755467e-05</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.382360445755467e-05</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.382360445755467e-05</v>
+        <v>5.382360445755488e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002338352051555596</v>
+        <v>0.0002338352051555599</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003783777001962798</v>
+        <v>0.0003783777001962799</v>
       </c>
       <c r="D6" t="n">
         <v>0.0004086477503252015</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003387795484485679</v>
+        <v>0.0003387795484485674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002381495902124237</v>
+        <v>0.0002381495902124238</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003785578283551014</v>
+        <v>0.0003785578283551015</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000378624704432532</v>
+        <v>0.0003786247044325317</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003783420568892435</v>
+        <v>0.0003783420568892439</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003786531597426998</v>
+        <v>0.0003786531597426997</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002311456658692287</v>
+        <v>0.0002311456658692289</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005298694435519212</v>
+        <v>0.0005298694435519213</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001363623516663548</v>
+        <v>0.0001363623516663551</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001721384588266232</v>
+        <v>0.0001721384588266236</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001724258838102717</v>
+        <v>0.0001724258838102718</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002137597751793303</v>
+        <v>0.0002137597751793308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001721432262579624</v>
+        <v>0.0001721432262579627</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001723590050768504</v>
+        <v>0.0001723590050768507</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001724258811540989</v>
+        <v>0.0001724258811540991</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001721432336109928</v>
+        <v>0.0001721432336109929</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001724258811540989</v>
+        <v>0.0001724258811540991</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001515305316536635</v>
+        <v>0.0001270154595233634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001724258811540989</v>
+        <v>0.0001724258811540991</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.546633064725675e-05</v>
+        <v>2.546633064725679e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.269130315789842e-05</v>
+        <v>2.269130315789844e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.207614686577292e-05</v>
+        <v>2.207614686577297e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.355728062130825e-05</v>
+        <v>2.35572806213083e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.355728062130825e-05</v>
+        <v>2.35572806213083e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.386253545977778e-05</v>
+        <v>2.386253545977784e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.235532216590432e-05</v>
+        <v>2.235532216590437e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.355728062130825e-05</v>
+        <v>2.35572806213083e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.405151290430906e-05</v>
+        <v>2.405151290430909e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.465380968787704e-05</v>
+        <v>2.465380968787737e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.347767270714283e-05</v>
+        <v>2.347767270714288e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.613890768220507e-05</v>
+        <v>2.613890768220509e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.355963414570202e-05</v>
+        <v>2.355963414570205e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.368021882021146e-05</v>
+        <v>2.368021882021151e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.461677904240408e-05</v>
+        <v>2.461677904240413e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.461677904240408e-05</v>
+        <v>2.461677904240413e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.496002826956558e-05</v>
+        <v>2.496002826956557e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.379633535158399e-05</v>
+        <v>2.379633535158405e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.461677904240408e-05</v>
+        <v>2.461677904240413e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.51442721943019e-05</v>
+        <v>2.514427219430192e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.543250732354456e-05</v>
+        <v>2.543250732354499e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.448762491513113e-05</v>
+        <v>2.448762491513118e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.406952072551888e-05</v>
+        <v>8.406952072551899e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002181561387013354</v>
+        <v>0.0002181561387013351</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002567692941055753</v>
+        <v>0.000256769294105575</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002208444835713965</v>
+        <v>0.0002208444835713953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002208444835713965</v>
+        <v>0.0002208444835713953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002296383831922625</v>
+        <v>0.0002296383831922598</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002691447238549736</v>
+        <v>0.0002691447238549735</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002208444835713965</v>
+        <v>0.0002208444835713953</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002565380342690677</v>
+        <v>0.0002565380342690679</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002025748062918032</v>
+        <v>0.0002025748062918029</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002467231865952742</v>
+        <v>0.000246723186595274</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.844923908727853e-06</v>
+        <v>8.844923908727866e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.731690211358066e-06</v>
+        <v>7.73169021135808e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.844923908727853e-06</v>
+        <v>8.844923908727866e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.169275209326774e-06</v>
+        <v>8.169275209326686e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.169275209326752e-06</v>
+        <v>8.169275209326679e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.77769975374805e-06</v>
+        <v>8.777699753751087e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.844923908727853e-06</v>
+        <v>8.844923908727866e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.560336297367503e-06</v>
+        <v>8.560336297373209e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.844923908727853e-06</v>
+        <v>8.844923908727866e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.844923908727853e-06</v>
+        <v>8.844923908727866e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.844923908727853e-06</v>
+        <v>8.844923908727866e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.38759177010952e-05</v>
+        <v>3.387591770109521e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.57138684833672e-05</v>
+        <v>1.571386848336719e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.61628340766816e-05</v>
+        <v>1.616283407668161e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.553989329305287e-05</v>
+        <v>1.553989329305285e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.584881477808964e-05</v>
+        <v>1.584881477808961e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.380869354611545e-05</v>
+        <v>3.380869354611538e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.61578873124706e-05</v>
+        <v>3.61578873124705e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.583054772810241e-05</v>
+        <v>1.583054772810234e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.435319893909798e-05</v>
+        <v>3.435319893909794e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.608493123911716e-05</v>
+        <v>1.608493123911714e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.61323596753554e-05</v>
+        <v>1.613235967535543e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.497429088176277e-05</v>
+        <v>5.497429088176271e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.46860723390811e-05</v>
+        <v>5.468607233908104e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.49742697112905e-05</v>
+        <v>5.497426971129044e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.471905662033071e-05</v>
+        <v>5.471905662033055e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.471905662033071e-05</v>
+        <v>5.471905662033055e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.490706672678299e-05</v>
+        <v>5.490706672678291e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.497429088176277e-05</v>
+        <v>5.497429088176271e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.468970327040239e-05</v>
+        <v>5.468970327040231e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.497429088176277e-05</v>
+        <v>5.497429088176271e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.497429088176277e-05</v>
+        <v>5.497429088176271e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.497429088176277e-05</v>
+        <v>5.497429088176271e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002355452301602021</v>
+        <v>0.0002355452301602028</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003808961931719498</v>
+        <v>0.0003808961931719499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004113151017813703</v>
+        <v>0.0004113151017813705</v>
       </c>
       <c r="E6" t="n">
         <v>0.0003410782937201315</v>
@@ -3462,22 +3462,22 @@
         <v>0.0002398929034796563</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003810604164399551</v>
+        <v>0.0003810604164399552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000381127640595212</v>
+        <v>0.0003811276405952122</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003808430529835747</v>
+        <v>0.000380843052983575</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000381156251731325</v>
+        <v>0.0003811562517313251</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002328409621422525</v>
+        <v>0.0002328409621422528</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000533200641718083</v>
+        <v>0.0005332006417180835</v>
       </c>
     </row>
     <row r="7">
@@ -3490,34 +3490,34 @@
         <v>0.0001313973382011598</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000165671750275663</v>
+        <v>0.0001656717502756631</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001659599719707258</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002055599177445454</v>
+        <v>0.0002055599177445455</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001656753738484252</v>
+        <v>0.0001656753738484254</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000165892744663365</v>
+        <v>0.0001658927446633649</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001659599688183446</v>
+        <v>0.0001659599688183447</v>
       </c>
       <c r="I7" t="n">
         <v>0.0001656753812069844</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001659599688183446</v>
+        <v>0.0001659599688183447</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001459342462266996</v>
+        <v>0.0001451217772369867</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001659599688183446</v>
+        <v>0.0001659599688183447</v>
       </c>
     </row>
     <row r="8">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.729465408307197e-05</v>
+        <v>2.729465408307195e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.271921262863385e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.253967266788323e-05</v>
+        <v>2.253967266788319e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.400887145213541e-05</v>
@@ -3545,19 +3545,19 @@
         <v>2.414693600219115e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.28116619033843e-05</v>
+        <v>2.281166190338428e-05</v>
       </c>
       <c r="I8" t="n">
         <v>2.400887145213541e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.425576969182712e-05</v>
+        <v>2.42557696918271e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.479603920951246e-05</v>
+        <v>2.479603920951236e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.368597582014179e-05</v>
+        <v>2.368597582014178e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3573,31 +3573,31 @@
         <v>2.374151457183539e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.417062528005325e-05</v>
+        <v>2.417062528005321e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.50908146666693e-05</v>
+        <v>2.509081466666929e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.50908146666693e-05</v>
+        <v>2.509081466666929e-05</v>
       </c>
       <c r="G9" t="n">
         <v>2.533260927400451e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.428387223087574e-05</v>
+        <v>2.428387223087572e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.50908146666693e-05</v>
+        <v>2.509081466666929e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5724945105774e-05</v>
+        <v>2.572494510577401e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.562078543420151e-05</v>
+        <v>2.562078543420142e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.48154608436188e-05</v>
+        <v>2.481546084361881e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.328627833446991e-05</v>
+        <v>7.328627833446957e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002036041184664387</v>
+        <v>0.000203604118466439</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002545092525409223</v>
+        <v>0.0002545092525409212</v>
       </c>
       <c r="E2" t="n">
         <v>0.0002200310953525521</v>
@@ -3698,22 +3698,22 @@
         <v>0.0002200310953525521</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002201960300747265</v>
+        <v>0.0002201960300747109</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002653814320927508</v>
+        <v>0.0002653814320927501</v>
       </c>
       <c r="I2" t="n">
         <v>0.0002200310953525521</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002173052489693049</v>
+        <v>0.000217305248969304</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001995138663597104</v>
+        <v>0.000199513866359709</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002271160688826433</v>
+        <v>0.0002271160688826421</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.789838540568277e-06</v>
+        <v>7.78983854056724e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.736245506874554e-06</v>
+        <v>6.736245506874532e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.789838540568277e-06</v>
+        <v>7.78983854056724e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.063370770053729e-06</v>
+        <v>7.063370770053771e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.063370770053728e-06</v>
+        <v>7.063370770053768e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.723257471015088e-06</v>
+        <v>7.72325747101438e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.789838540568277e-06</v>
+        <v>7.78983854056724e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.508885500998028e-06</v>
+        <v>7.508885500998633e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.789838540568277e-06</v>
+        <v>7.78983854056724e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.789838540568277e-06</v>
+        <v>7.78983854056724e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.789838540568277e-06</v>
+        <v>7.78983854056724e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.320121177151233e-05</v>
+        <v>1.517123323065631e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.478829632031293e-05</v>
+        <v>1.478829632031295e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.525871362316203e-05</v>
+        <v>1.525871362316102e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.465377666915522e-05</v>
+        <v>1.465377666915528e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.490762093161498e-05</v>
+        <v>1.4907620931615e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.313463070195851e-05</v>
+        <v>3.313463070195737e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.439650976041822e-05</v>
+        <v>3.439650976041672e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.489028019108779e-05</v>
+        <v>3.292025873194275e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.351369890318096e-05</v>
+        <v>3.351369890317888e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.516307802128425e-05</v>
+        <v>1.516307802128333e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.518498600884832e-05</v>
+        <v>1.518498600884798e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.602977410080331e-05</v>
+        <v>5.602977410080265e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.574305474822616e-05</v>
+        <v>5.574305474822613e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.602974481955765e-05</v>
+        <v>5.602974481955676e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.575960685324206e-05</v>
+        <v>5.575960685324212e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.575960685324206e-05</v>
+        <v>5.575960685324212e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.596319303124959e-05</v>
+        <v>5.596319303124867e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.602977410080331e-05</v>
+        <v>5.602977410080265e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.574882106123371e-05</v>
+        <v>5.574882106123367e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.602977410080331e-05</v>
+        <v>5.602977410080265e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.602977410080331e-05</v>
+        <v>5.602977410080265e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.602977410080331e-05</v>
+        <v>5.602977410080265e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457271676430837</v>
+        <v>0.0002457271676430811</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000397994820273051</v>
+        <v>0.0003979948202730503</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004298659488839411</v>
+        <v>0.0004298659488839395</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000356285089143477</v>
+        <v>0.0003562850891434773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002502871248636084</v>
+        <v>0.0002502871248636089</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003981745946924271</v>
+        <v>0.0003981745946924264</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003982411757620346</v>
+        <v>0.0003982411757620354</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003979602227224109</v>
+        <v>0.0003979602227224111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003982711491617583</v>
+        <v>0.0003982711491617575</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002428941416391522</v>
+        <v>0.0002428941416391526</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005575548102816237</v>
+        <v>0.0005575548102816253</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001510907071096543</v>
+        <v>0.0001510907071096537</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001910140563179324</v>
+        <v>0.0001910140563179331</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000191300778076955</v>
+        <v>0.0001913007780769546</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002374213817254833</v>
+        <v>0.0002374213817254839</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001910198149438424</v>
+        <v>0.0001910198149438423</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000191234194600956</v>
+        <v>0.0001912341946009555</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001913007756705096</v>
+        <v>0.0001913007756705095</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001910198226309399</v>
+        <v>0.0001910198226309406</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001913007756705096</v>
+        <v>0.0001913007756705095</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001670576809026911</v>
+        <v>0.0001680029050413636</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001913007756705096</v>
+        <v>0.0001913007756705095</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.548628216571078e-05</v>
+        <v>2.548628216571011e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.317469698933085e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.218259837026113e-05</v>
+        <v>2.218259837026074e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.360746794667798e-05</v>
+        <v>2.360746794667801e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.360746794667798e-05</v>
+        <v>2.360746794667801e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.411681759149579e-05</v>
+        <v>2.411681759149544e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.245720385274449e-05</v>
+        <v>2.245720385274417e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.360746794667798e-05</v>
+        <v>2.360746794667801e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.429724876359971e-05</v>
+        <v>2.429724876360006e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.483073134134199e-05</v>
+        <v>2.483073134134145e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.37893698430916e-05</v>
+        <v>2.378936984309114e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.603774987792353e-05</v>
+        <v>2.603774987792268e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.385613688865241e-05</v>
+        <v>2.385613688865242e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.361178189959878e-05</v>
+        <v>2.36117818995976e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.453582976650107e-05</v>
+        <v>2.45358297665011e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.453582976650107e-05</v>
+        <v>2.45358297665011e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.502813532352069e-05</v>
+        <v>2.502813532352043e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.372577027243503e-05</v>
+        <v>2.372577027243382e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.453582976650107e-05</v>
+        <v>2.45358297665011e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.510044524559793e-05</v>
+        <v>2.51004452455974e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.547793380463114e-05</v>
+        <v>2.547793380463076e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.454373710251761e-05</v>
+        <v>2.454373710251726e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.130342075174038e-05</v>
+        <v>8.130342075173969e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.0002100005021519486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002544506438587375</v>
+        <v>0.0002544506438587369</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002190374172076137</v>
+        <v>0.0002190374172076113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002190374172076137</v>
+        <v>0.0002190374172076113</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002252313765716257</v>
+        <v>0.0002252313765716198</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002682880457311488</v>
+        <v>0.0002682880457311472</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002190374172076137</v>
+        <v>0.0002190374172076113</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002516273766250275</v>
+        <v>0.000251627376625027</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002002517322008407</v>
+        <v>0.0002002517322008381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002395797993109459</v>
+        <v>0.0002395797993109451</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.995810337532478e-06</v>
+        <v>7.995810337531652e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.938021267482613e-06</v>
+        <v>6.938021267482626e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.995810337532478e-06</v>
+        <v>7.995810337531652e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.305761543105534e-06</v>
+        <v>7.30576154310553e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.30576154310555e-06</v>
+        <v>7.30576154310553e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.928428974973993e-06</v>
+        <v>7.928428974973261e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.995810337532478e-06</v>
+        <v>7.995810337531652e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.709788576156923e-06</v>
+        <v>7.709788576156736e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.995810337532478e-06</v>
+        <v>7.995810337531652e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.995810337532478e-06</v>
+        <v>7.995810337531652e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.995810337532478e-06</v>
+        <v>7.995810337531652e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.238138643647969e-05</v>
+        <v>1.511449456044619e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.472260187631288e-05</v>
+        <v>1.472260187631293e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.518660974897554e-05</v>
+        <v>1.518663127051667e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458325299530092e-05</v>
+        <v>1.458325299530086e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484572816883856e-05</v>
+        <v>1.484572816883853e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.504711319788783e-05</v>
+        <v>1.504711319788757e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.407055765922342e-05</v>
+        <v>3.407055765922313e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.482847279907111e-05</v>
+        <v>3.209536467510415e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.560129608106937e-05</v>
+        <v>3.274564919407366e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.50932313217884e-05</v>
+        <v>1.50932313217883e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51305926581245e-05</v>
+        <v>1.513059265812436e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.37549271117789e-05</v>
+        <v>5.375492711177869e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.346748506913875e-05</v>
+        <v>5.346748506913879e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.375491231012489e-05</v>
+        <v>5.375491231012455e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.348924737064386e-05</v>
+        <v>5.348924737064395e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.348924737064386e-05</v>
+        <v>5.348924737064395e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.368754574922052e-05</v>
+        <v>5.368754574922008e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.37549271117789e-05</v>
+        <v>5.375492711177869e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.346890535040359e-05</v>
+        <v>5.346890535040365e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.37549271117789e-05</v>
+        <v>5.375492711177869e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.37549271117789e-05</v>
+        <v>5.375492711177869e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.37549271117789e-05</v>
+        <v>5.375492711177869e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002337440758365784</v>
+        <v>0.0002337440758365768</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003782395275265697</v>
+        <v>0.0003782395275265688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004084907421169332</v>
+        <v>0.000408490742116932</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003386521493100884</v>
+        <v>0.0003386521493100887</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000238058071836978</v>
+        <v>0.0002380580718369765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003784116291805879</v>
+        <v>0.0003784116291805845</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003784790105433308</v>
+        <v>0.0003784790105433303</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003781929887817713</v>
+        <v>0.0003781929887817693</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003785074551302401</v>
+        <v>0.0003785074551302388</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002310555501151236</v>
+        <v>0.0002310555501151218</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000529666752406751</v>
+        <v>0.0005296667524067477</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001363727196563701</v>
+        <v>0.0001363727196563697</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001721531272499298</v>
+        <v>0.0001721531272499292</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001724405719731036</v>
+        <v>0.0001724405719731029</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000213776074434992</v>
+        <v>0.0002137760744349914</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001721545401411418</v>
+        <v>0.0001721545401411414</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001723731879300113</v>
+        <v>0.0001723731879300104</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00017244056929257</v>
+        <v>0.0001724405692925691</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001721545475311942</v>
+        <v>0.0001721545475311941</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00017244056929257</v>
+        <v>0.0001724405692925691</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001270247078174707</v>
+        <v>0.0001515427166913981</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00017244056929257</v>
+        <v>0.0001724405692925691</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.408915690643908e-05</v>
+        <v>3.40891569064389e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.311646418492915e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.20363081371799e-05</v>
+        <v>2.203630813717978e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.371586882829568e-05</v>
+        <v>2.37158688282957e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.371586882829568e-05</v>
+        <v>2.37158688282957e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.472063282043392e-05</v>
+        <v>2.472063282043378e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.227163155913224e-05</v>
+        <v>2.227163155913216e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.371586882829568e-05</v>
+        <v>2.37158688282957e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.348483332122431e-05</v>
+        <v>2.348483332122419e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.537283058851726e-05</v>
+        <v>2.537283058851723e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.338920927478319e-05</v>
+        <v>2.338920927478316e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.466073857100731e-05</v>
+        <v>3.466073857100707e-05</v>
       </c>
       <c r="C9" t="n">
         <v>2.402640592094312e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.364838966381534e-05</v>
+        <v>2.36483896638152e-05</v>
       </c>
       <c r="E9" t="n">
         <v>2.478311236076824e-05</v>
@@ -4374,22 +4374,22 @@
         <v>2.478311236076824e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.584277470292974e-05</v>
+        <v>2.584277470292962e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.374669799353847e-05</v>
+        <v>2.374669799353839e-05</v>
       </c>
       <c r="I9" t="n">
         <v>2.478311236076824e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.490592866822074e-05</v>
+        <v>2.490592866822069e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.616184075663695e-05</v>
+        <v>2.616184075663681e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.444121095018617e-05</v>
+        <v>2.444121095018594e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.332251137702232e-05</v>
+        <v>8.332251137702261e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002166425821214579</v>
+        <v>0.0002166425821214575</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00025293896657721</v>
+        <v>0.0002529389665772102</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002208035569144129</v>
+        <v>0.0002208035569144128</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002208035569144129</v>
+        <v>0.0002208035569144128</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002285210671437063</v>
+        <v>0.0002285210671437047</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002696255025663369</v>
+        <v>0.0002696255025663373</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002208035569144129</v>
+        <v>0.0002208035569144128</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002609882497868031</v>
+        <v>0.0002609882497868035</v>
       </c>
       <c r="K2" t="n">
         <v>0.0002018301883058993</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002450931595243696</v>
+        <v>0.0002450931595243697</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.65288978120423e-06</v>
+        <v>8.652889781204423e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.541272952922101e-06</v>
+        <v>7.541272952922095e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.65288978120423e-06</v>
+        <v>8.652889781204423e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.037877665053772e-06</v>
+        <v>8.037877665053939e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.037877665053679e-06</v>
+        <v>8.037877665053951e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.58401744372841e-06</v>
+        <v>8.584017443728687e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.65288978120423e-06</v>
+        <v>8.652889781204423e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.357184892460671e-06</v>
+        <v>8.357184892460874e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.65288978120423e-06</v>
+        <v>8.652889781204445e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.65288978120423e-06</v>
+        <v>8.652889781204423e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.65288978120423e-06</v>
+        <v>8.652889781204423e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.350351614749693e-05</v>
+        <v>1.58714385073669e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.546936716645221e-05</v>
+        <v>1.546936716645218e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.591782337644885e-05</v>
+        <v>1.591782337644892e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.53126457680575e-05</v>
+        <v>1.531264576805762e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.559879347164543e-05</v>
+        <v>1.55987934716454e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.343464381002105e-05</v>
+        <v>3.343464381002117e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.57144245142005e-05</v>
+        <v>3.571442451420063e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.557573361862332e-05</v>
+        <v>3.320781125875354e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.396743988476394e-05</v>
+        <v>1.637346486125525e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.583971009124313e-05</v>
+        <v>1.583971009124316e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.589470405404856e-05</v>
+        <v>1.589470405404859e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.467543576404724e-05</v>
+        <v>5.467543576404734e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.43873206655727e-05</v>
+        <v>5.438732066557274e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.467541786412437e-05</v>
+        <v>5.467541786412452e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.442942967777286e-05</v>
+        <v>5.442942967777312e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.442942967777286e-05</v>
+        <v>5.442942967777312e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.460656342657135e-05</v>
+        <v>5.460656342657133e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.467543576404724e-05</v>
+        <v>5.467543576404734e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.437973087530363e-05</v>
+        <v>5.437973087530371e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.467543576404724e-05</v>
+        <v>5.467543576404734e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.467543576404724e-05</v>
+        <v>5.467543576404734e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.467543576404724e-05</v>
+        <v>5.467543576404734e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002351283661971103</v>
+        <v>0.0002351283661971109</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003802726428222139</v>
+        <v>0.0003802726428222144</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004106251501429645</v>
+        <v>0.0004106251501429653</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003405033341964536</v>
+        <v>0.0003405033341964541</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002394698875762123</v>
+        <v>0.0002394698875762125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003804157178513605</v>
+        <v>0.0003804157178513606</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003804845901891087</v>
+        <v>0.0003804845901891091</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003801888853000926</v>
+        <v>0.0003801888853000924</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003805131568746458</v>
+        <v>0.0003805131568746464</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002324282997083076</v>
+        <v>0.0002324282997083078</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005323213206603247</v>
+        <v>0.0005323213206603258</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001311341385605497</v>
+        <v>0.0001311341385605499</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001653527023763694</v>
+        <v>0.0001653527023763696</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001656408205248487</v>
+        <v>0.0001656408205248486</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002051650819786417</v>
+        <v>0.0002051650819786416</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001653451052485769</v>
+        <v>0.000165345105248577</v>
       </c>
       <c r="G7" t="n">
         <v>0.000165571945137368</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001656408174748438</v>
+        <v>0.000165640817474844</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001653451125861003</v>
+        <v>0.0001653451125861006</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001656408174748438</v>
+        <v>0.000165640817474844</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000144836359754257</v>
+        <v>0.0001448363597542572</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001656408174748438</v>
+        <v>0.000165640817474844</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.819510156487283e-05</v>
+        <v>5.819510156487272e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.336888899278677e-05</v>
+        <v>2.336888899278681e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.24560620905339e-05</v>
+        <v>2.245606209053388e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.392785032007182e-05</v>
+        <v>2.392785032007202e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.392785032007182e-05</v>
+        <v>2.392785032007202e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.699791675638976e-05</v>
+        <v>2.699791675638975e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.262445179547964e-05</v>
+        <v>2.262445179547974e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.392785032007182e-05</v>
+        <v>2.392785032007202e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.388460434260802e-05</v>
+        <v>2.388460434260807e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.514229361618223e-05</v>
+        <v>2.514229361618211e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.359539754712573e-05</v>
+        <v>2.359539754712564e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.841218284027447e-05</v>
+        <v>5.841218284027453e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.436099793520645e-05</v>
+        <v>2.436099793520641e-05</v>
       </c>
       <c r="D9" t="n">
         <v>2.40351695274676e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.501144035129944e-05</v>
+        <v>2.50114403512995e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.501144035129944e-05</v>
+        <v>2.501144035129948e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.81244626000664e-05</v>
+        <v>2.812446260006645e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.410623448615112e-05</v>
+        <v>2.410623448615125e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.501144035129944e-05</v>
+        <v>2.50114403512995e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.541984416272333e-05</v>
+        <v>2.541984416272339e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.595195261475513e-05</v>
+        <v>2.595195261475507e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.470707968642881e-05</v>
+        <v>2.470707968642875e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001883585416468595</v>
+        <v>0.0001883585416468594</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002078188942697028</v>
+        <v>0.0002078188942697021</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001966769740404309</v>
+        <v>0.0001966769740404304</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002078188942697028</v>
+        <v>0.0002078188942697021</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002078188942697028</v>
+        <v>0.0002078188942697021</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001888222617823289</v>
+        <v>0.0001888222617823283</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002038699187735628</v>
+        <v>0.0002038699187735645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002078188942697028</v>
+        <v>0.0002078188942697021</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001973971314192453</v>
+        <v>0.0001973971314192456</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001834198150645252</v>
+        <v>0.000183419815064526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001920505311137833</v>
+        <v>0.0001920505311137788</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.027221813380596e-06</v>
+        <v>7.027221813380243e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.291283185805955e-06</v>
+        <v>6.291283185805515e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.027221813380596e-06</v>
+        <v>7.027221813380243e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.339469236671884e-06</v>
+        <v>6.339469236671555e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.33946923667188e-06</v>
+        <v>6.339469236671554e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.962028001241713e-06</v>
+        <v>6.962028001241275e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.027221813380596e-06</v>
+        <v>7.027221813380243e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.754487183324777e-06</v>
+        <v>6.754487183324648e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.027221813380596e-06</v>
+        <v>7.027221813380243e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.027221813380596e-06</v>
+        <v>7.027221813380243e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.027221813380596e-06</v>
+        <v>7.027221813380243e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.219932888130513e-05</v>
+        <v>3.219932888130489e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420733772466967e-05</v>
+        <v>1.420733772466925e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.455100141086982e-05</v>
+        <v>1.455100141086948e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.399782032069951e-05</v>
+        <v>1.399782032069918e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.424180826160008e-05</v>
+        <v>1.424180826159969e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.444020629805963e-05</v>
+        <v>3.21341350691659e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.451952028914409e-05</v>
+        <v>3.227888246084647e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.192659425124963e-05</v>
+        <v>3.192659425124925e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.226864294932596e-05</v>
+        <v>3.226864294932582e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453375791672691e-05</v>
+        <v>1.453375791672654e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.452068547462713e-05</v>
+        <v>1.452068547462676e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.542088017586352e-05</v>
+        <v>5.542088017586322e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.514814554580803e-05</v>
+        <v>5.514814554580763e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.542070969737293e-05</v>
+        <v>5.54207096973726e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.514696499143948e-05</v>
+        <v>5.514696499143896e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.514696499143948e-05</v>
+        <v>5.514696499143896e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.535568636372454e-05</v>
+        <v>5.535568636372424e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.542088017586352e-05</v>
+        <v>5.542088017586322e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.514814554580803e-05</v>
+        <v>5.514814554580763e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.542088017586352e-05</v>
+        <v>5.542088017586322e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.542088017586352e-05</v>
+        <v>5.542088017586322e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.542088017586352e-05</v>
+        <v>5.542088017586322e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000247215709315175</v>
+        <v>0.0002472157093151746</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004006838452641277</v>
+        <v>0.0004006838452641282</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004328003668881065</v>
+        <v>0.000432800366888107</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003586419868442875</v>
+        <v>0.0003586419868442879</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002518147913271921</v>
+        <v>0.0002518147913271922</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004008620790374248</v>
+        <v>0.0004008620790374243</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004009272728495572</v>
+        <v>0.0004009272728495581</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004006545382195073</v>
+        <v>0.0004006545382195075</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004009574816040655</v>
+        <v>0.0004009574816040658</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002443604381046929</v>
+        <v>0.0002443604381046928</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005614918541387784</v>
+        <v>0.0005614918541387788</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001507563243906446</v>
+        <v>0.0001507563243906442</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001907107607462872</v>
+        <v>0.0001907107607462867</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001909834966176942</v>
+        <v>0.0001909834966176941</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002371320544751101</v>
+        <v>0.0002371320544751098</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001907107529406784</v>
+        <v>0.0001907107529406781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001909183015642038</v>
+        <v>0.0001909183015642035</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001909834953763428</v>
+        <v>0.0001909834953763426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001907107607462872</v>
+        <v>0.0001907107607462867</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001909834953763428</v>
+        <v>0.0001909834953763426</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001676757150450421</v>
+        <v>0.0001676757150450418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001909834953763428</v>
+        <v>0.0001909834953763426</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.377994250782085e-05</v>
+        <v>2.377994250782084e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>2.434165951225635e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.346929706211964e-05</v>
+        <v>2.346929706211963e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>2.434165951225635e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>2.434165951225635e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.365129209309337e-05</v>
+        <v>2.365129209309338e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.363600253402219e-05</v>
+        <v>2.363600253402214e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>2.434165951225635e-05</v>
       </c>
       <c r="J8" t="n">
         <v>2.342964006754811e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.373305316759398e-05</v>
+        <v>2.373305316759396e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.354978181079986e-05</v>
+        <v>2.365195157613795e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.409356076082682e-05</v>
+        <v>2.40935607608268e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.464077201902054e-05</v>
+        <v>2.464077201902058e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.396706614081862e-05</v>
+        <v>2.396706614081864e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.464077201902054e-05</v>
+        <v>2.464077201902058e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.464077201902054e-05</v>
+        <v>2.464077201902058e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.401803567689475e-05</v>
+        <v>2.401803567689476e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.403577698396456e-05</v>
+        <v>2.403577698396454e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.464077201902054e-05</v>
+        <v>2.464077201902058e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.395130778331397e-05</v>
+        <v>2.395130778331396e-05</v>
       </c>
       <c r="K9" t="n">
         <v>2.407450640644618e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.400056174947374e-05</v>
+        <v>2.40420941672759e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001769823896620231</v>
+        <v>0.0001769823896620229</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002031011974385332</v>
+        <v>0.000203101197438533</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001932936259765709</v>
+        <v>0.0001932936259765697</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002031011974385332</v>
+        <v>0.000203101197438533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002031011974385332</v>
+        <v>0.000203101197438533</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001857118367455246</v>
+        <v>0.0001857118367455359</v>
       </c>
       <c r="H2" t="n">
         <v>0.0001973220518100462</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002031011974385332</v>
+        <v>0.000203101197438533</v>
       </c>
       <c r="J2" t="n">
         <v>0.0001934830844920068</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001943370070901189</v>
+        <v>0.0001943370070901187</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002007385468840594</v>
+        <v>0.0001937831456065299</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.160532067840222e-06</v>
+        <v>7.160532067840162e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.457559465456814e-06</v>
+        <v>6.457559465456778e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.160532067840222e-06</v>
+        <v>7.160532067840174e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.51057033112296e-06</v>
+        <v>6.510570331122822e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.51057033112297e-06</v>
+        <v>6.510570331122822e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.095333875101767e-06</v>
+        <v>7.095333875101843e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.160532067840222e-06</v>
+        <v>7.160532067840174e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.887841151501554e-06</v>
+        <v>6.887841151501295e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.160532067840222e-06</v>
+        <v>7.160532067840174e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.160532067840222e-06</v>
+        <v>7.160532067840174e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.160532067840222e-06</v>
+        <v>7.160532067840174e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.415600176696665e-05</v>
+        <v>3.079917089506755e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.385359019141574e-05</v>
+        <v>1.385359019141548e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.419130254736108e-05</v>
+        <v>1.419130254736404e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.36572735549741e-05</v>
+        <v>1.365727355497414e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.389086690497242e-05</v>
+        <v>1.389086690497226e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.409080357422841e-05</v>
+        <v>3.07339727023287e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.095652515952488e-05</v>
+        <v>3.095652515952449e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.388331085062775e-05</v>
+        <v>3.052647997872878e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.460977605701399e-05</v>
+        <v>3.085490860437177e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.418096107857268e-05</v>
+        <v>1.418096107857227e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.416814816998973e-05</v>
+        <v>1.416814816998989e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.232244614639457e-05</v>
+        <v>5.232244614639447e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.204975523005566e-05</v>
+        <v>5.204975523005563e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.232227192376713e-05</v>
+        <v>5.232227192376687e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.205205719597775e-05</v>
+        <v>5.205205719597778e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.205205719597775e-05</v>
+        <v>5.205205719597778e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.225724795365625e-05</v>
+        <v>5.225724795365618e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.232244614639457e-05</v>
+        <v>5.23224461463945e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.204975523005566e-05</v>
+        <v>5.204975523005563e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.232244614639457e-05</v>
+        <v>5.23224461463945e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.232244614639457e-05</v>
+        <v>5.23224461463945e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.232244614639457e-05</v>
+        <v>5.23224461463945e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002311890709617562</v>
+        <v>0.0002311890709617556</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000374351845506385</v>
+        <v>0.0003743518455065342</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004043298397938354</v>
+        <v>0.0004043298397938348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003351286322283221</v>
+        <v>0.0003351286322283217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002354635692210611</v>
+        <v>0.0002354635692210607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000374528713647457</v>
+        <v>0.0003745287136474567</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003745939118401917</v>
+        <v>0.0003745939118401909</v>
       </c>
       <c r="I6" t="n">
         <v>0.0003743212209238565</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003746220950262009</v>
+        <v>0.0003746220950262</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002285252524161893</v>
+        <v>0.0002285252524161885</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000524392259479263</v>
+        <v>0.0005243922594792615</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001336424445790535</v>
+        <v>0.0001336424445790538</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001688102047834627</v>
+        <v>0.0001688102047834618</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001690828969612105</v>
+        <v>0.0001690828969612102</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002097077258719478</v>
+        <v>0.0002097077258719467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001688101974345143</v>
+        <v>0.0001688101974345135</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001690176975070629</v>
+        <v>0.0001690176975070627</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001690828956998014</v>
+        <v>0.0001690828956998009</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001688102047834627</v>
+        <v>0.0001688102047834618</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001690828956998014</v>
+        <v>0.0001690828956998009</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001244570413137015</v>
+        <v>0.000124457041313701</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001690828956998014</v>
+        <v>0.0001690828956998009</v>
       </c>
     </row>
     <row r="8">
@@ -5510,34 +5510,34 @@
         <v>2.374143038804887e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.436881977115278e-05</v>
+        <v>2.436881977115274e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.351478981936108e-05</v>
+        <v>2.351478981936207e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.436881977115278e-05</v>
+        <v>2.436881977115274e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.436881977115278e-05</v>
+        <v>2.436881977115274e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36548662168908e-05</v>
+        <v>2.365486621689071e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.359101326876279e-05</v>
+        <v>2.359101326876278e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.436881977115278e-05</v>
+        <v>2.436881977115274e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.333896735554543e-05</v>
+        <v>2.333896735554537e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.368428180520959e-05</v>
+        <v>2.368428180520956e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3570086471472e-05</v>
+        <v>2.35466118965989e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5550,34 +5550,34 @@
         <v>2.414867049783149e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.473027913930716e-05</v>
+        <v>2.473027913930711e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.405639255276127e-05</v>
+        <v>2.405639255276155e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.473027913930716e-05</v>
+        <v>2.473027913930711e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.473027913930716e-05</v>
+        <v>2.473027913930711e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.409013347923654e-05</v>
+        <v>2.409013347923638e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.408840380473074e-05</v>
+        <v>2.408840380473067e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.473027913930716e-05</v>
+        <v>2.473027913930711e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.398525386766504e-05</v>
+        <v>2.398525386766494e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.412544663834236e-05</v>
+        <v>2.41254466383423e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.407015492697134e-05</v>
+        <v>2.407015492697128e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001875187311682302</v>
+        <v>0.0001875187311682287</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002103420983600301</v>
+        <v>0.000210342098360028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002095211526585454</v>
+        <v>0.0002095211526585455</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002103420983600301</v>
+        <v>0.000210342098360028</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002103420983600301</v>
+        <v>0.000210342098360028</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001969439593866439</v>
+        <v>0.0001969439593866412</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002169173070727709</v>
+        <v>0.0002169173070727738</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002103420983600301</v>
+        <v>0.000210342098360028</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000203207254132332</v>
+        <v>0.000203207254132331</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002091621389990651</v>
+        <v>0.0002091621389990633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002090097790224593</v>
+        <v>0.000209009779022474</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.27814463466213e-06</v>
+        <v>7.278144634662047e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.587564831986151e-06</v>
+        <v>6.587564831985925e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.27814463466213e-06</v>
+        <v>7.278144634662044e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.643798311945164e-06</v>
+        <v>6.643798311945082e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.643798311945197e-06</v>
+        <v>6.643798311945015e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.213022719382609e-06</v>
+        <v>7.213022719382574e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.27814463466213e-06</v>
+        <v>7.278144634662044e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.005982378390339e-06</v>
+        <v>7.005982378390125e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.27814463466213e-06</v>
+        <v>7.278144634662044e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.27814463466213e-06</v>
+        <v>7.278144634662044e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.27814463466213e-06</v>
+        <v>7.278144634662044e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.429832519501607e-05</v>
+        <v>1.429832519501595e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.399977456230699e-05</v>
+        <v>1.399977456230678e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.124802626406607e-05</v>
+        <v>3.124802626406542e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.380154244048303e-05</v>
+        <v>1.380154244048272e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.403569339300037e-05</v>
+        <v>1.403569339300025e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.423320327973655e-05</v>
+        <v>1.423320327973646e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.120534232563535e-05</v>
+        <v>3.12053423256349e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.073731423782959e-05</v>
+        <v>3.073731423782938e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.106393348250782e-05</v>
+        <v>1.475687943682701e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.431987370730707e-05</v>
+        <v>1.431987370730692e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.431092933768306e-05</v>
+        <v>1.431092933768305e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>5.247847414475673e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.220631188848496e-05</v>
+        <v>5.220631188848464e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.247829459734162e-05</v>
+        <v>5.247829459734159e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.221326914807879e-05</v>
+        <v>5.221326914807871e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.221326914807879e-05</v>
+        <v>5.221326914807871e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.241335222947722e-05</v>
+        <v>5.241335222947709e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.247847414475673e-05</v>
+        <v>5.247847414475669e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.220631188848496e-05</v>
+        <v>5.220631188848464e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.247847414475673e-05</v>
+        <v>5.247847414475669e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.247847414475673e-05</v>
+        <v>5.247847414475669e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.247847414475673e-05</v>
+        <v>5.247847414475669e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000231405119920144</v>
+        <v>0.0002314051199201438</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003746528531887099</v>
+        <v>0.0003746528531887098</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004046424197640253</v>
+        <v>0.0004046424197640245</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003354072938079208</v>
+        <v>0.0003354072938079203</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000235685461491318</v>
+        <v>0.0002356854614913172</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00037482479125086</v>
+        <v>0.0003748247912508595</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000374889913166137</v>
+        <v>0.000374889913166136</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003746177509098674</v>
+        <v>0.000374617750909867</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003749181120649048</v>
+        <v>0.0003749181120649046</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002287398162182956</v>
+        <v>0.0002287398162182953</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005247717777385048</v>
+        <v>0.0005247717777385031</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001277850236746298</v>
+        <v>0.0001277850236746303</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001613084630656726</v>
+        <v>0.0001613084630656725</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001615806266853016</v>
+        <v>0.0001615806266853015</v>
       </c>
       <c r="E7" t="n">
         <v>0.0002003078628505592</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001613084557328381</v>
+        <v>0.0001613084557328377</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001615155034066653</v>
+        <v>0.0001615155034066652</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001615806253219442</v>
+        <v>0.0001615806253219446</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001613084630656726</v>
+        <v>0.0001613084630656725</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001615806253219442</v>
+        <v>0.0001615806253219446</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001419993215753411</v>
+        <v>0.000141999321575341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001615806253219442</v>
+        <v>0.0001615806253219446</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.378134424077032e-05</v>
+        <v>2.37813442407703e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.433543666092163e-05</v>
+        <v>2.433543666092172e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.349709368491921e-05</v>
+        <v>2.349709368491918e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.433543666092163e-05</v>
+        <v>2.433543666092172e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.433543666092163e-05</v>
+        <v>2.433543666092172e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.364335786036913e-05</v>
+        <v>2.364335786036902e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.359011445215179e-05</v>
+        <v>2.359011445215184e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.433543666092163e-05</v>
+        <v>2.433543666092172e-05</v>
       </c>
       <c r="J8" t="n">
         <v>2.316681789934235e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.369831376118078e-05</v>
+        <v>2.369831376118086e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.352734471743653e-05</v>
+        <v>2.352734471743693e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5943,34 +5943,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.420374605840139e-05</v>
+        <v>2.420374605840148e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.476196981605924e-05</v>
+        <v>2.476196981605916e-05</v>
       </c>
       <c r="D9" t="n">
         <v>2.408800617170072e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.476196981605924e-05</v>
+        <v>2.476196981605916e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.476196981605924e-05</v>
+        <v>2.476196981605916e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.412439985491669e-05</v>
+        <v>2.412439985491667e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.412691957454646e-05</v>
+        <v>2.412691957454647e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.476196981605924e-05</v>
+        <v>2.476196981605916e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.395404852532791e-05</v>
+        <v>2.395404852532793e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.416998345432702e-05</v>
+        <v>2.416998345432707e-05</v>
       </c>
       <c r="L9" t="n">
         <v>2.410119735940383e-05</v>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002059799261726917</v>
+        <v>0.000205979926172692</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002147577044985772</v>
+        <v>0.0002147577044985771</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000245941553619526</v>
+        <v>0.0002459415536195259</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002147577044985772</v>
+        <v>0.0002147577044985771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002147577044985772</v>
+        <v>0.0002147577044985771</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002150067804600841</v>
+        <v>0.0002150067804600836</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002484737562262978</v>
+        <v>0.0002484737562262975</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002147577044985772</v>
+        <v>0.0002147577044985771</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002041997700276902</v>
+        <v>0.00020419977002769</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002069988347007245</v>
+        <v>0.0002069988347007239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002320135636463799</v>
+        <v>0.0002226371960876406</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.081121922711892e-06</v>
+        <v>7.081121922711865e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.358650745720087e-06</v>
+        <v>6.358650745720145e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.081121922711892e-06</v>
+        <v>7.081121922711865e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.406716003312551e-06</v>
+        <v>6.406716003312531e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.406716003312552e-06</v>
+        <v>6.406716003312516e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.015925385950752e-06</v>
+        <v>7.015925385950701e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.081121922711892e-06</v>
+        <v>7.081121922711865e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.808369922625124e-06</v>
+        <v>6.808369922625086e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.081121922711892e-06</v>
+        <v>7.081121922711865e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.081121922711892e-06</v>
+        <v>7.081121922711865e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.081121922711892e-06</v>
+        <v>7.081121922711865e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.458827760101101e-05</v>
+        <v>1.458827760101103e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.42955577321603e-05</v>
+        <v>1.429555773216024e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.464459932243066e-05</v>
+        <v>3.258376049238553e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.408346985017977e-05</v>
+        <v>1.408346985017953e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.432727088908627e-05</v>
+        <v>1.432727088908615e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.225199215150364e-05</v>
+        <v>1.452308106424975e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.239350172735838e-05</v>
+        <v>3.239350172735804e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.204443668817812e-05</v>
+        <v>1.431552560092425e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.238419514004916e-05</v>
+        <v>3.238419514004913e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.462092085779146e-05</v>
+        <v>1.462092085779151e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.460387346918933e-05</v>
+        <v>1.46038734691892e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.549103134688988e-05</v>
+        <v>5.549103134688987e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.521827934680313e-05</v>
+        <v>5.521827934680331e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.549085703340256e-05</v>
+        <v>5.549085703340271e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.522069083747747e-05</v>
+        <v>5.522069083747776e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.522069083747747e-05</v>
+        <v>5.522069083747776e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.54258348101287e-05</v>
+        <v>5.54258348101288e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.549103134688988e-05</v>
+        <v>5.549103134688987e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.521827934680313e-05</v>
+        <v>5.521827934680331e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.549103134688988e-05</v>
+        <v>5.549103134688987e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.549103134688988e-05</v>
+        <v>5.549103134688987e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.549103134688988e-05</v>
+        <v>5.549103134688987e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002473043513569886</v>
+        <v>0.0002473043513569889</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004008052549602836</v>
+        <v>0.0004008052549601674</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004329244316843044</v>
+        <v>0.000432924431684305</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003587550054673485</v>
+        <v>0.0003587550054673491</v>
       </c>
       <c r="F6" t="n">
         <v>0.00025190649112023</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004009800574553459</v>
+        <v>0.0004009800574553462</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004010452539921012</v>
+        <v>0.000401045253992102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004007725019920203</v>
+        <v>0.0004007725019920206</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004010754685124516</v>
+        <v>0.0004010754685124519</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002444485351576618</v>
+        <v>0.0002444485351576619</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005616404824252035</v>
+        <v>0.0005616404824252039</v>
       </c>
     </row>
     <row r="7">
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001509415492429225</v>
+        <v>0.000150941549242922</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001909354484193561</v>
+        <v>0.0001909354484193554</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001912082018844752</v>
+        <v>0.0001912082018844751</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000237402301827972</v>
+        <v>0.0002374023018279716</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001909354407533443</v>
+        <v>0.000190935440753344</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001911430038826812</v>
+        <v>0.0001911430038826813</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001912082004194426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001909354484193561</v>
+        <v>0.0001909354484193554</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001912082004194426</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001405052986366879</v>
+        <v>0.0001678775452046082</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001912082004194426</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.348737806551969e-05</v>
+        <v>2.348737806551966e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.426811836871282e-05</v>
+        <v>2.426811836871283e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.330829260215301e-05</v>
+        <v>2.330829260215298e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.426811836871282e-05</v>
+        <v>2.426811836871283e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.426811836871282e-05</v>
+        <v>2.426811836871283e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.360659860230853e-05</v>
+        <v>2.360659860230852e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.366726461418192e-05</v>
+        <v>2.366726461418191e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.426811836871282e-05</v>
+        <v>2.426811836871283e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.332588443982115e-05</v>
+        <v>2.332588443982114e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.365127055339241e-05</v>
+        <v>2.36512705533924e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.35404872178309e-05</v>
+        <v>2.300796750363189e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.399678937386071e-05</v>
+        <v>2.399678937386066e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.463555061936783e-05</v>
+        <v>2.463555061936779e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.392388359209469e-05</v>
+        <v>2.392388359209465e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.463555061936783e-05</v>
+        <v>2.463555061936781e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.463555061936783e-05</v>
+        <v>2.463555061936781e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.402240107958953e-05</v>
+        <v>2.402240107958949e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.407090479302108e-05</v>
+        <v>2.407090479302107e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.463555061936783e-05</v>
+        <v>2.463555061936781e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.393149129090957e-05</v>
+        <v>2.393149129090953e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.406359148117827e-05</v>
+        <v>2.406359148117821e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.380270119693451e-05</v>
+        <v>2.401920055386605e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6458,34 +6458,34 @@
         <v>0.0001987491412224536</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002227191136293563</v>
+        <v>0.000222719113629356</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000255459007536872</v>
+        <v>0.0002554590075368718</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002227191136293563</v>
+        <v>0.000222719113629356</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002227191136293563</v>
+        <v>0.000222719113629356</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002251723243846816</v>
+        <v>0.0002251723243846683</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002889923943542671</v>
+        <v>0.000288992394354267</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002227191136293563</v>
+        <v>0.000222719113629356</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002278130299220602</v>
+        <v>0.0002278130299220598</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002102787211528065</v>
+        <v>0.0002102787211528067</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002551110262605921</v>
+        <v>0.000255111026260592</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.279474135045356e-06</v>
+        <v>7.27947413504536e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.573903097556332e-06</v>
+        <v>6.573903097556275e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.279474135045356e-06</v>
+        <v>7.27947413504536e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.628991184744276e-06</v>
+        <v>6.628991184744255e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.628991184744276e-06</v>
+        <v>6.628991184744317e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.214156936741488e-06</v>
+        <v>7.214156936741499e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.279474135045356e-06</v>
+        <v>7.27947413504536e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.006038458320462e-06</v>
+        <v>7.00603845832039e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.279474135045356e-06</v>
+        <v>7.27947413504536e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.279474135045356e-06</v>
+        <v>7.27947413504536e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.279474135045356e-06</v>
+        <v>7.27947413504536e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.435510543443039e-05</v>
+        <v>3.109797354749366e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.405190883629866e-05</v>
+        <v>1.405190883629864e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.440708235690884e-05</v>
+        <v>1.440711950261254e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.385059418522503e-05</v>
+        <v>1.385059418522496e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.409093083040992e-05</v>
+        <v>1.409093083040987e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42897882361265e-05</v>
+        <v>1.428978823612652e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.12752260454203e-05</v>
+        <v>1.437495322744665e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.408166975770549e-05</v>
+        <v>1.408166975770542e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.481447539709806e-05</v>
+        <v>3.115887624782069e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.438175797693084e-05</v>
+        <v>1.438175797693085e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.437015888756134e-05</v>
+        <v>1.437015888756138e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.250914009457209e-05</v>
+        <v>5.250914009457208e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.223570441784718e-05</v>
+        <v>5.223570441784709e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.250896465970466e-05</v>
+        <v>5.250896465970461e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.223813132282306e-05</v>
+        <v>5.223813132282299e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.223813132282306e-05</v>
+        <v>5.223813132282299e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.24438228962682e-05</v>
+        <v>5.244382289626822e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.250914009457209e-05</v>
+        <v>5.250914009457208e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.223570441784718e-05</v>
+        <v>5.223570441784709e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.250914009457209e-05</v>
+        <v>5.250914009457208e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.250914009457209e-05</v>
+        <v>5.250914009457208e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.250914009457209e-05</v>
+        <v>5.250914009457208e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002314339200373253</v>
+        <v>0.0002314339200373247</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003746945045769138</v>
+        <v>0.0003746945045769136</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004046935100844343</v>
+        <v>0.0004046935100844329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003354443606037295</v>
+        <v>0.0003354443606037292</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002357108683748787</v>
+        <v>0.0002357108683748783</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000374871858074469</v>
+        <v>0.0003748718580744687</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003749371752727709</v>
+        <v>0.00037493717527277</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003746637395960478</v>
+        <v>0.0003746637395960473</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003749653777998357</v>
+        <v>0.000374965377799835</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002287682733945687</v>
+        <v>0.0002287682733945683</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005248383249368355</v>
+        <v>0.0005248383249368344</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001341714599003599</v>
+        <v>0.0001341714599003595</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001694598980339356</v>
+        <v>0.0001694598980339353</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001697333350993642</v>
+        <v>0.0001697333350993635</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002104975381624634</v>
+        <v>0.0002104975381624624</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001694598904576306</v>
+        <v>0.0001694598904576303</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001696680165123567</v>
+        <v>0.0001696680165123565</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001697333337106606</v>
+        <v>0.00016973333371066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001694598980339356</v>
+        <v>0.0001694598980339353</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001697333337106606</v>
+        <v>0.00016973333371066</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001482926866396884</v>
+        <v>0.0001482926866396879</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001697333337106606</v>
+        <v>0.00016973333371066</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.338225492646699e-05</v>
+        <v>2.338225492646696e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.412234434175239e-05</v>
+        <v>2.412234434175236e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.305173380891996e-05</v>
+        <v>2.305173380891995e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.412234434175239e-05</v>
+        <v>2.412234434175236e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.412234434175239e-05</v>
+        <v>2.412234434175236e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.337964143763241e-05</v>
+        <v>2.337964143763239e-05</v>
       </c>
       <c r="H8" t="n">
         <v>2.298617065890878e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.412234434175239e-05</v>
+        <v>2.412234434175236e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.317200899818131e-05</v>
+        <v>2.317200899818129e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.345828848714741e-05</v>
+        <v>2.34582884871474e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.321841241806182e-05</v>
+        <v>2.321841241806183e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.40589228381654e-05</v>
+        <v>2.405892283816537e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.469160803008358e-05</v>
+        <v>2.469160803008355e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.392434987063848e-05</v>
+        <v>2.392434987063846e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.469160803008358e-05</v>
+        <v>2.469160803008355e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.469160803008358e-05</v>
+        <v>2.469160803008355e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.403454928615799e-05</v>
+        <v>2.403454928615804e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.389925100539822e-05</v>
+        <v>2.389925100539818e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.469160803008358e-05</v>
+        <v>2.469160803008355e-05</v>
       </c>
       <c r="J9" t="n">
         <v>2.39738957659514e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.408996031473564e-05</v>
+        <v>2.408996031473566e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.383641934609477e-05</v>
+        <v>2.399335156107539e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002109417920603677</v>
+        <v>0.0002109417920603681</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002232854615972498</v>
+        <v>0.0002232854615972542</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002821104540841527</v>
+        <v>0.0002821104540841534</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002232854615972498</v>
+        <v>0.0002232854615972542</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002232854615972498</v>
+        <v>0.0002232854615972542</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002280311471395296</v>
+        <v>0.0002280311471395385</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002755624199005057</v>
+        <v>0.0002755624199005064</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002232854615972498</v>
+        <v>0.0002232854615972542</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002845800397415789</v>
+        <v>0.0002845800397415793</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002192191650576919</v>
+        <v>0.0002192191650576925</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002466414804392449</v>
+        <v>0.0002416665141605086</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.393584502328989e-06</v>
+        <v>7.393584502329166e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.676497434442079e-06</v>
+        <v>6.676497434442123e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.393584502328989e-06</v>
+        <v>7.393584502329194e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.736537705793476e-06</v>
+        <v>6.736537705793559e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.736537705793474e-06</v>
+        <v>6.736537705793526e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.328138993006364e-06</v>
+        <v>7.328138993006674e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.393584502328989e-06</v>
+        <v>7.393584502329166e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.119380466463704e-06</v>
+        <v>7.119380466463971e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.393584502328989e-06</v>
+        <v>7.393584502329166e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.393584502328989e-06</v>
+        <v>7.393584502329166e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.393584502328989e-06</v>
+        <v>7.393584502329166e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.454998115619975e-05</v>
+        <v>1.454998115619966e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.423956261786164e-05</v>
+        <v>1.423956261786176e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.164689245851773e-05</v>
+        <v>1.467559677310189e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.40330986282841e-05</v>
+        <v>1.403309862828418e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.428357621643284e-05</v>
+        <v>1.42835762164331e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.448453564687698e-05</v>
+        <v>3.132155030039545e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.161441313198255e-05</v>
+        <v>3.161441313198262e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.427577712033435e-05</v>
+        <v>1.427577712033453e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.503205648362078e-05</v>
+        <v>3.145264061592902e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.456049373315234e-05</v>
+        <v>1.456049373315229e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.456357398606306e-05</v>
+        <v>1.456357398606309e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.270305999474872e-05</v>
+        <v>5.270305999474908e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.242885595888369e-05</v>
+        <v>5.242885595888395e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.270288271180758e-05</v>
+        <v>5.27028827118079e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.243049922432689e-05</v>
+        <v>5.24304992243272e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.243049922432689e-05</v>
+        <v>5.24304992243272e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.263761448542653e-05</v>
+        <v>5.263761448542659e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.270305999474872e-05</v>
+        <v>5.270305999474908e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.242885595888369e-05</v>
+        <v>5.242885595888395e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.270305999474872e-05</v>
+        <v>5.270305999474908e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.270305999474872e-05</v>
+        <v>5.270305999474908e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.270305999474872e-05</v>
+        <v>5.270305999474908e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002317233213183929</v>
+        <v>0.000231723321318393</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003751183883302418</v>
+        <v>0.0003751183883304085</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004051470734119367</v>
+        <v>0.0004051470734119373</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003358311312829351</v>
+        <v>0.0003358311312829354</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002360033449011113</v>
+        <v>0.0002360033449011115</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000375297099206767</v>
+        <v>0.0003752970992067672</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003753625447160902</v>
+        <v>0.0003753625447160906</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003750883406802239</v>
+        <v>0.0003750883406802247</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003753907739646344</v>
+        <v>0.0003753907739646347</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000229055148997208</v>
+        <v>0.0002290551489972084</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005254057244949857</v>
+        <v>0.0005254057244949862</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001285084775402477</v>
+        <v>0.0001285084775402479</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001622091658750602</v>
+        <v>0.0001622091658750608</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001624833714509849</v>
+        <v>0.0001624833714509853</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002014154630012757</v>
+        <v>0.0002014154630012762</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001622091581329531</v>
+        <v>0.0001622091581329536</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000162417924401603</v>
+        <v>0.0001624179244016033</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001624833699109255</v>
+        <v>0.0001624833699109262</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001622091658750602</v>
+        <v>0.0001622091658750608</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001624833699109255</v>
+        <v>0.0001624833699109262</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001427981844893963</v>
+        <v>0.0001419995315882524</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001624833699109255</v>
+        <v>0.0001624833699109262</v>
       </c>
     </row>
     <row r="8">
@@ -7094,31 +7094,31 @@
         <v>2.325590875566808e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>2.39883860147279e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.193661481985266e-05</v>
+        <v>2.193661481985267e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>2.39883860147279e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>2.39883860147279e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.317083691564507e-05</v>
+        <v>2.31708369156449e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.268736317151922e-05</v>
+        <v>2.26873631715192e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>2.39883860147279e-05</v>
       </c>
       <c r="J8" t="n">
         <v>2.173180408810712e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.345537167565311e-05</v>
+        <v>2.345537167565314e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.296247051766399e-05</v>
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.407514437967126e-05</v>
+        <v>2.407514437967137e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.471535180074146e-05</v>
+        <v>2.471535180074155e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.353788320553588e-05</v>
+        <v>2.353788320553585e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.471535180074146e-05</v>
+        <v>2.471535180074155e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.471535180074146e-05</v>
+        <v>2.471535180074155e-05</v>
       </c>
       <c r="G9" t="n">
         <v>2.401691646150657e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.384561668727515e-05</v>
+        <v>2.384561668727525e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.471535180074146e-05</v>
+        <v>2.471535180074155e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.345558487993795e-05</v>
+        <v>2.345558487993804e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.415646016169552e-05</v>
+        <v>2.415646016169543e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.395705698194956e-05</v>
+        <v>2.401222727292481e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001941739711695787</v>
+        <v>0.0001941739711695786</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002095333304772813</v>
+        <v>0.0002095333304772815</v>
       </c>
       <c r="D2" t="n">
         <v>0.0002171313206726979</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002095333304772813</v>
+        <v>0.0002095333304772815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002095333304772813</v>
+        <v>0.0002095333304772815</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001984745725370543</v>
+        <v>0.0001984745725370494</v>
       </c>
       <c r="H2" t="n">
         <v>0.0002385427550628069</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002095333304772813</v>
+        <v>0.0002095333304772815</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001970365957671475</v>
+        <v>0.000197036595767148</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001860683099611696</v>
+        <v>0.0001860683099611697</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002107397655905819</v>
+        <v>0.0002107397655905822</v>
       </c>
     </row>
     <row r="3">
@@ -7290,28 +7290,28 @@
         <v>7.03486764017296e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.30645080755688e-06</v>
+        <v>6.306450807557014e-06</v>
       </c>
       <c r="D3" t="n">
         <v>7.03486764017296e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.354210223090722e-06</v>
+        <v>6.354210223090813e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.354210223090721e-06</v>
+        <v>6.35421022309081e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.969707096879518e-06</v>
+        <v>6.969707096879529e-06</v>
       </c>
       <c r="H3" t="n">
         <v>7.03486764017296e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.762342415526481e-06</v>
+        <v>6.762342415526698e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.034867640172963e-06</v>
+        <v>7.03486764017296e-06</v>
       </c>
       <c r="K3" t="n">
         <v>7.03486764017296e-06</v>
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.451204694894538e-05</v>
+        <v>1.45120469489454e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.421790622804383e-05</v>
+        <v>1.421790622804394e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.45623570419454e-05</v>
+        <v>1.456235704194539e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.400809477566759e-05</v>
+        <v>1.40080947756676e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.424930402743211e-05</v>
+        <v>1.424930402743213e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.213478570967873e-05</v>
+        <v>3.213478570967882e-05</v>
       </c>
       <c r="H4" t="n">
         <v>3.228223280406549e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.423952172429888e-05</v>
+        <v>3.192742102832582e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.226999623467907e-05</v>
+        <v>3.226999623467913e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453319126251816e-05</v>
+        <v>1.453319126251817e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.452711215492479e-05</v>
+        <v>1.452711215492481e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.541733842619666e-05</v>
+        <v>5.541733842619663e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.514481320155019e-05</v>
+        <v>5.51448132015504e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.541716642826102e-05</v>
+        <v>5.541716642826105e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.514536342928398e-05</v>
+        <v>5.514536342928421e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.514536342928398e-05</v>
+        <v>5.514536342928421e-05</v>
       </c>
       <c r="G5" t="n">
         <v>5.535217788290324e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.541733842619666e-05</v>
+        <v>5.541733842619663e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.514481320155019e-05</v>
+        <v>5.51448132015504e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.541733842619666e-05</v>
+        <v>5.541733842619663e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.541733842619666e-05</v>
+        <v>5.541733842619663e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.541733842619666e-05</v>
+        <v>5.541733842619663e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000247205745857266</v>
+        <v>0.0002472057458572657</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000400663367006361</v>
+        <v>0.000400663367006475</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004327754576178222</v>
+        <v>0.0004327754576178221</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003586247179200539</v>
+        <v>0.0003586247179200542</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000251805678282895</v>
+        <v>0.0002518056782828952</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004008397698930186</v>
+        <v>0.0004008397698930182</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004009049304363069</v>
+        <v>0.0004009049304363066</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004006324052116654</v>
+        <v>0.0004006324052116655</v>
       </c>
       <c r="J6" t="n">
         <v>0.0004009351367579694</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002443507045922374</v>
+        <v>0.0002443507045922373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005614565808715365</v>
+        <v>0.0005614565808715359</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001507301711160759</v>
+        <v>0.0001507301711160758</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001906749515015644</v>
+        <v>0.0001906749515015646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001909474779827862</v>
+        <v>0.0001909474779827864</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002370848608797496</v>
+        <v>0.0002370848608797499</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001906749437518116</v>
+        <v>0.0001906749437518119</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001908823161829173</v>
+        <v>0.0001908823161829174</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001909474767262108</v>
+        <v>0.000190947476726211</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001906749515015644</v>
+        <v>0.0001906749515015646</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001909474767262108</v>
+        <v>0.000190947476726211</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001667000182046193</v>
+        <v>0.0001676454124386589</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001909474767262108</v>
+        <v>0.000190947476726211</v>
       </c>
     </row>
     <row r="8">
@@ -7487,13 +7487,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.368806920185122e-05</v>
+        <v>2.368806920185123e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.434095800129638e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.34391379158782e-05</v>
+        <v>2.343913791587823e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.434095800129638e-05</v>
@@ -7502,22 +7502,22 @@
         <v>2.434095800129638e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.368040103563584e-05</v>
+        <v>2.368040103563585e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.364645208168206e-05</v>
+        <v>2.364645208168204e-05</v>
       </c>
       <c r="I8" t="n">
         <v>2.434095800129638e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.343458488733118e-05</v>
+        <v>2.343458488733119e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.383990698139243e-05</v>
+        <v>2.383990698139244e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.352407335515732e-05</v>
+        <v>2.355874903751902e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.405235675399701e-05</v>
+        <v>2.405235675399702e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.463904052681522e-05</v>
+        <v>2.463904052681524e-05</v>
       </c>
       <c r="D9" t="n">
         <v>2.39509985457324e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.463904052681522e-05</v>
+        <v>2.463904052681524e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.463904052681522e-05</v>
+        <v>2.463904052681524e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.40262603998387e-05</v>
+        <v>2.402626039983871e-05</v>
       </c>
       <c r="H9" t="n">
         <v>2.403623260309037e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.463904052681522e-05</v>
+        <v>2.463904052681524e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.394953280012771e-05</v>
+        <v>2.394953280012772e-05</v>
       </c>
       <c r="K9" t="n">
         <v>2.411423669300439e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.398631615306496e-05</v>
+        <v>2.400041770034141e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001939647785914969</v>
+        <v>0.0001939647785914966</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000215240157987632</v>
+        <v>0.0002152401579876324</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002176632073446973</v>
+        <v>0.0002176632073446963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000215240157987632</v>
+        <v>0.0002152401579876324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000215240157987632</v>
+        <v>0.0002152401579876324</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002095060531221382</v>
+        <v>0.0002095060531221388</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002545489321098476</v>
+        <v>0.0002545489321098475</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000215240157987632</v>
+        <v>0.0002152401579876324</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001959774106372091</v>
+        <v>0.000195977410637209</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002017719385838802</v>
+        <v>0.00020177193858388</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002131527083021827</v>
+        <v>0.0002302449264612332</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.227929983052684e-06</v>
+        <v>7.227929983052644e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.526183011348223e-06</v>
+        <v>6.526183011348155e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.227929983052684e-06</v>
+        <v>7.227929983052644e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.58007204854731e-06</v>
+        <v>6.580072048547063e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.58007204854731e-06</v>
+        <v>6.580072048547038e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.162770235773656e-06</v>
+        <v>7.162770235773621e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.227929983052675e-06</v>
+        <v>7.227929983052644e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.955496219246602e-06</v>
+        <v>6.955496219246468e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.227929983052684e-06</v>
+        <v>7.227929983052644e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.227929983052684e-06</v>
+        <v>7.227929983052644e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.227929983052684e-06</v>
+        <v>7.227929983052644e-06</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.4268308709999e-05</v>
+        <v>3.096389913786888e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.397153422624131e-05</v>
+        <v>1.397153422624137e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.428176428713795e-05</v>
+        <v>1.428176428713698e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.377272253949304e-05</v>
+        <v>1.377272253949297e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.400587286079984e-05</v>
+        <v>1.400587286079978e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.08987393905899e-05</v>
+        <v>1.420314896271986e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.112994694699657e-05</v>
+        <v>3.112994694699661e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.069146537406282e-05</v>
+        <v>3.069146537406278e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.102218741217022e-05</v>
+        <v>1.472405663455847e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.428830192061584e-05</v>
+        <v>1.428830192061589e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42805423425638e-05</v>
+        <v>1.428054234256378e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.242393790169342e-05</v>
+        <v>5.242393790169343e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.21515041378873e-05</v>
+        <v>5.215150413788745e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.242376280440715e-05</v>
+        <v>5.242376280440708e-05</v>
       </c>
       <c r="E5" t="n">
         <v>5.215390006511613e-05</v>
@@ -7781,19 +7781,19 @@
         <v>5.235877815441442e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.242393790169342e-05</v>
+        <v>5.242393790169343e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.21515041378873e-05</v>
+        <v>5.215150413788745e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.242393790169342e-05</v>
+        <v>5.242393790169343e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.242393790169342e-05</v>
+        <v>5.242393790169343e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.242393790169342e-05</v>
+        <v>5.242393790169343e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7806,34 +7806,34 @@
         <v>0.0002313217140051108</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003745347272243782</v>
+        <v>0.0003745347272245285</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004045227067419663</v>
+        <v>0.0004045227067419653</v>
       </c>
       <c r="E6" t="n">
         <v>0.0003352978611104183</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002355981071354826</v>
+        <v>0.000235598107135482</v>
       </c>
       <c r="G6" t="n">
         <v>0.0003747112759329242</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003747764356801999</v>
+        <v>0.0003747764356801997</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003745040019163974</v>
+        <v>0.0003745040019163966</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003748046286691401</v>
+        <v>0.0003748046286691402</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002286569688981447</v>
+        <v>0.0002286569688981445</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005246268879822689</v>
+        <v>0.0005246268879822684</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001339431641633198</v>
+        <v>0.0001339431641633195</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001691793746685082</v>
+        <v>0.0001691793746685079</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001694518097603187</v>
+        <v>0.0001694518097603185</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002101555891403883</v>
+        <v>0.000210155589140388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001691793672203967</v>
+        <v>0.0001691793672203965</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001693866486850351</v>
+        <v>0.0001693866486850349</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001694518084323142</v>
+        <v>0.000169451808432314</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001691793746685082</v>
+        <v>0.0001691793746685079</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001694518084323142</v>
+        <v>0.000169451808432314</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001488779610482022</v>
+        <v>0.0001247400866828778</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001694518084323142</v>
+        <v>0.000169451808432314</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.344981893216419e-05</v>
+        <v>2.34498189321642e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.417113083568109e-05</v>
+        <v>2.417113083568106e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.363621254469109e-05</v>
+        <v>2.363621254469104e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.417113083568109e-05</v>
+        <v>2.417113083568106e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.417113083568109e-05</v>
+        <v>2.417113083568106e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.349714120556536e-05</v>
+        <v>2.349714120556535e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.32337878318923e-05</v>
+        <v>2.323378783189226e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.417113083568109e-05</v>
+        <v>2.417113083568106e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.333404521686582e-05</v>
+        <v>2.33340452168658e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.361622265049846e-05</v>
+        <v>2.361622265049845e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.300324232428763e-05</v>
+        <v>2.349711598565969e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.405912063773686e-05</v>
+        <v>2.405912063773681e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.46861902072389e-05</v>
+        <v>2.468619020723889e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.413506699912067e-05</v>
+        <v>2.413506699912061e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.46861902072389e-05</v>
+        <v>2.468619020723889e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.46861902072389e-05</v>
+        <v>2.468619020723889e-05</v>
       </c>
       <c r="G9" t="n">
         <v>2.405537752201428e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.39725090624118e-05</v>
+        <v>2.397250906241177e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.46861902072389e-05</v>
+        <v>2.468619020723889e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.401249175867169e-05</v>
+        <v>2.401249175867167e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.412695446464391e-05</v>
+        <v>2.412695446464389e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.387850860574593e-05</v>
+        <v>2.407929847355598e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen resource use mineral and metals results.xlsx
+++ b/Results/Hydrogen/hydrogen resource use mineral and metals results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001935735589870597</v>
+        <v>0.0001935735589870775</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002040040674436352</v>
+        <v>0.0002040040674436358</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002000800157511673</v>
+        <v>0.0002000800157511695</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002040040674436352</v>
+        <v>0.0002040040674436358</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002040040674436352</v>
+        <v>0.0002040040674436358</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001933283329190958</v>
+        <v>0.0001933283329190875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002123147444838203</v>
+        <v>0.0002123147444838256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002040040674436352</v>
+        <v>0.0002040040674436358</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002051859758543249</v>
+        <v>0.0002051859758543324</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001880522325361677</v>
+        <v>0.0001880522325361664</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001830942685195616</v>
+        <v>0.00021891121983768</v>
       </c>
     </row>
     <row r="3">
@@ -558,25 +558,25 @@
         <v>7.009195243562171e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.237164548629607e-06</v>
+        <v>6.237164548629586e-06</v>
       </c>
       <c r="D3" t="n">
         <v>7.009195243562171e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.290240984330954e-06</v>
+        <v>6.290240984330907e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.290240984330901e-06</v>
+        <v>6.290240984330907e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.944075853536611e-06</v>
+        <v>6.944075853536668e-06</v>
       </c>
       <c r="H3" t="n">
         <v>7.009195243562171e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.736972321668502e-06</v>
+        <v>6.736972321668516e-06</v>
       </c>
       <c r="J3" t="n">
         <v>7.009195243562171e-06</v>
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.497604381613681e-05</v>
+        <v>1.49760438161368e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.468345985084661e-05</v>
+        <v>1.468345985084654e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.501760574022107e-05</v>
+        <v>1.501756062443498e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.446150067815858e-05</v>
+        <v>1.44615006781585e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.471482014425002e-05</v>
+        <v>1.471482014424998e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.374217107488779e-05</v>
+        <v>3.374217107488768e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.389714753427673e-05</v>
+        <v>3.389714753427678e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.470382089424315e-05</v>
+        <v>3.353506754301951e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.549016207442176e-05</v>
+        <v>3.389183659218017e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.500520413419421e-05</v>
+        <v>1.500520413419415e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.499162606565577e-05</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.871822997695725e-05</v>
+        <v>5.871822997695717e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.844600705506368e-05</v>
+        <v>5.844600705506353e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.871807095055649e-05</v>
+        <v>5.871807095055637e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.844522827023941e-05</v>
+        <v>5.844522827023928e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.844522827023941e-05</v>
+        <v>5.844522827023928e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.865311058693171e-05</v>
+        <v>5.865311058693173e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.871822997695725e-05</v>
+        <v>5.871822997695717e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.844600705506368e-05</v>
+        <v>5.844600705506353e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.871822997695725e-05</v>
+        <v>5.871822997695717e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.871822997695725e-05</v>
+        <v>5.871822997695717e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.871822997695725e-05</v>
+        <v>5.871822997695717e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002636158199084478</v>
+        <v>0.0002636158199084475</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004275866290765122</v>
+        <v>0.0004275866290766056</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004618773946628727</v>
+        <v>0.0004618773946628716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003826729381143049</v>
+        <v>0.0003826729381143045</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000268548471692977</v>
+        <v>0.0002685484716929765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000427761993859406</v>
+        <v>0.0004277619938594055</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004278271132494315</v>
+        <v>0.0004278271132494311</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004275548903275382</v>
+        <v>0.0004275548903275373</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004278593855037424</v>
+        <v>0.0004278593855037418</v>
       </c>
       <c r="K6" t="n">
         <v>0.0002605655108261053</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000599359540296598</v>
+        <v>0.0005993595402965971</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001719121541572034</v>
+        <v>0.0001719121541572035</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000217752365206595</v>
+        <v>0.0002177523652065944</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002180245894140145</v>
+        <v>0.0002180245894140144</v>
       </c>
       <c r="E7" t="n">
         <v>0.0002709651271567176</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002177523569879734</v>
+        <v>0.0002177523569879736</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000217959468738463</v>
+        <v>0.0002179594687384625</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002180245881284885</v>
+        <v>0.0002180245881284881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000217752365206595</v>
+        <v>0.0002177523652065944</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002180245881284885</v>
+        <v>0.0002180245881284881</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001913068633287065</v>
+        <v>0.0001599608023851115</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002180245881284885</v>
+        <v>0.0002180245881284881</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.385573862651478e-05</v>
+        <v>2.385573862651371e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.432162270134178e-05</v>
+        <v>2.432162270134165e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.354132960877268e-05</v>
+        <v>2.354132960877245e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.432162270134178e-05</v>
+        <v>2.432162270134165e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.432162270134178e-05</v>
+        <v>2.432162270134165e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.370689737389612e-05</v>
+        <v>2.370689737389595e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.364781919033465e-05</v>
+        <v>2.364781919033467e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.432162270134178e-05</v>
+        <v>2.432162270134165e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.350067514567043e-05</v>
+        <v>2.350067514567034e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.380481646432656e-05</v>
+        <v>2.380481646432694e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.403174743013526e-05</v>
+        <v>2.40317474301352e-05</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.410301955484857e-05</v>
+        <v>2.410301955484884e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.461411604961561e-05</v>
+        <v>2.461411604961558e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.39749891662585e-05</v>
+        <v>2.397498916625843e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.461411604961561e-05</v>
+        <v>2.461411604961558e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.461411604961561e-05</v>
+        <v>2.461411604961558e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.401957877997261e-05</v>
+        <v>2.401957877997247e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.40191320343004e-05</v>
+        <v>2.401913203430039e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.461411604961561e-05</v>
+        <v>2.461411604961558e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.395878627148911e-05</v>
+        <v>2.395878627148902e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.408231691073683e-05</v>
+        <v>2.408231691073672e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.41750591233439e-05</v>
+        <v>2.400828182235043e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002026894475674547</v>
+        <v>0.0002026894475674553</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000224209484441457</v>
+        <v>0.0002242094844414574</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002509936864833091</v>
+        <v>0.0002509936864833095</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000224209484441457</v>
+        <v>0.0002242094844414574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000224209484441457</v>
+        <v>0.0002242094844414574</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002169713003079466</v>
+        <v>0.0002169713003079398</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002608802603758049</v>
+        <v>0.0002608802603758058</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000224209484441457</v>
+        <v>0.0002242094844414574</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002420478535739981</v>
+        <v>0.0002420478535739984</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002127730768727177</v>
+        <v>0.000212773076872718</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002478418725875164</v>
+        <v>0.0002478418725875169</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.373115638524916e-06</v>
+        <v>7.373115638525164e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.674192023508942e-06</v>
+        <v>6.67419202350897e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.373115638524916e-06</v>
+        <v>7.373115638525164e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.732292372054028e-06</v>
+        <v>6.732292372054242e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.732292372054033e-06</v>
+        <v>6.732292372054168e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.308014120495858e-06</v>
+        <v>7.308014120496081e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.373115638524916e-06</v>
+        <v>7.373115638525164e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.101096945604866e-06</v>
+        <v>7.101096945605109e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.373115638524916e-06</v>
+        <v>7.373115638525164e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.373115638524916e-06</v>
+        <v>7.373115638525164e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.373115638524916e-06</v>
+        <v>7.373115638525164e-06</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.128834242931006e-05</v>
+        <v>1.448684823134626e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.419750503446338e-05</v>
+        <v>1.419750503446345e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.153875109644862e-05</v>
+        <v>3.153875109644866e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.399370246527434e-05</v>
+        <v>1.399370246527444e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.422951514774204e-05</v>
+        <v>1.422951514774211e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.442174671331719e-05</v>
+        <v>3.122324091128107e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.150185212541411e-05</v>
+        <v>3.150185212541438e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.421482953842615e-05</v>
+        <v>1.421482953842628e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.135013345722578e-05</v>
+        <v>1.496112608407591e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.449830216340387e-05</v>
+        <v>1.449830216340397e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.450863744538355e-05</v>
+        <v>1.450863744538362e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.264659396672982e-05</v>
+        <v>5.264659396673e-05</v>
       </c>
       <c r="C5" t="n">
         <v>5.237457527380983e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.264641483547723e-05</v>
+        <v>5.264641483547737e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.237887593478664e-05</v>
+        <v>5.237887593478675e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.237887593478664e-05</v>
+        <v>5.237887593478676e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.258149244870087e-05</v>
+        <v>5.258149244870092e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.264659396672982e-05</v>
+        <v>5.264659396673e-05</v>
       </c>
       <c r="I5" t="n">
         <v>5.237457527380983e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.264659396672982e-05</v>
+        <v>5.264659396673e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.264659396672982e-05</v>
+        <v>5.264659396673e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.264659396672982e-05</v>
+        <v>5.264659396673e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002316358188573536</v>
+        <v>0.0002316358188573543</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003749825714244227</v>
+        <v>0.0003749825714245897</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004049955411668773</v>
+        <v>0.0004049955411668788</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003357095489115571</v>
+        <v>0.0003357095489115581</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002359179330855697</v>
+        <v>0.0002359179330855706</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003751569076989212</v>
+        <v>0.0003751569076989227</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003752220092169493</v>
+        <v>0.0003752220092169499</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003749499905240302</v>
+        <v>0.0003749499905240316</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003752502280430826</v>
+        <v>0.0003752502280430828</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002289686316520694</v>
+        <v>0.0002289686316520698</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005252097915530941</v>
+        <v>0.0005252097915530959</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001283129392820626</v>
+        <v>0.0001283129392820628</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001619628525312568</v>
+        <v>0.0001619628525312573</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001622348725261557</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002011080342756389</v>
+        <v>0.0002011080342756397</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001619628448251548</v>
+        <v>0.0001619628448251544</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001621697697061477</v>
+        <v>0.000162169769706148</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001622348712241769</v>
+        <v>0.0001622348712241773</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001619628525312568</v>
+        <v>0.0001619628525312573</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001622348712241769</v>
+        <v>0.0001622348712241773</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001425803711828134</v>
+        <v>0.000142580371182814</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001622348712241769</v>
+        <v>0.0001622348712241773</v>
       </c>
     </row>
     <row r="8">
@@ -1154,34 +1154,34 @@
         <v>2.347016982471871e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.396737767583452e-05</v>
+        <v>2.396737767583463e-05</v>
       </c>
       <c r="D8" t="n">
         <v>2.268968697791862e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.396737767583452e-05</v>
+        <v>2.396737767583463e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.396737767583452e-05</v>
+        <v>2.396737767583463e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.332815850080948e-05</v>
+        <v>2.332815850080943e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.279181874624596e-05</v>
+        <v>2.279181874624589e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.396737767583452e-05</v>
+        <v>2.396737767583463e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.24385417235747e-05</v>
+        <v>2.243854172357465e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.358843971508075e-05</v>
+        <v>2.35884397150807e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.285449295959983e-05</v>
+        <v>2.285449295959973e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.413388657555966e-05</v>
+        <v>2.413388657555963e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.468514655100236e-05</v>
+        <v>2.468514655100243e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.381605844790877e-05</v>
+        <v>2.381605844790871e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.468514655100236e-05</v>
+        <v>2.468514655100243e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.468514655100236e-05</v>
+        <v>2.468514655100243e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.405328875620381e-05</v>
+        <v>2.40532887562038e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.385949285475735e-05</v>
+        <v>2.385949285475729e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.468514655100236e-05</v>
+        <v>2.468514655100243e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.371462127959986e-05</v>
+        <v>2.371462127959985e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.418212331498682e-05</v>
+        <v>2.418212331498676e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.39296578412246e-05</v>
+        <v>2.388461267592059e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.487374384631378e-05</v>
+        <v>5.48737438463138e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001837381753976421</v>
+        <v>0.0001837381753976418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002103634245795215</v>
+        <v>0.000210363424579523</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001996662267368513</v>
+        <v>0.0001996662267368503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001996662267368513</v>
+        <v>0.0001996662267368503</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001950318933652942</v>
+        <v>0.0001950318933652924</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002488412807092181</v>
+        <v>0.0002488412807092175</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001996662267368513</v>
+        <v>0.0001996662267368503</v>
       </c>
       <c r="J2" t="n">
         <v>0.0001804002696949416</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001857923905799877</v>
+        <v>0.0001857923905799875</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000205948357103289</v>
+        <v>0.0002059483571032892</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.772792968808202e-06</v>
+        <v>7.772792968808402e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.717567924689478e-06</v>
+        <v>6.717567924689485e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.772792968808204e-06</v>
+        <v>7.772792968808358e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.012422048455135e-06</v>
+        <v>7.012422048455733e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.012422048455147e-06</v>
+        <v>7.012422048455729e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.706586888088948e-06</v>
+        <v>7.706586888089337e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.772792968808204e-06</v>
+        <v>7.772792968808405e-06</v>
       </c>
       <c r="I3" t="n">
         <v>7.494319255459681e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.772792968808204e-06</v>
+        <v>7.772792968808405e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.772792968808204e-06</v>
+        <v>7.772792968808358e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.772792968808204e-06</v>
+        <v>7.772792968808358e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.498613777198976e-05</v>
+        <v>3.297101029389283e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.460911138497509e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.50305499898147e-05</v>
+        <v>1.503052610080571e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.447375519395881e-05</v>
+        <v>1.447375519395879e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.472259446570155e-05</v>
+        <v>1.472259446570144e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.29048042131735e-05</v>
+        <v>1.49199316912705e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.417369431215746e-05</v>
+        <v>3.417369431215769e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.269253658054426e-05</v>
+        <v>1.470766405864128e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.327869733207848e-05</v>
+        <v>3.327869733207858e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.499690876896671e-05</v>
+        <v>1.499690876896669e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.499980339580083e-05</v>
@@ -1430,25 +1430,25 @@
         <v>5.612545906410925e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.583905353821118e-05</v>
+        <v>5.583905353821129e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.612543033442471e-05</v>
+        <v>5.612543033442469e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.584721932500763e-05</v>
+        <v>5.584721932500754e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.584721932500763e-05</v>
+        <v>5.584721932500754e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.605925298338998e-05</v>
+        <v>5.605925298338999e-05</v>
       </c>
       <c r="H5" t="n">
         <v>5.612545906410925e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.584698535076067e-05</v>
+        <v>5.584698535076077e-05</v>
       </c>
       <c r="J5" t="n">
         <v>5.612545906410925e-05</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457835089929885</v>
+        <v>0.0002457835089929894</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003981316985769989</v>
+        <v>0.000398131698576999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004300313017741971</v>
+        <v>0.0004300313017741981</v>
       </c>
       <c r="E6" t="n">
         <v>0.000356400501888275</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002503425125749641</v>
+        <v>0.0002503425125749645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000398321600468503</v>
+        <v>0.0003983216004685032</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003983878065492782</v>
+        <v>0.0003983878065492793</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003981093328358732</v>
+        <v>0.0003981093328358739</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003984177976934831</v>
+        <v>0.0003984177976934845</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002429488058164022</v>
+        <v>0.0002429488058164025</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005577957559360675</v>
+        <v>0.0005577957559360687</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001504740734113479</v>
+        <v>0.0001504740734113478</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001902509210503248</v>
+        <v>0.0001902509210503251</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001905373285113467</v>
+        <v>0.0001905373285113472</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002364909897675137</v>
+        <v>0.0002364909897675136</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001902588452478825</v>
+        <v>0.0001902588452478824</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001904711204955037</v>
+        <v>0.0001904711204955041</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001905373265762229</v>
+        <v>0.0001905373265762233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001902588528628745</v>
+        <v>0.0001902588528628744</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001905373265762229</v>
+        <v>0.0001905373265762233</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001673245211658601</v>
+        <v>0.0001673245211658602</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001905373265762229</v>
+        <v>0.0001905373265762234</v>
       </c>
     </row>
     <row r="8">
@@ -1547,34 +1547,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.247154246741567e-05</v>
+        <v>2.247154246741569e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.328514793911324e-05</v>
+        <v>2.328514793911327e-05</v>
       </c>
       <c r="D8" t="n">
         <v>2.313359994991288e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.399793153413446e-05</v>
+        <v>2.399793153413447e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.399793153413446e-05</v>
+        <v>2.399793153413447e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.425962834643511e-05</v>
+        <v>2.425962834643521e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.272535501200992e-05</v>
+        <v>2.272535501200993e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.399793153413446e-05</v>
+        <v>2.399793153413447e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.509917192149554e-05</v>
+        <v>2.50991719214955e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.485067655947613e-05</v>
+        <v>2.485067655947616e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.421399040944306e-05</v>
@@ -1587,16 +1587,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.283322846787493e-05</v>
+        <v>2.283322846787495e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.370824170256375e-05</v>
+        <v>2.37082417025638e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.396033189640638e-05</v>
+        <v>2.396033189640641e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.465248614438861e-05</v>
+        <v>2.46524861443886e-05</v>
       </c>
       <c r="F9" t="n">
         <v>2.46524861443886e-05</v>
@@ -1605,19 +1605,19 @@
         <v>2.484400454485887e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.379591219041644e-05</v>
+        <v>2.379591219041641e-05</v>
       </c>
       <c r="I9" t="n">
         <v>2.46524861443886e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.542337093625876e-05</v>
+        <v>2.542337093625878e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.53165107642487e-05</v>
+        <v>2.531651076424873e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.471835643339086e-05</v>
+        <v>2.47183564333909e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.441859923284876e-05</v>
+        <v>6.441859923284899e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001914971352138083</v>
+        <v>0.0001914971352138085</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002144240329414868</v>
+        <v>0.0002144240329414866</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000206348066959308</v>
+        <v>0.0002063480669593083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000206348066959308</v>
+        <v>0.0002063480669593083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002002365037494075</v>
+        <v>0.0002002365037494212</v>
       </c>
       <c r="H2" t="n">
         <v>0.0002553818069768233</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000206348066959308</v>
+        <v>0.0002063480669593083</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001739040493052595</v>
+        <v>0.0001739040493052596</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001887912903729794</v>
+        <v>0.0001887912903729795</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002107352647795442</v>
+        <v>0.0002107352647795446</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.989837725523818e-06</v>
+        <v>7.989837725524054e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.916706306901309e-06</v>
+        <v>6.91670630690138e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.989837725523818e-06</v>
+        <v>7.989837725524049e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.263185167352093e-06</v>
+        <v>7.263185167352276e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.263185167352161e-06</v>
+        <v>7.263185167352275e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.923530598182897e-06</v>
+        <v>7.923530598183078e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.989837725523818e-06</v>
+        <v>7.989837725524049e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.710885607556675e-06</v>
+        <v>7.710885607556821e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.989837725523818e-06</v>
+        <v>7.989837725524054e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.989837725523818e-06</v>
+        <v>7.989837725524049e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.989837725523818e-06</v>
+        <v>7.989837725524049e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.217663676942644e-05</v>
+        <v>3.217663676942667e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.45571840551879e-05</v>
+        <v>1.455718405518796e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.273208706570811e-05</v>
+        <v>3.273208706570838e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.443406995913399e-05</v>
+        <v>1.443406995913407e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.468164059692736e-05</v>
+        <v>1.468164059692747e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.487707306673396e-05</v>
+        <v>3.211032964208547e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.380508330664217e-05</v>
+        <v>3.380508330664245e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.466442807610769e-05</v>
+        <v>1.466442807610779e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.540836900313111e-05</v>
+        <v>1.540836900313124e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.494534434225287e-05</v>
+        <v>1.494534434225299e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.495591713966414e-05</v>
+        <v>1.49559171396643e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.385103823788062e-05</v>
+        <v>5.385103823788092e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.35640805319763e-05</v>
+        <v>5.35640805319764e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.385102508882479e-05</v>
+        <v>5.385102508882498e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.357805061668015e-05</v>
+        <v>5.357805061668038e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.357805061668015e-05</v>
+        <v>5.357805061668038e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.378473111053967e-05</v>
+        <v>5.378473111053971e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.385103823788062e-05</v>
+        <v>5.385103823788092e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.357208611991338e-05</v>
+        <v>5.35720861199135e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.385103823788062e-05</v>
+        <v>5.385103823788092e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.385103823788062e-05</v>
+        <v>5.385103823788092e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.385103823788062e-05</v>
+        <v>5.385103823788092e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,25 +1863,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002337983606782207</v>
+        <v>0.0002337983606782209</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003783661378744207</v>
+        <v>0.0003783661378741208</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004086483394083594</v>
+        <v>0.0004086483394083597</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003387633946298116</v>
+        <v>0.0003387633946298119</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002381135608550356</v>
+        <v>0.0002381135608550358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003785525573901408</v>
+        <v>0.0003785525573901409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003786188645176478</v>
+        <v>0.0003786188645176482</v>
       </c>
       <c r="I6" t="n">
         <v>0.0003783399123995144</v>
@@ -1890,10 +1890,10 @@
         <v>0.0003786473259211811</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002311082454662111</v>
+        <v>0.0002311082454662116</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005298959904951555</v>
+        <v>0.0005298959904951557</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001358654933365094</v>
+        <v>0.0001358654933365099</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001715283412897268</v>
+        <v>0.0001715283412897267</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000171815301160275</v>
+        <v>0.0001718153011602753</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002130216532042642</v>
+        <v>0.0002130216532042647</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001715363395962254</v>
+        <v>0.000171536339596226</v>
       </c>
       <c r="G7" t="n">
         <v>0.0001717489918682899</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001718152989956308</v>
+        <v>0.0001718152989956317</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001715363468776639</v>
+        <v>0.000171536346877664</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001718152989956308</v>
+        <v>0.0001718152989956317</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001509858413213925</v>
+        <v>0.0001509858413213927</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001718152989956308</v>
+        <v>0.0001718152989956317</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.228276766715809e-05</v>
+        <v>2.228276766715812e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.297969864705029e-05</v>
+        <v>2.297969864705031e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.298817098237004e-05</v>
+        <v>2.298817098237012e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.376664638398829e-05</v>
+        <v>2.376664638398833e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.376664638398829e-05</v>
+        <v>2.376664638398833e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.39624676659849e-05</v>
+        <v>2.396246766598478e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.252485794675109e-05</v>
+        <v>2.252485794675115e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.376664638398829e-05</v>
+        <v>2.376664638398833e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.526185407683759e-05</v>
+        <v>2.526185407683776e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.462794024727053e-05</v>
+        <v>2.462794024727068e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.400886845866932e-05</v>
+        <v>2.400886845866942e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.280976987009752e-05</v>
+        <v>2.280976987009756e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.363948088727784e-05</v>
+        <v>2.363948088727788e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.402298141247171e-05</v>
+        <v>2.402298141247176e-05</v>
       </c>
       <c r="E9" t="n">
         <v>2.465741721863756e-05</v>
@@ -1998,22 +1998,22 @@
         <v>2.465741721863756e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.475595241867486e-05</v>
+        <v>2.475595241867487e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.383650637053422e-05</v>
+        <v>2.383650637053431e-05</v>
       </c>
       <c r="I9" t="n">
         <v>2.465741721863756e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.56166572907106e-05</v>
+        <v>2.561665729071067e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.526912387183542e-05</v>
+        <v>2.526912387183572e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.470065305263963e-05</v>
+        <v>2.470065305263971e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2102,34 +2102,34 @@
         <v>7.070180831158737e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002019928830689156</v>
+        <v>0.0002019928830689154</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002230597720151999</v>
+        <v>0.0002230597720151986</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002132652479684897</v>
+        <v>0.0002132652479684896</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002132652479684897</v>
+        <v>0.0002132652479684896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002093530857426922</v>
+        <v>0.0002093530857426979</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002618203328689703</v>
+        <v>0.0002618203328689711</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002132652479684897</v>
+        <v>0.0002132652479684896</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001797530578559325</v>
+        <v>0.0001797530578559327</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001953606309691964</v>
+        <v>0.000195360630969196</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000226433849218894</v>
+        <v>0.0002264338492188939</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.462572046443285e-06</v>
+        <v>8.462572046443045e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.318217761990423e-06</v>
+        <v>7.318217761990365e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.462572046443285e-06</v>
+        <v>8.462572046443072e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.736305826807106e-06</v>
+        <v>7.736305826806987e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.736305826807108e-06</v>
+        <v>7.736305826807016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.396031998872836e-06</v>
+        <v>8.396031998872799e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.462572046443285e-06</v>
+        <v>8.462572046443072e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.182320976082519e-06</v>
+        <v>8.182320976082529e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.462572046443285e-06</v>
+        <v>8.462572046443072e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.462572046443285e-06</v>
+        <v>8.462572046443072e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.462572046443285e-06</v>
+        <v>8.462572046443072e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.545931168409722e-05</v>
+        <v>1.545931168409707e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.505655270402011e-05</v>
+        <v>1.505655270402008e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.549387292255058e-05</v>
+        <v>1.549389131096212e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.493129140382042e-05</v>
+        <v>1.493129140382014e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.519702450936246e-05</v>
+        <v>1.519702450936226e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.290339767369005e-05</v>
+        <v>3.290339767368999e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.507755790383042e-05</v>
+        <v>3.507755790383012e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.268968665089974e-05</v>
+        <v>3.26896866508996e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.340316363659437e-05</v>
+        <v>3.340316363659413e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.545376441671985e-05</v>
+        <v>1.545376441671923e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.547331314667231e-05</v>
+        <v>1.547331314667217e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.456736747643028e-05</v>
+        <v>5.456736747643024e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.427978421170291e-05</v>
+        <v>5.427978421170289e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.456735859554198e-05</v>
+        <v>5.456735859554189e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.42975687558759e-05</v>
+        <v>5.429756875587578e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.42975687558759e-05</v>
+        <v>5.429756875587578e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.450082742885991e-05</v>
+        <v>5.450082742885987e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.456736747643028e-05</v>
+        <v>5.456736747643024e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.428711640606963e-05</v>
+        <v>5.428711640606956e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.456736747643028e-05</v>
+        <v>5.456736747643024e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.456736747643028e-05</v>
+        <v>5.456736747643024e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.456736747643028e-05</v>
+        <v>5.456736747643024e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002349019307757335</v>
+        <v>0.0002349019307757334</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003799725106798093</v>
+        <v>0.0003799725106802214</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004103544203820695</v>
+        <v>0.0004103544203820692</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003402321380684161</v>
+        <v>0.0003402321380684156</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002392343252554366</v>
+        <v>0.0002392343252554359</v>
       </c>
       <c r="G6" t="n">
         <v>0.0003801549276774692</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003802214677252961</v>
+        <v>0.0003802214677252964</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003799412166546789</v>
+        <v>0.0003799412166546787</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003802500272022767</v>
+        <v>0.0003802500272022768</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002322025457674285</v>
+        <v>0.000232202545767428</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005320198755143491</v>
+        <v>0.0005320198755143483</v>
       </c>
     </row>
     <row r="7">
@@ -2299,34 +2299,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001305205635803969</v>
+        <v>0.0001305205635803972</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000164616626149889</v>
+        <v>0.0001646166261498888</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001649042119687618</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002043019498310497</v>
+        <v>0.0002043019498310498</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001646239510932788</v>
+        <v>0.0001646239510932787</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000164837669367046</v>
+        <v>0.0001648376693670456</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001649042094146162</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001646239583442554</v>
+        <v>0.0001646239583442553</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001649042094146162</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001216090611882833</v>
+        <v>0.0001441739295038859</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001649042094146162</v>
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.225131904037646e-05</v>
+        <v>2.225131904037644e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.285731098958352e-05</v>
+        <v>2.285731098958348e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.304361864344337e-05</v>
+        <v>2.304361864344332e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.379901718291023e-05</v>
+        <v>2.379901718291017e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.379901718291023e-05</v>
+        <v>2.379901718291017e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.382309349740377e-05</v>
+        <v>2.382309349740362e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.265147194069727e-05</v>
+        <v>2.265147194069716e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.379901718291023e-05</v>
+        <v>2.379901718291017e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.548671077331439e-05</v>
+        <v>2.548671077331427e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.443109674420187e-05</v>
+        <v>2.443109674420178e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.387863418888508e-05</v>
+        <v>2.387863418888504e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.286061262381635e-05</v>
+        <v>2.286061262381633e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.365874962303301e-05</v>
+        <v>2.365874962303297e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.41948845640621e-05</v>
+        <v>2.419488456406203e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.478144618268815e-05</v>
+        <v>2.478144618268809e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.478144618268815e-05</v>
+        <v>2.478144618268809e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.473926188024883e-05</v>
+        <v>2.473926188024875e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.403751173090862e-05</v>
+        <v>2.403751173090854e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.478144618268815e-05</v>
+        <v>2.478144618268809e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.591220380027333e-05</v>
+        <v>2.591220380027324e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.516322581107698e-05</v>
+        <v>2.516322581107697e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.476017178722573e-05</v>
+        <v>2.476017178722567e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.904731031296648e-05</v>
+        <v>6.904731031296657e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001973139772697763</v>
+        <v>0.0001973139772697765</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002353398729773577</v>
+        <v>0.0002353398729773579</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002140535341067191</v>
+        <v>0.0002140535341067183</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002140535341067191</v>
+        <v>0.0002140535341067183</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002110948963313763</v>
+        <v>0.0002110948963313922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002597830945985628</v>
+        <v>0.000259783094598562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002140535341067191</v>
+        <v>0.0002140535341067183</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002001576616681813</v>
+        <v>0.0002001576616681829</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001939069554095048</v>
+        <v>0.0001939069554095046</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002229212460156785</v>
+        <v>0.0002229212460156788</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.777053384210193e-06</v>
+        <v>7.777053384210213e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.7276916568016e-06</v>
+        <v>6.727691656801604e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.777053384210193e-06</v>
+        <v>7.777053384210213e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.048573225549333e-06</v>
+        <v>7.048573225549359e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.048573225549337e-06</v>
+        <v>7.048573225549358e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.710666395539195e-06</v>
+        <v>7.710666395539202e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.777053384210193e-06</v>
+        <v>7.777053384210213e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.497359736888524e-06</v>
+        <v>7.497359736888507e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.777053384210193e-06</v>
+        <v>7.777053384210213e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.777053384210193e-06</v>
+        <v>7.777053384210213e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.777053384210193e-06</v>
+        <v>7.777053384210213e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.509762386104534e-05</v>
+        <v>1.509762386104538e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.47184672923823e-05</v>
+        <v>1.471846729238233e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.516195005831339e-05</v>
+        <v>1.516197446623038e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458637758947246e-05</v>
+        <v>1.458637758947248e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.483480461677747e-05</v>
+        <v>1.48348046167775e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.50312368723743e-05</v>
+        <v>1.503123687237441e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.429843035957228e-05</v>
+        <v>3.429843035957232e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.481793021372367e-05</v>
+        <v>3.282598110545379e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.341517025565642e-05</v>
+        <v>1.558464458946873e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.509310060115627e-05</v>
+        <v>1.509310060115633e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.511161695920529e-05</v>
+        <v>1.511161695920536e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.604578562860038e-05</v>
+        <v>5.604578562860035e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.575924644451252e-05</v>
+        <v>5.575924644451267e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.604575559153605e-05</v>
+        <v>5.604575559153614e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.577552232021442e-05</v>
+        <v>5.577552232021443e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.577552232021442e-05</v>
+        <v>5.577552232021443e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.597939863992931e-05</v>
+        <v>5.597939863992944e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.604578562860038e-05</v>
+        <v>5.604578562860035e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.576609198127869e-05</v>
+        <v>5.576609198127868e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.604578562860038e-05</v>
+        <v>5.604578562860035e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.604578562860038e-05</v>
+        <v>5.604578562860035e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.604578562860038e-05</v>
+        <v>5.604578562860035e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000245729589478685</v>
+        <v>0.0002457295894786855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003980159365107918</v>
+        <v>0.0003980159365110328</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004298922814344911</v>
+        <v>0.0004298922814344916</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003563020038142282</v>
+        <v>0.0003563020038142292</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002502906257109214</v>
+        <v>0.0002502906257109219</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003981970147965393</v>
+        <v>0.00039819701479654</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003982634017852639</v>
+        <v>0.0003982634017852653</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003979837081378881</v>
+        <v>0.000397983708137889</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000398293379077143</v>
+        <v>0.0003982933790771438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000242896195601797</v>
+        <v>0.0002428961956017978</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005575977234348904</v>
+        <v>0.0005575977234348921</v>
       </c>
     </row>
     <row r="7">
@@ -2695,34 +2695,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001508580476521698</v>
+        <v>0.0001508580476521695</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001907251841499393</v>
+        <v>0.000190725184149939</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001910117255375444</v>
+        <v>0.0001910117255375441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002370685124299286</v>
+        <v>0.0002370685124299281</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001907320220146186</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000190945336345356</v>
+        <v>0.0001909453363453562</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001910117233340269</v>
+        <v>0.0001910117233340271</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001907320296867051</v>
+        <v>0.0001907320296867053</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001910117233340269</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001404510776737082</v>
+        <v>0.0001677465268750932</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001910117233340269</v>
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.470317080570983e-05</v>
+        <v>2.470317080570988e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.302162718945213e-05</v>
+        <v>2.302162718945216e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.259543214190577e-05</v>
+        <v>2.259543214190583e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.370279827026794e-05</v>
+        <v>2.370279827026803e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.370279827026794e-05</v>
+        <v>2.370279827026803e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.416662044128444e-05</v>
+        <v>2.416662044128443e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.254121834259018e-05</v>
+        <v>2.25412183425902e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.370279827026794e-05</v>
+        <v>2.370279827026803e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.465218969266413e-05</v>
+        <v>2.465218969266414e-05</v>
       </c>
       <c r="K8" t="n">
         <v>2.47870109791e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.386810238861697e-05</v>
+        <v>2.3868102388617e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.521239825552124e-05</v>
+        <v>2.52123982555213e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.362420400032431e-05</v>
+        <v>2.362420400032434e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.376287170615981e-05</v>
+        <v>2.376287170615984e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.45511238468128e-05</v>
+        <v>2.455112384681282e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.45511238468128e-05</v>
+        <v>2.455112384681282e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.495966812416227e-05</v>
+        <v>2.495966812416226e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.374283912791648e-05</v>
+        <v>2.374283912791651e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.45511238468128e-05</v>
+        <v>2.455112384681282e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.523292858060891e-05</v>
+        <v>2.52329285806089e-05</v>
       </c>
       <c r="K9" t="n">
         <v>2.536080077299487e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.457312165719672e-05</v>
+        <v>2.45731216571968e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.881951424520655e-05</v>
+        <v>7.881951424520651e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002064834359259811</v>
+        <v>0.0002064834359259808</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002539331552619358</v>
+        <v>0.0002539331552619362</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002183132195402463</v>
+        <v>0.000218313219540245</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002183132195402463</v>
+        <v>0.000218313219540245</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002224531614704987</v>
+        <v>0.0002224531614704952</v>
       </c>
       <c r="H2" t="n">
         <v>0.0002656626302862936</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002183132195402463</v>
+        <v>0.000218313219540245</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002277509741660675</v>
+        <v>0.0002277509741660676</v>
       </c>
       <c r="K2" t="n">
         <v>0.0001987206311797725</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.033137865801241e-06</v>
+        <v>8.033137865801233e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.973164309892548e-06</v>
+        <v>6.973164309892627e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.033137865801241e-06</v>
+        <v>8.033137865801233e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.320163517487637e-06</v>
+        <v>7.320163517487623e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.320163517487636e-06</v>
+        <v>7.320163517487625e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.966261788552815e-06</v>
+        <v>7.966261788552841e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.033137865801241e-06</v>
+        <v>8.033137865801233e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.750490322695071e-06</v>
+        <v>7.750490322694988e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.033137865801241e-06</v>
+        <v>8.033137865801233e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.033137865801241e-06</v>
+        <v>8.033137865801233e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.033137865801241e-06</v>
+        <v>8.033137865801233e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.511299145321708e-05</v>
+        <v>1.511299145321724e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.471992429430005e-05</v>
+        <v>1.471992429430007e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.518676824863586e-05</v>
+        <v>3.296417044345365e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458577436072934e-05</v>
+        <v>1.458577436072936e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484677414433514e-05</v>
+        <v>1.484677414433533e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.232943113970086e-05</v>
+        <v>1.504611537596873e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.408614472446407e-05</v>
+        <v>3.408614472446397e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.211365967384319e-05</v>
+        <v>3.211365967384323e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.559207877921165e-05</v>
+        <v>3.276462268138103e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.508972469323926e-05</v>
+        <v>1.508972469323927e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.512820896449283e-05</v>
+        <v>1.512820896449282e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.382360445755488e-05</v>
+        <v>5.382360445755503e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.35361821300792e-05</v>
+        <v>5.353618213007926e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.382358687963056e-05</v>
+        <v>5.38235868796305e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.355339273686708e-05</v>
+        <v>5.355339273686704e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.355339273686708e-05</v>
+        <v>5.355339273686704e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.375672838030649e-05</v>
+        <v>5.375672838030652e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.382360445755488e-05</v>
+        <v>5.382360445755503e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.354095691444871e-05</v>
+        <v>5.354095691444891e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.382360445755488e-05</v>
+        <v>5.382360445755503e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.382360445755488e-05</v>
+        <v>5.382360445755503e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.382360445755488e-05</v>
+        <v>5.382360445755503e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002338352051555599</v>
+        <v>0.0002338352051555598</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003783777001962799</v>
+        <v>0.0003783777001959718</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004086477503252015</v>
+        <v>0.0004086477503252024</v>
       </c>
       <c r="E6" t="n">
         <v>0.0003387795484485674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002381495902124238</v>
+        <v>0.000238149590212423</v>
       </c>
       <c r="G6" t="n">
         <v>0.0003785578283551015</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003786247044325317</v>
+        <v>0.0003786247044325315</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003783420568892439</v>
+        <v>0.0003783420568892431</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003786531597426997</v>
+        <v>0.0003786531597427001</v>
       </c>
       <c r="K6" t="n">
         <v>0.0002311456658692289</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005298694435519213</v>
+        <v>0.0005298694435519203</v>
       </c>
     </row>
     <row r="7">
@@ -3091,34 +3091,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001363623516663551</v>
+        <v>0.0001363623516663553</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001721384588266236</v>
+        <v>0.0001721384588266234</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001724258838102718</v>
+        <v>0.0001724258838102716</v>
       </c>
       <c r="E7" t="n">
         <v>0.0002137597751793308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001721432262579627</v>
+        <v>0.0001721432262579632</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001723590050768507</v>
+        <v>0.0001723590050768509</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001724258811540991</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001721432336109929</v>
+        <v>0.0001721432336109933</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001724258811540991</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001270154595233634</v>
+        <v>0.0001515305316536636</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001724258811540991</v>
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.546633064725679e-05</v>
+        <v>2.546633064725677e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.269130315789844e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.207614686577297e-05</v>
+        <v>2.207614686577292e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.35572806213083e-05</v>
+        <v>2.355728062130836e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.35572806213083e-05</v>
+        <v>2.355728062130834e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.386253545977784e-05</v>
+        <v>2.386253545977787e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.235532216590437e-05</v>
+        <v>2.235532216590441e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.35572806213083e-05</v>
+        <v>2.355728062130836e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.405151290430909e-05</v>
+        <v>2.405151290430913e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.465380968787737e-05</v>
+        <v>2.465380968787719e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.347767270714288e-05</v>
+        <v>2.347767270714294e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3174,34 +3174,34 @@
         <v>2.613890768220509e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.355963414570205e-05</v>
+        <v>2.355963414570202e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.368021882021151e-05</v>
+        <v>2.368021882021153e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.461677904240413e-05</v>
+        <v>2.461677904240414e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.461677904240413e-05</v>
+        <v>2.461677904240414e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.496002826956557e-05</v>
+        <v>2.496002826956548e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.379633535158405e-05</v>
+        <v>2.379633535158406e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.461677904240413e-05</v>
+        <v>2.461677904240414e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.514427219430192e-05</v>
+        <v>2.514427219430191e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.543250732354499e-05</v>
+        <v>2.543250732354482e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.448762491513118e-05</v>
+        <v>2.448762491513117e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,28 +3287,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.406952072551899e-05</v>
+        <v>8.406952072551919e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.0002181561387013351</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000256769294105575</v>
+        <v>0.0002567692941055755</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002208444835713953</v>
+        <v>0.0002208444835713961</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002208444835713953</v>
+        <v>0.0002208444835713961</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002296383831922598</v>
+        <v>0.0002296383831922629</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002691447238549735</v>
+        <v>0.000269144723854974</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002208444835713953</v>
+        <v>0.0002208444835713961</v>
       </c>
       <c r="J2" t="n">
         <v>0.0002565380342690679</v>
@@ -3317,7 +3317,7 @@
         <v>0.0002025748062918029</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000246723186595274</v>
+        <v>0.0002467231865952739</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.844923908727866e-06</v>
+        <v>8.844923908727514e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.73169021135808e-06</v>
+        <v>7.731690211358097e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.844923908727866e-06</v>
+        <v>8.844923908727514e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.169275209326686e-06</v>
+        <v>8.169275209326676e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.169275209326679e-06</v>
+        <v>8.169275209326676e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.777699753751087e-06</v>
+        <v>8.777699753747701e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.844923908727866e-06</v>
+        <v>8.844923908727514e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.560336297373209e-06</v>
+        <v>8.560336297367381e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.844923908727866e-06</v>
+        <v>8.844923908727514e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.844923908727866e-06</v>
+        <v>8.844923908727514e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.844923908727866e-06</v>
+        <v>8.844923908727514e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.387591770109521e-05</v>
+        <v>3.387591770109478e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.571386848336719e-05</v>
+        <v>1.571386848336732e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.616283407668161e-05</v>
+        <v>1.616283407668198e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.553989329305285e-05</v>
+        <v>1.553989329305291e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.584881477808961e-05</v>
+        <v>1.584881477808987e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.380869354611538e-05</v>
+        <v>3.380869354611537e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.61578873124705e-05</v>
+        <v>1.614374497408962e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.583054772810234e-05</v>
+        <v>3.359133008973474e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.435319893909794e-05</v>
+        <v>1.663509256489162e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.608493123911714e-05</v>
+        <v>1.608493123911744e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.613235967535543e-05</v>
+        <v>1.613235967535529e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.497429088176271e-05</v>
+        <v>5.497429088176302e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.468607233908104e-05</v>
+        <v>5.468607233908111e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.497426971129044e-05</v>
+        <v>5.497426971129081e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.471905662033055e-05</v>
+        <v>5.471905662033061e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.471905662033055e-05</v>
+        <v>5.471905662033061e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.490706672678291e-05</v>
+        <v>5.490706672678285e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.497429088176271e-05</v>
+        <v>5.497429088176302e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.468970327040231e-05</v>
+        <v>5.46897032704024e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.497429088176271e-05</v>
+        <v>5.497429088176302e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.497429088176271e-05</v>
+        <v>5.497429088176302e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.497429088176271e-05</v>
+        <v>5.497429088176302e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002355452301602028</v>
+        <v>0.000235545230160202</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003808961931719499</v>
+        <v>0.0003808961931724022</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004113151017813705</v>
+        <v>0.0004113151017813704</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003410782937201315</v>
+        <v>0.0003410782937201317</v>
       </c>
       <c r="F6" t="n">
         <v>0.0002398929034796563</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003810604164399552</v>
+        <v>0.0003810604164399557</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003811276405952122</v>
+        <v>0.0003811276405952123</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000380843052983575</v>
+        <v>0.0003808430529835748</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003811562517313251</v>
+        <v>0.0003811562517313241</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002328409621422528</v>
+        <v>0.000232840962142253</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005332006417180835</v>
+        <v>0.0005332006417180838</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001313973382011598</v>
+        <v>0.0001313973382011602</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001656717502756631</v>
+        <v>0.0001656717502756634</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001659599719707258</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002055599177445455</v>
+        <v>0.0002055599177445456</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001656753738484254</v>
+        <v>0.0001656753738484256</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001658927446633649</v>
+        <v>0.0001658927446633651</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001659599688183447</v>
+        <v>0.0001659599688183448</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001656753812069844</v>
+        <v>0.0001656753812069845</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001659599688183447</v>
+        <v>0.0001659599688183448</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001451217772369867</v>
+        <v>0.0001459342462267001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001659599688183447</v>
+        <v>0.0001659599688183448</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.729465408307195e-05</v>
+        <v>2.729465408307202e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.271921262863385e-05</v>
+        <v>2.27192126286339e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.253967266788319e-05</v>
+        <v>2.253967266788333e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.400887145213541e-05</v>
+        <v>2.400887145213546e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.400887145213541e-05</v>
+        <v>2.400887145213545e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.414693600219115e-05</v>
+        <v>2.414693600219118e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.281166190338428e-05</v>
+        <v>2.281166190338431e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.400887145213541e-05</v>
+        <v>2.400887145213545e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.42557696918271e-05</v>
+        <v>2.425576969182715e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.479603920951236e-05</v>
+        <v>2.479603920951242e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.368597582014178e-05</v>
+        <v>2.368597582014191e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.800499373527576e-05</v>
+        <v>2.80049937352759e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.374151457183539e-05</v>
+        <v>2.374151457183541e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.417062528005321e-05</v>
+        <v>2.417062528005332e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.509081466666929e-05</v>
+        <v>2.509081466666934e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.509081466666929e-05</v>
+        <v>2.509081466666934e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.533260927400451e-05</v>
+        <v>2.53326092740045e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.428387223087572e-05</v>
+        <v>2.42838722308755e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.509081466666929e-05</v>
+        <v>2.509081466666934e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.572494510577401e-05</v>
+        <v>2.57249451057741e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.562078543420142e-05</v>
+        <v>2.562078543420137e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.481546084361881e-05</v>
+        <v>2.481546084361884e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.328627833446957e-05</v>
+        <v>7.328627833446994e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000203604118466439</v>
+        <v>0.0002036041184664386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002545092525409212</v>
+        <v>0.0002545092525409226</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002200310953525521</v>
+        <v>0.0002200310953525527</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002200310953525521</v>
+        <v>0.0002200310953525527</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002201960300747109</v>
+        <v>0.0002201960300747262</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002653814320927501</v>
+        <v>0.0002653814320927516</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002200310953525521</v>
+        <v>0.0002200310953525527</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000217305248969304</v>
+        <v>0.0002173052489693049</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000199513866359709</v>
+        <v>0.0001995138663597101</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002271160688826421</v>
+        <v>0.0002271160688826436</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.78983854056724e-06</v>
+        <v>7.789838540568517e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.736245506874532e-06</v>
+        <v>6.736245506874537e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.78983854056724e-06</v>
+        <v>7.789838540568517e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.063370770053771e-06</v>
+        <v>7.063370770053728e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.063370770053768e-06</v>
+        <v>7.063370770053721e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.72325747101438e-06</v>
+        <v>7.723257471014168e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.78983854056724e-06</v>
+        <v>7.789838540568517e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.508885500998633e-06</v>
+        <v>7.508885500998713e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.78983854056724e-06</v>
+        <v>7.789838540568517e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.78983854056724e-06</v>
+        <v>7.789838540568517e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.78983854056724e-06</v>
+        <v>7.789838540568517e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.517123323065631e-05</v>
+        <v>1.517123323065766e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.478829632031295e-05</v>
+        <v>1.478829632031291e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.525871362316102e-05</v>
+        <v>1.525871362316244e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.465377666915528e-05</v>
+        <v>1.465377666915522e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4907620931615e-05</v>
+        <v>1.490762093161494e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.313463070195737e-05</v>
+        <v>1.510465216110341e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.439650976041672e-05</v>
+        <v>3.43965097604178e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.292025873194275e-05</v>
+        <v>1.489028019108779e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.351369890317888e-05</v>
+        <v>1.566454902718263e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.516307802128333e-05</v>
+        <v>1.516307802128405e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.518498600884798e-05</v>
+        <v>1.518498600884824e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.602977410080265e-05</v>
+        <v>5.602977410080345e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.574305474822613e-05</v>
+        <v>5.574305474822598e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.602974481955676e-05</v>
+        <v>5.602974481955796e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.575960685324212e-05</v>
+        <v>5.575960685324187e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.575960685324212e-05</v>
+        <v>5.575960685324187e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.596319303124867e-05</v>
+        <v>5.596319303124999e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.602977410080265e-05</v>
+        <v>5.602977410080345e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.574882106123367e-05</v>
+        <v>5.574882106123351e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.602977410080265e-05</v>
+        <v>5.602977410080345e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.602977410080265e-05</v>
+        <v>5.602977410080345e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.602977410080265e-05</v>
+        <v>5.602977410080345e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457271676430811</v>
+        <v>0.0002457271676430823</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003979948202730503</v>
+        <v>0.0003979948202728098</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004298659488839395</v>
+        <v>0.0004298659488839403</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003562850891434773</v>
+        <v>0.0003562850891434766</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002502871248636089</v>
+        <v>0.0002502871248636086</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003981745946924264</v>
+        <v>0.0003981745946924276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003982411757620354</v>
+        <v>0.0003982411757620347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003979602227224111</v>
+        <v>0.0003979602227224108</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003982711491617575</v>
+        <v>0.0003982711491617584</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002428941416391526</v>
+        <v>0.0002428941416391522</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005575548102816253</v>
+        <v>0.0005575548102816258</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001510907071096537</v>
+        <v>0.0001510907071096544</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001910140563179331</v>
+        <v>0.0001910140563179324</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001913007780769546</v>
+        <v>0.0001913007780769551</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002374213817254839</v>
+        <v>0.0002374213817254833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001910198149438423</v>
+        <v>0.0001910198149438422</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001912341946009555</v>
+        <v>0.0001912341946009559</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001913007756705095</v>
+        <v>0.0001913007756705096</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001910198226309406</v>
+        <v>0.0001910198226309399</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001913007756705095</v>
+        <v>0.0001913007756705096</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001680029050413636</v>
+        <v>0.0001680029050413635</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001913007756705095</v>
+        <v>0.0001913007756705096</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.548628216571011e-05</v>
+        <v>2.54862821657109e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.317469698933085e-05</v>
+        <v>2.317469698933077e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.218259837026074e-05</v>
+        <v>2.218259837026108e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.360746794667801e-05</v>
+        <v>2.360746794667797e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.360746794667801e-05</v>
+        <v>2.360746794667797e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.411681759149544e-05</v>
+        <v>2.411681759149591e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.245720385274417e-05</v>
+        <v>2.245720385274456e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.360746794667801e-05</v>
+        <v>2.360746794667797e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.429724876360006e-05</v>
+        <v>2.429724876359951e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.483073134134145e-05</v>
+        <v>2.483073134134232e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.378936984309114e-05</v>
+        <v>2.378936984309169e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.603774987792268e-05</v>
+        <v>2.603774987792383e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.385613688865242e-05</v>
+        <v>2.385613688865238e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.36117818995976e-05</v>
+        <v>2.361178189959867e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.45358297665011e-05</v>
+        <v>2.453582976650106e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.45358297665011e-05</v>
+        <v>2.453582976650106e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.502813532352043e-05</v>
+        <v>2.502813532352057e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.372577027243382e-05</v>
+        <v>2.372577027243514e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.45358297665011e-05</v>
+        <v>2.453582976650106e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.51004452455974e-05</v>
+        <v>2.510044524559784e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.547793380463076e-05</v>
+        <v>2.547793380463136e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.454373710251726e-05</v>
+        <v>2.454373710251777e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.130342075173969e-05</v>
+        <v>8.130342075173966e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002100005021519486</v>
+        <v>0.0002100005021519489</v>
       </c>
       <c r="D2" t="n">
         <v>0.0002544506438587369</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002190374172076113</v>
+        <v>0.000219037417207612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002190374172076113</v>
+        <v>0.000219037417207612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002252313765716198</v>
+        <v>0.0002252313765716168</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002682880457311472</v>
+        <v>0.0002682880457311471</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002190374172076113</v>
+        <v>0.000219037417207612</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000251627376625027</v>
+        <v>0.0002516273766250272</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002002517322008381</v>
+        <v>0.0002002517322008379</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002395797993109451</v>
+        <v>0.000239579799310945</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.995810337531652e-06</v>
+        <v>7.995810337532046e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.938021267482626e-06</v>
+        <v>6.938021267482627e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.995810337531652e-06</v>
+        <v>7.995810337532046e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.30576154310553e-06</v>
+        <v>7.305761543105625e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.30576154310553e-06</v>
+        <v>7.305761543105625e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.928428974973261e-06</v>
+        <v>7.928428974973408e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.995810337531652e-06</v>
+        <v>7.995810337532046e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.709788576156736e-06</v>
+        <v>7.709788576157046e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.995810337531652e-06</v>
+        <v>7.995810337532046e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.995810337531652e-06</v>
+        <v>7.995810337532046e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.995810337531652e-06</v>
+        <v>7.995810337532046e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.511449456044619e-05</v>
+        <v>3.238138643647917e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.472260187631293e-05</v>
+        <v>1.472260187631284e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.518663127051667e-05</v>
+        <v>1.51866097489752e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458325299530086e-05</v>
+        <v>1.458325299530093e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484572816883853e-05</v>
+        <v>1.484572816883849e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.504711319788757e-05</v>
+        <v>1.504711319788745e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.407055765922313e-05</v>
+        <v>3.407055765922325e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.209536467510415e-05</v>
+        <v>3.209536467510417e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.274564919407366e-05</v>
+        <v>1.560129608106891e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.50932313217883e-05</v>
+        <v>1.509323132178788e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.513059265812436e-05</v>
+        <v>1.513059265812431e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.375492711177869e-05</v>
+        <v>5.375492711177868e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.346748506913879e-05</v>
+        <v>5.346748506913875e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.375491231012455e-05</v>
+        <v>5.375491231012456e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.348924737064395e-05</v>
+        <v>5.348924737064407e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.348924737064395e-05</v>
+        <v>5.348924737064407e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.368754574922008e-05</v>
+        <v>5.368754574922007e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.375492711177869e-05</v>
+        <v>5.375492711177868e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.346890535040365e-05</v>
+        <v>5.34689053504037e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.375492711177869e-05</v>
+        <v>5.375492711177868e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.375492711177869e-05</v>
+        <v>5.375492711177868e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.375492711177869e-05</v>
+        <v>5.375492711177868e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002337440758365768</v>
+        <v>0.000233744075836577</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003782395275265688</v>
+        <v>0.0003782395275265686</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000408490742116932</v>
+        <v>0.0004084907421169311</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003386521493100887</v>
+        <v>0.000338652149310088</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002380580718369765</v>
+        <v>0.000238058071836977</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003784116291805845</v>
+        <v>0.0003784116291805861</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003784790105433303</v>
+        <v>0.0003784790105433296</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003781929887817693</v>
+        <v>0.0003781929887817695</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003785074551302388</v>
+        <v>0.0003785074551302379</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002310555501151218</v>
+        <v>0.0002310555501151225</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005296667524067477</v>
+        <v>0.0005296667524067481</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001363727196563697</v>
+        <v>0.0001363727196563696</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001721531272499292</v>
+        <v>0.0001721531272499293</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001724405719731029</v>
+        <v>0.0001724405719731027</v>
       </c>
       <c r="E7" t="n">
         <v>0.0002137760744349914</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001721545401411414</v>
+        <v>0.0001721545401411415</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001723731879300104</v>
+        <v>0.0001723731879300105</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001724405692925691</v>
+        <v>0.0001724405692925692</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001721545475311941</v>
+        <v>0.0001721545475311942</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001724405692925691</v>
+        <v>0.0001724405692925692</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001515427166913981</v>
+        <v>0.0001270247078174702</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001724405692925691</v>
+        <v>0.0001724405692925692</v>
       </c>
     </row>
     <row r="8">
@@ -4322,31 +4322,31 @@
         <v>3.40891569064389e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.311646418492915e-05</v>
+        <v>2.311646418492916e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.203630813717978e-05</v>
+        <v>2.203630813717976e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.37158688282957e-05</v>
+        <v>2.371586882829572e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.37158688282957e-05</v>
+        <v>2.371586882829572e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.472063282043378e-05</v>
+        <v>2.47206328204338e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.227163155913216e-05</v>
+        <v>2.227163155913214e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.37158688282957e-05</v>
+        <v>2.371586882829572e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.348483332122419e-05</v>
+        <v>2.348483332122417e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.537283058851723e-05</v>
+        <v>2.537283058851712e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.338920927478316e-05</v>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.466073857100707e-05</v>
+        <v>3.466073857100708e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.402640592094312e-05</v>
+        <v>2.402640592094314e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.36483896638152e-05</v>
+        <v>2.364838966381521e-05</v>
       </c>
       <c r="E9" t="n">
         <v>2.478311236076824e-05</v>
@@ -4374,22 +4374,22 @@
         <v>2.478311236076824e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.584277470292962e-05</v>
+        <v>2.584277470292961e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.374669799353839e-05</v>
+        <v>2.374669799353837e-05</v>
       </c>
       <c r="I9" t="n">
         <v>2.478311236076824e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.490592866822069e-05</v>
+        <v>2.490592866822068e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.616184075663681e-05</v>
+        <v>2.616184075663674e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.444121095018594e-05</v>
+        <v>2.444121095018595e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.332251137702261e-05</v>
+        <v>8.332251137702226e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002166425821214575</v>
+        <v>0.0002166425821214574</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002529389665772102</v>
+        <v>0.0002529389665772096</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002208035569144128</v>
+        <v>0.0002208035569144127</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002208035569144128</v>
+        <v>0.0002208035569144127</v>
       </c>
       <c r="G2" t="n">
         <v>0.0002285210671437047</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002696255025663373</v>
+        <v>0.000269625502566337</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002208035569144128</v>
+        <v>0.0002208035569144127</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002609882497868035</v>
+        <v>0.000260988249786803</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002018301883058993</v>
+        <v>0.0002018301883058992</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002450931595243697</v>
+        <v>0.0002450931595243695</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.652889781204423e-06</v>
+        <v>8.652889781204233e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.541272952922095e-06</v>
+        <v>7.541272952922017e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.652889781204423e-06</v>
+        <v>8.652889781204233e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.037877665053939e-06</v>
+        <v>8.037877665053792e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.037877665053951e-06</v>
+        <v>8.037877665053797e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.584017443728687e-06</v>
+        <v>8.584017443728453e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.652889781204423e-06</v>
+        <v>8.652889781204233e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.357184892460874e-06</v>
+        <v>8.357184892460705e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.652889781204445e-06</v>
+        <v>8.652889781204233e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.652889781204423e-06</v>
+        <v>8.652889781204233e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.652889781204423e-06</v>
+        <v>8.652889781204233e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.58714385073669e-05</v>
+        <v>3.350351614749699e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.546936716645218e-05</v>
+        <v>1.546936716645214e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.591782337644892e-05</v>
+        <v>1.591784233642247e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.531264576805762e-05</v>
+        <v>1.531264576805759e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.55987934716454e-05</v>
+        <v>1.559879347164544e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.343464381002117e-05</v>
+        <v>1.580256616989101e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.571442451420063e-05</v>
+        <v>3.571442451420041e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.320781125875354e-05</v>
+        <v>1.557573361862332e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.637346486125525e-05</v>
+        <v>3.396743988476388e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.583971009124316e-05</v>
+        <v>1.583971009124308e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.589470405404859e-05</v>
+        <v>1.589470405404849e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.467543576404734e-05</v>
+        <v>5.467543576404718e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.438732066557274e-05</v>
+        <v>5.438732066557262e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.467541786412452e-05</v>
+        <v>5.467541786412435e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.442942967777312e-05</v>
+        <v>5.442942967777285e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.442942967777312e-05</v>
+        <v>5.442942967777285e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.460656342657133e-05</v>
+        <v>5.460656342657137e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.467543576404734e-05</v>
+        <v>5.467543576404718e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.437973087530371e-05</v>
+        <v>5.437973087530362e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.467543576404734e-05</v>
+        <v>5.467543576404718e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.467543576404734e-05</v>
+        <v>5.467543576404718e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.467543576404734e-05</v>
+        <v>5.467543576404718e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002351283661971109</v>
+        <v>0.0002351283661971102</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003802726428222144</v>
+        <v>0.0003802726428217748</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004106251501429653</v>
+        <v>0.0004106251501429643</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003405033341964541</v>
+        <v>0.0003405033341964531</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002394698875762125</v>
+        <v>0.0002394698875762123</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003804157178513606</v>
+        <v>0.0003804157178513604</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003804845901891091</v>
+        <v>0.0003804845901891084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003801888853000924</v>
+        <v>0.0003801888853000922</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003805131568746464</v>
+        <v>0.0003805131568746453</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002324282997083078</v>
+        <v>0.0002324282997083074</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005323213206603258</v>
+        <v>0.0005323213206603242</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001311341385605499</v>
+        <v>0.0001311341385605494</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001653527023763696</v>
+        <v>0.0001653527023763693</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001656408205248486</v>
+        <v>0.0001656408205248487</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002051650819786416</v>
+        <v>0.000205165081978641</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000165345105248577</v>
+        <v>0.0001653451052485768</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000165571945137368</v>
+        <v>0.0001655719451373677</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000165640817474844</v>
+        <v>0.0001656408174748437</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001653451125861006</v>
+        <v>0.0001653451125860998</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000165640817474844</v>
+        <v>0.0001656408174748437</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001448363597542572</v>
+        <v>0.0001448363597542567</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000165640817474844</v>
+        <v>0.0001656408174748437</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.819510156487272e-05</v>
+        <v>5.819510156487284e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.336888899278681e-05</v>
+        <v>2.336888899278676e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.245606209053388e-05</v>
+        <v>2.245606209053387e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.392785032007202e-05</v>
+        <v>2.392785032007179e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.392785032007202e-05</v>
+        <v>2.392785032007179e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.699791675638975e-05</v>
+        <v>2.699791675638971e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.262445179547974e-05</v>
+        <v>2.262445179547969e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.392785032007202e-05</v>
+        <v>2.392785032007179e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.388460434260807e-05</v>
+        <v>2.388460434260808e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.514229361618211e-05</v>
+        <v>2.514229361618212e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.359539754712564e-05</v>
+        <v>2.359539754712568e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.841218284027453e-05</v>
+        <v>5.841218284027443e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.436099793520641e-05</v>
+        <v>2.436099793520642e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.40351695274676e-05</v>
+        <v>2.403516952746754e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.50114403512995e-05</v>
+        <v>2.501144035129942e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.501144035129948e-05</v>
+        <v>2.501144035129942e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.812446260006645e-05</v>
+        <v>2.812446260006638e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.410623448615125e-05</v>
+        <v>2.410623448615109e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.50114403512995e-05</v>
+        <v>2.501144035129942e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.541984416272339e-05</v>
+        <v>2.541984416272337e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.595195261475507e-05</v>
+        <v>2.595195261475496e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.470707968642875e-05</v>
+        <v>2.470707968642883e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001883585416468594</v>
+        <v>0.00018835854164686</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002078188942697021</v>
+        <v>0.000207818894269702</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001966769740404304</v>
+        <v>0.0001966769740404309</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002078188942697021</v>
+        <v>0.000207818894269702</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002078188942697021</v>
+        <v>0.000207818894269702</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001888222617823283</v>
+        <v>0.0001888222617823272</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002038699187735645</v>
+        <v>0.0002038699187735649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002078188942697021</v>
+        <v>0.000207818894269702</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001973971314192456</v>
+        <v>0.0001973971314192439</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000183419815064526</v>
+        <v>0.0001834198150645251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001920505311137788</v>
+        <v>0.0001920505311137785</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.027221813380243e-06</v>
+        <v>7.027221813380257e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.291283185805515e-06</v>
+        <v>6.291283185805561e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.027221813380243e-06</v>
+        <v>7.027221813380257e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.339469236671555e-06</v>
+        <v>6.339469236671698e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.339469236671554e-06</v>
+        <v>6.339469236671699e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.962028001241275e-06</v>
+        <v>6.962028001241259e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.027221813380243e-06</v>
+        <v>7.027221813380257e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.754487183324648e-06</v>
+        <v>6.754487183324734e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.027221813380243e-06</v>
+        <v>7.027221813380257e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.027221813380243e-06</v>
+        <v>7.027221813380257e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.027221813380243e-06</v>
+        <v>7.027221813380257e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4951,34 +4951,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.219932888130489e-05</v>
+        <v>1.450540011019829e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420733772466925e-05</v>
+        <v>1.420733772466935e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.455100141086948e-05</v>
+        <v>1.455096025756212e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.399782032069918e-05</v>
+        <v>1.399782032069919e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.424180826159969e-05</v>
+        <v>1.424180826159976e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.21341350691659e-05</v>
+        <v>1.444020629805927e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.227888246084647e-05</v>
+        <v>3.227888246084649e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.192659425124925e-05</v>
+        <v>3.192659425124946e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.226864294932582e-05</v>
+        <v>1.498879124756719e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453375791672654e-05</v>
+        <v>1.453375791672653e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.452068547462676e-05</v>
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.542088017586322e-05</v>
+        <v>5.542088017586323e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.514814554580763e-05</v>
+        <v>5.51481455458077e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.54207096973726e-05</v>
+        <v>5.542070969737263e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.514696499143896e-05</v>
+        <v>5.514696499143909e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.514696499143896e-05</v>
+        <v>5.514696499143909e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.535568636372424e-05</v>
+        <v>5.535568636372423e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.542088017586322e-05</v>
+        <v>5.542088017586323e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.514814554580763e-05</v>
+        <v>5.51481455458077e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.542088017586322e-05</v>
+        <v>5.542088017586323e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.542088017586322e-05</v>
+        <v>5.542088017586323e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.542088017586322e-05</v>
+        <v>5.542088017586323e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002472157093151746</v>
+        <v>0.0002472157093151749</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004006838452641282</v>
+        <v>0.0004006838452642411</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000432800366888107</v>
+        <v>0.0004328003668881066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003586419868442879</v>
+        <v>0.0003586419868442881</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002518147913271922</v>
+        <v>0.0002518147913271921</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004008620790374243</v>
+        <v>0.0004008620790374244</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004009272728495581</v>
+        <v>0.0004009272728495579</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004006545382195075</v>
+        <v>0.0004006545382195073</v>
       </c>
       <c r="J6" t="n">
         <v>0.0004009574816040658</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002443604381046928</v>
+        <v>0.0002443604381046927</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005614918541387788</v>
+        <v>0.0005614918541387786</v>
       </c>
     </row>
     <row r="7">
@@ -5074,34 +5074,34 @@
         <v>0.0001507563243906442</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001907107607462867</v>
+        <v>0.0001907107607462869</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001909834966176941</v>
+        <v>0.0001909834966176943</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002371320544751098</v>
+        <v>0.0002371320544751099</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001907107529406781</v>
+        <v>0.0001907107529406782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001909183015642035</v>
+        <v>0.0001909183015642033</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001909834953763426</v>
+        <v>0.0001909834953763427</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001907107607462867</v>
+        <v>0.0001907107607462869</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001909834953763426</v>
+        <v>0.0001909834953763427</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001676757150450418</v>
+        <v>0.0001676757150450422</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001909834953763426</v>
+        <v>0.0001909834953763427</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.377994250782084e-05</v>
+        <v>2.377994250782085e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.434165951225635e-05</v>
+        <v>2.434165951225634e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.346929706211963e-05</v>
+        <v>2.34692970621196e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.434165951225635e-05</v>
+        <v>2.434165951225634e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.434165951225635e-05</v>
+        <v>2.434165951225634e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.365129209309338e-05</v>
+        <v>2.365129209309335e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.363600253402214e-05</v>
+        <v>2.363600253402212e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.434165951225635e-05</v>
+        <v>2.434165951225634e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.342964006754811e-05</v>
+        <v>2.34296400675481e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.373305316759396e-05</v>
+        <v>2.373305316759395e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.365195157613795e-05</v>
+        <v>2.365195157613799e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.40935607608268e-05</v>
+        <v>2.409356076082678e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.464077201902058e-05</v>
+        <v>2.464077201902055e-05</v>
       </c>
       <c r="D9" t="n">
         <v>2.396706614081864e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.464077201902058e-05</v>
+        <v>2.464077201902055e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.464077201902058e-05</v>
+        <v>2.464077201902055e-05</v>
       </c>
       <c r="G9" t="n">
         <v>2.401803567689476e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.403577698396454e-05</v>
+        <v>2.40357769839645e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.464077201902058e-05</v>
+        <v>2.464077201902055e-05</v>
       </c>
       <c r="J9" t="n">
         <v>2.395130778331396e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.407450640644618e-05</v>
+        <v>2.407450640644616e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.40420941672759e-05</v>
+        <v>2.400056174947372e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001769823896620229</v>
+        <v>0.0001769823896620232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000203101197438533</v>
+        <v>0.0002031011974385333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001932936259765697</v>
+        <v>0.0001932936259765656</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000203101197438533</v>
+        <v>0.0002031011974385333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000203101197438533</v>
+        <v>0.0002031011974385333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001857118367455359</v>
+        <v>0.0001857118367455416</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001973220518100462</v>
+        <v>0.0001973220518100461</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000203101197438533</v>
+        <v>0.0002031011974385333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001934830844920068</v>
+        <v>0.0001934830844920071</v>
       </c>
       <c r="K2" t="n">
         <v>0.0001943370070901187</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001937831456065299</v>
+        <v>0.0001937831456065301</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.160532067840162e-06</v>
+        <v>7.160532067840128e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.457559465456778e-06</v>
+        <v>6.457559465456773e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.160532067840174e-06</v>
+        <v>7.160532067840135e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.510570331122822e-06</v>
+        <v>6.510570331122788e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.510570331122822e-06</v>
+        <v>6.510570331122795e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.095333875101843e-06</v>
+        <v>7.095333875101822e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.160532067840174e-06</v>
+        <v>7.160532067840135e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.887841151501295e-06</v>
+        <v>6.887841151501242e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.160532067840174e-06</v>
+        <v>7.160532067840135e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.160532067840174e-06</v>
+        <v>7.160532067840135e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.160532067840174e-06</v>
+        <v>7.160532067840135e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.079917089506755e-05</v>
+        <v>1.415600176696668e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.385359019141548e-05</v>
+        <v>1.38535901914158e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.419130254736404e-05</v>
+        <v>1.419130254736109e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.365727355497414e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.389086690497226e-05</v>
+        <v>1.389086690497243e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.07339727023287e-05</v>
+        <v>1.409080357422838e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.095652515952449e-05</v>
+        <v>3.095652515952458e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.052647997872878e-05</v>
+        <v>3.052647997872832e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.085490860437177e-05</v>
+        <v>1.460977605701403e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.418096107857227e-05</v>
+        <v>1.418096107857257e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.416814816998989e-05</v>
+        <v>1.416814816998973e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.232244614639447e-05</v>
+        <v>5.232244614639465e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.204975523005563e-05</v>
+        <v>5.204975523005561e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.232227192376687e-05</v>
+        <v>5.232227192376702e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.205205719597778e-05</v>
+        <v>5.205205719597781e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.205205719597778e-05</v>
+        <v>5.205205719597781e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.225724795365618e-05</v>
+        <v>5.225724795365626e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.23224461463945e-05</v>
+        <v>5.232244614639463e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.204975523005563e-05</v>
+        <v>5.204975523005561e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.23224461463945e-05</v>
+        <v>5.232244614639463e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.23224461463945e-05</v>
+        <v>5.232244614639463e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.23224461463945e-05</v>
+        <v>5.232244614639463e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002311890709617556</v>
+        <v>0.0002311890709617557</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003743518455065342</v>
+        <v>0.0003743518455065346</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004043298397938348</v>
+        <v>0.0004043298397938347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003351286322283217</v>
+        <v>0.0003351286322283222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002354635692210607</v>
+        <v>0.0002354635692210609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003745287136474567</v>
+        <v>0.0003745287136474568</v>
       </c>
       <c r="H6" t="n">
         <v>0.0003745939118401909</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003743212209238565</v>
+        <v>0.0003743212209238561</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003746220950262</v>
+        <v>0.0003746220950262004</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002285252524161885</v>
+        <v>0.0002285252524161888</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005243922594792615</v>
+        <v>0.000524392259479262</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001336424445790538</v>
+        <v>0.0001336424445790533</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001688102047834618</v>
+        <v>0.0001688102047834622</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001690828969612102</v>
+        <v>0.0001690828969612104</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002097077258719467</v>
+        <v>0.0002097077258719471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001688101974345135</v>
+        <v>0.0001688101974345138</v>
       </c>
       <c r="G7" t="n">
         <v>0.0001690176975070627</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001690828956998009</v>
+        <v>0.0001690828956998013</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001688102047834618</v>
+        <v>0.0001688102047834622</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001690828956998009</v>
+        <v>0.0001690828956998013</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000124457041313701</v>
+        <v>0.000148548559665589</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001690828956998009</v>
+        <v>0.0001690828956998013</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.374143038804887e-05</v>
+        <v>2.374143038804893e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.436881977115274e-05</v>
+        <v>2.436881977115282e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.351478981936207e-05</v>
+        <v>2.351478981936115e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.436881977115274e-05</v>
+        <v>2.436881977115282e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.436881977115274e-05</v>
+        <v>2.436881977115282e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.365486621689071e-05</v>
+        <v>2.365486621689064e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.359101326876278e-05</v>
+        <v>2.359101326876283e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.436881977115274e-05</v>
+        <v>2.436881977115282e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.333896735554537e-05</v>
+        <v>2.333896735554543e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.368428180520956e-05</v>
+        <v>2.368428180520962e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.35466118965989e-05</v>
+        <v>2.354661189659894e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.414867049783149e-05</v>
+        <v>2.414867049783151e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.473027913930711e-05</v>
+        <v>2.473027913930716e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.405639255276155e-05</v>
+        <v>2.405639255276145e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.473027913930711e-05</v>
+        <v>2.473027913930716e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.473027913930711e-05</v>
+        <v>2.473027913930716e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.409013347923638e-05</v>
+        <v>2.409013347923643e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.408840380473067e-05</v>
+        <v>2.408840380473071e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.473027913930711e-05</v>
+        <v>2.473027913930716e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.398525386766494e-05</v>
+        <v>2.398525386766504e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.41254466383423e-05</v>
+        <v>2.412544663834238e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.407015492697128e-05</v>
+        <v>2.407970398860816e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001875187311682287</v>
+        <v>0.0001875187311682294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000210342098360028</v>
+        <v>0.0002103420983600297</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002095211526585455</v>
+        <v>0.0002095211526585468</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000210342098360028</v>
+        <v>0.0002103420983600297</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000210342098360028</v>
+        <v>0.0002103420983600297</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001969439593866412</v>
+        <v>0.0001969439593866454</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002169173070727738</v>
+        <v>0.0002169173070727707</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000210342098360028</v>
+        <v>0.0002103420983600297</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000203207254132331</v>
+        <v>0.0002032072541323314</v>
       </c>
       <c r="K2" t="n">
         <v>0.0002091621389990633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000209009779022474</v>
+        <v>0.0002236116655485306</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.278144634662047e-06</v>
+        <v>7.278144634662158e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.587564831985925e-06</v>
+        <v>6.587564831986071e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.278144634662044e-06</v>
+        <v>7.278144634662144e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.643798311945082e-06</v>
+        <v>6.643798311945052e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.643798311945015e-06</v>
+        <v>6.643798311945045e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.213022719382574e-06</v>
+        <v>7.213022719382576e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.278144634662044e-06</v>
+        <v>7.278144634662144e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.005982378390125e-06</v>
+        <v>7.005982378390288e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.278144634662044e-06</v>
+        <v>7.278144634662146e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.278144634662044e-06</v>
+        <v>7.278144634662144e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.278144634662044e-06</v>
+        <v>7.278144634662144e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.429832519501595e-05</v>
+        <v>1.429832519501606e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.399977456230678e-05</v>
+        <v>1.399977456230687e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.124802626406542e-05</v>
+        <v>1.433321669576721e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.380154244048272e-05</v>
+        <v>1.380154244048294e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.403569339300025e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.423320327973646e-05</v>
+        <v>3.094435457882189e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.12053423256349e-05</v>
+        <v>3.120534232563558e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.073731423782938e-05</v>
+        <v>1.402616293874423e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.475687943682701e-05</v>
+        <v>3.106393348250758e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.431987370730692e-05</v>
+        <v>1.431987370730711e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.431092933768305e-05</v>
+        <v>1.431092933768302e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.247847414475673e-05</v>
+        <v>5.247847414475686e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.220631188848464e-05</v>
+        <v>5.220631188848479e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.247829459734159e-05</v>
+        <v>5.247829459734169e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.221326914807871e-05</v>
+        <v>5.22132691480787e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.221326914807871e-05</v>
+        <v>5.22132691480787e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.241335222947709e-05</v>
+        <v>5.241335222947718e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.247847414475669e-05</v>
+        <v>5.247847414475679e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.220631188848464e-05</v>
+        <v>5.220631188848479e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.247847414475669e-05</v>
+        <v>5.247847414475679e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.247847414475669e-05</v>
+        <v>5.247847414475679e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.247847414475669e-05</v>
+        <v>5.247847414475679e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002314051199201438</v>
+        <v>0.0002314051199201439</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003746528531887098</v>
+        <v>0.0003746528531887104</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004046424197640245</v>
+        <v>0.0004046424197640256</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003354072938079203</v>
+        <v>0.0003354072938079209</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002356854614913172</v>
+        <v>0.0002356854614913177</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003748247912508595</v>
+        <v>0.0003748247912508598</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000374889913166136</v>
+        <v>0.0003748899131661372</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000374617750909867</v>
+        <v>0.0003746177509098673</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003749181120649046</v>
+        <v>0.0003749181120649048</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002287398162182953</v>
+        <v>0.0002287398162182957</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005247717777385031</v>
+        <v>0.0005247717777385041</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001277850236746303</v>
+        <v>0.0001277850236746304</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001613084630656725</v>
+        <v>0.0001613084630656731</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001615806266853015</v>
+        <v>0.0001615806266853018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002003078628505592</v>
+        <v>0.0002003078628505597</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001613084557328377</v>
+        <v>0.0001613084557328385</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001615155034066652</v>
+        <v>0.0001615155034066649</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001615806253219446</v>
+        <v>0.0001615806253219447</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001613084630656725</v>
+        <v>0.0001613084630656731</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001615806253219446</v>
+        <v>0.0001615806253219447</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000141999321575341</v>
+        <v>0.0001419993215753409</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001615806253219446</v>
+        <v>0.0001615806253219447</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.37813442407703e-05</v>
+        <v>2.378134424077038e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.433543666092172e-05</v>
+        <v>2.433543666092167e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.349709368491918e-05</v>
+        <v>2.349709368491921e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.433543666092172e-05</v>
+        <v>2.433543666092167e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.433543666092172e-05</v>
+        <v>2.433543666092167e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.364335786036902e-05</v>
+        <v>2.36433578603692e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.359011445215184e-05</v>
+        <v>2.359011445215191e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.433543666092172e-05</v>
+        <v>2.433543666092167e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.316681789934235e-05</v>
+        <v>2.316681789934239e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.369831376118086e-05</v>
+        <v>2.369831376118085e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.352734471743693e-05</v>
+        <v>2.35273447174366e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.420374605840148e-05</v>
+        <v>2.420374605840146e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.476196981605916e-05</v>
+        <v>2.476196981605928e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.408800617170072e-05</v>
+        <v>2.408800617170076e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.476196981605916e-05</v>
+        <v>2.476196981605928e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.476196981605916e-05</v>
+        <v>2.476196981605928e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.412439985491667e-05</v>
+        <v>2.412439985491677e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.412691957454647e-05</v>
+        <v>2.412691957454649e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.476196981605916e-05</v>
+        <v>2.476196981605928e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.395404852532793e-05</v>
+        <v>2.395404852532796e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.416998345432707e-05</v>
+        <v>2.416998345432704e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.410119735940383e-05</v>
+        <v>2.410119735940385e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000205979926172692</v>
+        <v>0.0002059799261726977</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002147577044985771</v>
+        <v>0.0002147577044985776</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002459415536195259</v>
+        <v>0.000245941553619526</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002147577044985771</v>
+        <v>0.0002147577044985776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002147577044985771</v>
+        <v>0.0002147577044985776</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002150067804600836</v>
+        <v>0.0002150067804600814</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002484737562262975</v>
+        <v>0.0002484737562262976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002147577044985771</v>
+        <v>0.0002147577044985776</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00020419977002769</v>
+        <v>0.0002041997700276915</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002069988347007239</v>
+        <v>0.0002069988347007254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002226371960876406</v>
+        <v>0.0002226371960876411</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.081121922711865e-06</v>
+        <v>7.081121922712115e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.358650745720145e-06</v>
+        <v>6.35865074572002e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.081121922711865e-06</v>
+        <v>7.081121922712115e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.406716003312531e-06</v>
+        <v>6.406716003312364e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.406716003312516e-06</v>
+        <v>6.406716003312399e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.015925385950701e-06</v>
+        <v>7.015925385950733e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.081121922711865e-06</v>
+        <v>7.081121922712115e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.808369922625086e-06</v>
+        <v>6.808369922625261e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.081121922711865e-06</v>
+        <v>7.081121922712115e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.081121922711865e-06</v>
+        <v>7.081121922712115e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.081121922711865e-06</v>
+        <v>7.081121922712115e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.458827760101103e-05</v>
+        <v>3.231718868826488e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.429555773216024e-05</v>
+        <v>1.429555773216019e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.258376049238553e-05</v>
+        <v>3.25837604923856e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.408346985017953e-05</v>
+        <v>1.408346985017964e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.432727088908615e-05</v>
+        <v>1.432727088908611e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.452308106424975e-05</v>
+        <v>3.225199215150372e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.239350172735804e-05</v>
+        <v>1.460235949990754e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.431552560092425e-05</v>
+        <v>3.204443668817792e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.238419514004913e-05</v>
+        <v>3.238419514004916e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.462092085779151e-05</v>
+        <v>1.462092085779149e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46038734691892e-05</v>
+        <v>1.460387346918924e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6182,25 +6182,25 @@
         <v>5.549103134688987e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.521827934680331e-05</v>
+        <v>5.521827934680301e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.549085703340271e-05</v>
+        <v>5.549085703340252e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.522069083747776e-05</v>
+        <v>5.522069083747753e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.522069083747776e-05</v>
+        <v>5.522069083747753e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.54258348101288e-05</v>
+        <v>5.542583481012866e-05</v>
       </c>
       <c r="H5" t="n">
         <v>5.549103134688987e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.521827934680331e-05</v>
+        <v>5.521827934680301e-05</v>
       </c>
       <c r="J5" t="n">
         <v>5.549103134688987e-05</v>
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002473043513569889</v>
+        <v>0.0002473043513569891</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004008052549601674</v>
+        <v>0.0004008052549601681</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000432924431684305</v>
+        <v>0.0004329244316843057</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003587550054673491</v>
+        <v>0.0003587550054673494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00025190649112023</v>
+        <v>0.0002519064911202299</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004009800574553462</v>
+        <v>0.0004009800574553467</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000401045253992102</v>
+        <v>0.0004010452539921022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004007725019920206</v>
+        <v>0.0004007725019920214</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004010754685124519</v>
+        <v>0.0004010754685124515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002444485351576619</v>
+        <v>0.0002444485351576618</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005616404824252039</v>
+        <v>0.0005616404824252042</v>
       </c>
     </row>
     <row r="7">
@@ -6259,13 +6259,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000150941549242922</v>
+        <v>0.0001509415492429223</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001909354484193554</v>
+        <v>0.0001909354484193558</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001912082018844751</v>
+        <v>0.0001912082018844754</v>
       </c>
       <c r="E7" t="n">
         <v>0.0002374023018279716</v>
@@ -6274,22 +6274,22 @@
         <v>0.000190935440753344</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001911430038826813</v>
+        <v>0.0001911430038826816</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001912082004194426</v>
+        <v>0.0001912082004194428</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001909354484193554</v>
+        <v>0.0001909354484193558</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001912082004194426</v>
+        <v>0.0001912082004194428</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001678775452046082</v>
+        <v>0.0001678775452046084</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001912082004194426</v>
+        <v>0.0001912082004194428</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.348737806551966e-05</v>
+        <v>2.348737806551969e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.426811836871283e-05</v>
+        <v>2.426811836871284e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.330829260215298e-05</v>
+        <v>2.3308292602153e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.426811836871283e-05</v>
+        <v>2.426811836871284e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.426811836871283e-05</v>
+        <v>2.426811836871284e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.360659860230852e-05</v>
+        <v>2.360659860230855e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.366726461418191e-05</v>
+        <v>2.366726461418194e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.426811836871283e-05</v>
+        <v>2.426811836871284e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.332588443982114e-05</v>
+        <v>2.332588443982115e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.36512705533924e-05</v>
+        <v>2.365127055339232e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.300796750363189e-05</v>
+        <v>2.35404872178309e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.399678937386066e-05</v>
+        <v>2.399678937386069e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.463555061936779e-05</v>
+        <v>2.463555061936786e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.392388359209465e-05</v>
+        <v>2.392388359209467e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.463555061936781e-05</v>
+        <v>2.463555061936786e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.463555061936781e-05</v>
+        <v>2.463555061936786e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.402240107958949e-05</v>
+        <v>2.402240107958956e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.407090479302107e-05</v>
+        <v>2.407090479302106e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.463555061936781e-05</v>
+        <v>2.463555061936786e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.393149129090953e-05</v>
+        <v>2.39314912909095e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.406359148117821e-05</v>
+        <v>2.406359148117819e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.401920055386605e-05</v>
+        <v>2.401920055386602e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001987491412224536</v>
+        <v>0.0001987491412224537</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000222719113629356</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="D2" t="n">
         <v>0.0002554590075368718</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000222719113629356</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000222719113629356</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002251723243846683</v>
+        <v>0.0002251723243846819</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000288992394354267</v>
+        <v>0.0002889923943542668</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000222719113629356</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="J2" t="n">
         <v>0.0002278130299220598</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002102787211528067</v>
+        <v>0.0002102787211528063</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000255111026260592</v>
+        <v>0.0002551110262605922</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.27947413504536e-06</v>
+        <v>7.279474135045375e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.573903097556275e-06</v>
+        <v>6.573903097556324e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.27947413504536e-06</v>
+        <v>7.279474135045375e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.628991184744255e-06</v>
+        <v>6.628991184744278e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.628991184744317e-06</v>
+        <v>6.628991184744326e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.214156936741499e-06</v>
+        <v>7.214156936741529e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.27947413504536e-06</v>
+        <v>7.279474135045375e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.00603845832039e-06</v>
+        <v>7.006038458320472e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.27947413504536e-06</v>
+        <v>7.279474135045375e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.27947413504536e-06</v>
+        <v>7.279474135045375e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.27947413504536e-06</v>
+        <v>7.279474135045375e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6535,34 +6535,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.109797354749366e-05</v>
+        <v>3.109797354749381e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.405190883629864e-05</v>
+        <v>1.405190883629871e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.440711950261254e-05</v>
+        <v>1.440708235690887e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.385059418522496e-05</v>
+        <v>1.385059418522502e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.409093083040987e-05</v>
+        <v>1.409093083040994e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.428978823612652e-05</v>
+        <v>3.103265634918993e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.437495322744665e-05</v>
+        <v>3.127522604542043e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.408166975770542e-05</v>
+        <v>3.082453787076889e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.115887624782069e-05</v>
+        <v>1.481447539709815e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.438175797693085e-05</v>
+        <v>1.438175797693084e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.437015888756138e-05</v>
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.250914009457208e-05</v>
+        <v>5.250914009457199e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.223570441784709e-05</v>
+        <v>5.22357044178471e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.250896465970461e-05</v>
+        <v>5.250896465970457e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.223813132282299e-05</v>
+        <v>5.223813132282308e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.223813132282299e-05</v>
+        <v>5.223813132282308e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.244382289626822e-05</v>
+        <v>5.244382289626825e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.250914009457208e-05</v>
+        <v>5.250914009457199e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.223570441784709e-05</v>
+        <v>5.22357044178471e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.250914009457208e-05</v>
+        <v>5.250914009457199e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.250914009457208e-05</v>
+        <v>5.250914009457199e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.250914009457208e-05</v>
+        <v>5.250914009457199e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002314339200373247</v>
+        <v>0.0002314339200373251</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003746945045769136</v>
+        <v>0.0003746945045769128</v>
       </c>
       <c r="D6" t="n">
         <v>0.0004046935100844329</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003354443606037292</v>
+        <v>0.0003354443606037287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002357108683748783</v>
+        <v>0.0002357108683748788</v>
       </c>
       <c r="G6" t="n">
         <v>0.0003748718580744687</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00037493717527277</v>
+        <v>0.0003749371752727702</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003746637395960473</v>
+        <v>0.0003746637395960474</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000374965377799835</v>
+        <v>0.0003749653777998353</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002287682733945683</v>
+        <v>0.0002287682733945688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005248383249368344</v>
+        <v>0.0005248383249368346</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001341714599003595</v>
+        <v>0.0001341714599003598</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001694598980339353</v>
+        <v>0.0001694598980339356</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001697333350993635</v>
+        <v>0.0001697333350993637</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002104975381624624</v>
+        <v>0.0002104975381624633</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001694598904576303</v>
+        <v>0.0001694598904576305</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001696680165123565</v>
+        <v>0.0001696680165123567</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00016973333371066</v>
+        <v>0.0001697333337106603</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001694598980339353</v>
+        <v>0.0001694598980339356</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00016973333371066</v>
+        <v>0.0001697333337106603</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001482926866396879</v>
+        <v>0.0001491286449467973</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00016973333371066</v>
+        <v>0.0001697333337106603</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.338225492646696e-05</v>
+        <v>2.3382254926467e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.412234434175236e-05</v>
+        <v>2.412234434175238e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.305173380891995e-05</v>
+        <v>2.305173380891997e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.412234434175236e-05</v>
+        <v>2.412234434175238e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.412234434175236e-05</v>
+        <v>2.412234434175238e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.337964143763239e-05</v>
+        <v>2.337964143763238e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.298617065890878e-05</v>
+        <v>2.298617065890879e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.412234434175236e-05</v>
+        <v>2.412234434175238e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.317200899818129e-05</v>
+        <v>2.317200899818132e-05</v>
       </c>
       <c r="K8" t="n">
         <v>2.34582884871474e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.321841241806183e-05</v>
+        <v>2.283242600165165e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6738,34 +6738,34 @@
         <v>2.405892283816537e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.469160803008355e-05</v>
+        <v>2.469160803008357e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.392434987063846e-05</v>
+        <v>2.392434987063851e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.469160803008355e-05</v>
+        <v>2.469160803008357e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.469160803008355e-05</v>
+        <v>2.469160803008357e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.403454928615804e-05</v>
+        <v>2.403454928615798e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.389925100539818e-05</v>
+        <v>2.389925100539816e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.469160803008355e-05</v>
+        <v>2.469160803008357e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.39738957659514e-05</v>
+        <v>2.397389576595141e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.408996031473566e-05</v>
+        <v>2.408996031473563e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.399335156107539e-05</v>
+        <v>2.383641934609479e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002109417920603681</v>
+        <v>0.0002109417920603678</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002232854615972542</v>
+        <v>0.0002232854615972502</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002821104540841534</v>
+        <v>0.0002821104540841528</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002232854615972542</v>
+        <v>0.0002232854615972502</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002232854615972542</v>
+        <v>0.0002232854615972502</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002280311471395385</v>
+        <v>0.0002280311471395341</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002755624199005064</v>
+        <v>0.0002755624199005057</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002232854615972542</v>
+        <v>0.0002232854615972502</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002845800397415793</v>
+        <v>0.0002845800397415786</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002192191650576925</v>
+        <v>0.0002192191650576918</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002416665141605086</v>
+        <v>0.0002466414804392448</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.393584502329166e-06</v>
+        <v>7.39358450232895e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.676497434442123e-06</v>
+        <v>6.676497434442079e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.393584502329194e-06</v>
+        <v>7.39358450232895e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.736537705793559e-06</v>
+        <v>6.736537705793609e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.736537705793526e-06</v>
+        <v>6.736537705793608e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.328138993006674e-06</v>
+        <v>7.328138993006462e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.393584502329166e-06</v>
+        <v>7.39358450232895e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.119380466463971e-06</v>
+        <v>7.119380466463827e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.393584502329166e-06</v>
+        <v>7.39358450232895e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.393584502329166e-06</v>
+        <v>7.39358450232895e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.393584502329166e-06</v>
+        <v>7.39358450232895e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.454998115619966e-05</v>
+        <v>1.454998115619957e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.423956261786176e-05</v>
+        <v>1.423956261786171e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.467559677310189e-05</v>
+        <v>1.467559677310181e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.403309862828418e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.42835762164331e-05</v>
+        <v>1.428357621643298e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.132155030039545e-05</v>
+        <v>1.448453564687712e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.161441313198262e-05</v>
+        <v>3.161441313198264e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.427577712033453e-05</v>
+        <v>1.427577712033446e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.145264061592902e-05</v>
+        <v>1.503205648362078e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.456049373315229e-05</v>
+        <v>1.456049373315226e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.456357398606309e-05</v>
+        <v>1.456357398606307e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.270305999474908e-05</v>
+        <v>5.270305999474899e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.242885595888395e-05</v>
+        <v>5.242885595888386e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.27028827118079e-05</v>
+        <v>5.270288271180765e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.24304992243272e-05</v>
+        <v>5.243049922432716e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.24304992243272e-05</v>
+        <v>5.243049922432716e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.263761448542659e-05</v>
+        <v>5.263761448542658e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.270305999474908e-05</v>
+        <v>5.270305999474899e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.242885595888395e-05</v>
+        <v>5.242885595888386e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.270305999474908e-05</v>
+        <v>5.270305999474899e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.270305999474908e-05</v>
+        <v>5.270305999474899e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.270305999474908e-05</v>
+        <v>5.270305999474899e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,34 +7011,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000231723321318393</v>
+        <v>0.0002317233213183929</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003751183883304085</v>
+        <v>0.0003751183883304083</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004051470734119373</v>
+        <v>0.0004051470734119369</v>
       </c>
       <c r="E6" t="n">
         <v>0.0003358311312829354</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002360033449011115</v>
+        <v>0.0002360033449011114</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003752970992067672</v>
+        <v>0.0003752970992067671</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003753625447160906</v>
+        <v>0.0003753625447160912</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003750883406802247</v>
+        <v>0.0003750883406802243</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003753907739646347</v>
+        <v>0.0003753907739646344</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002290551489972084</v>
+        <v>0.0002290551489972081</v>
       </c>
       <c r="L6" t="n">
         <v>0.0005254057244949862</v>
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001285084775402479</v>
+        <v>0.0001285084775402477</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001622091658750608</v>
+        <v>0.0001622091658750606</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001624833714509853</v>
+        <v>0.0001624833714509851</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002014154630012762</v>
+        <v>0.0002014154630012761</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001622091581329536</v>
+        <v>0.0001622091581329532</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001624179244016033</v>
+        <v>0.0001624179244016031</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001624833699109262</v>
+        <v>0.0001624833699109258</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001622091658750608</v>
+        <v>0.0001622091658750606</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001624833699109262</v>
+        <v>0.0001624833699109258</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001419995315882524</v>
+        <v>0.000141999531588252</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001624833699109262</v>
+        <v>0.0001624833699109258</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.325590875566808e-05</v>
+        <v>2.325590875566804e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.39883860147279e-05</v>
+        <v>2.398838601472786e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.193661481985267e-05</v>
+        <v>2.19366148198526e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.39883860147279e-05</v>
+        <v>2.398838601472786e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.39883860147279e-05</v>
+        <v>2.398838601472786e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.31708369156449e-05</v>
+        <v>2.317083691564488e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.26873631715192e-05</v>
+        <v>2.268736317151919e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.39883860147279e-05</v>
+        <v>2.398838601472786e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.173180408810712e-05</v>
+        <v>2.173180408810706e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.345537167565314e-05</v>
+        <v>2.345537167565301e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.296247051766399e-05</v>
+        <v>2.309814273171538e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7131,34 +7131,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.407514437967137e-05</v>
+        <v>2.407514437967129e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.471535180074155e-05</v>
+        <v>2.471535180074149e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.353788320553585e-05</v>
+        <v>2.353788320553581e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.471535180074155e-05</v>
+        <v>2.471535180074149e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.471535180074155e-05</v>
+        <v>2.471535180074149e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.401691646150657e-05</v>
+        <v>2.401691646150654e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.384561668727525e-05</v>
+        <v>2.384561668727516e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.471535180074155e-05</v>
+        <v>2.471535180074149e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.345558487993804e-05</v>
+        <v>2.345558487993805e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.415646016169543e-05</v>
+        <v>2.415646016169546e-05</v>
       </c>
       <c r="L9" t="n">
         <v>2.401222727292481e-05</v>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001941739711695786</v>
+        <v>0.000194173971169578</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002095333304772815</v>
+        <v>0.0002095333304772803</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002171313206726979</v>
+        <v>0.0002171313206726944</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002095333304772815</v>
+        <v>0.0002095333304772803</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002095333304772815</v>
+        <v>0.0002095333304772803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001984745725370494</v>
+        <v>0.000198474572537036</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002385427550628069</v>
+        <v>0.0002385427550627798</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002095333304772815</v>
+        <v>0.0002095333304772803</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000197036595767148</v>
+        <v>0.0001970365957671459</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001860683099611697</v>
+        <v>0.0001860683099611692</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002107397655905822</v>
+        <v>0.0001979557948330319</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.03486764017296e-06</v>
+        <v>7.034867640172722e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.306450807557014e-06</v>
+        <v>6.306450807556842e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.03486764017296e-06</v>
+        <v>7.03486764017272e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.354210223090813e-06</v>
+        <v>6.354210223090525e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.35421022309081e-06</v>
+        <v>6.354210223090423e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.969707096879529e-06</v>
+        <v>6.96970709687929e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.03486764017296e-06</v>
+        <v>7.034867640172722e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.762342415526698e-06</v>
+        <v>6.762342415526493e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.03486764017296e-06</v>
+        <v>7.03486764017272e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.03486764017296e-06</v>
+        <v>7.03486764017272e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.03486764017296e-06</v>
+        <v>7.03486764017272e-06</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.45120469489454e-05</v>
+        <v>1.451204694894525e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.421790622804394e-05</v>
+        <v>1.421790622804391e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.456235704194539e-05</v>
+        <v>1.456235704194518e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.40080947756676e-05</v>
+        <v>1.400809477566735e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.424930402743213e-05</v>
+        <v>1.42493040274319e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.213478570967882e-05</v>
+        <v>3.213478570967854e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.228223280406549e-05</v>
+        <v>3.228223280406536e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.192742102832582e-05</v>
+        <v>3.192742102832557e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.226999623467913e-05</v>
+        <v>3.226999623467888e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453319126251817e-05</v>
+        <v>1.453319126251813e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.452711215492481e-05</v>
+        <v>1.452711215492475e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.541733842619663e-05</v>
+        <v>5.541733842619626e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.51448132015504e-05</v>
+        <v>5.514481320155009e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.541716642826105e-05</v>
+        <v>5.541716642826073e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.514536342928421e-05</v>
+        <v>5.514536342928333e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.514536342928421e-05</v>
+        <v>5.514536342928333e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.535217788290324e-05</v>
+        <v>5.535217788290285e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.541733842619663e-05</v>
+        <v>5.541733842619626e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.51448132015504e-05</v>
+        <v>5.514481320155009e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.541733842619663e-05</v>
+        <v>5.541733842619626e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.541733842619663e-05</v>
+        <v>5.541733842619626e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.541733842619663e-05</v>
+        <v>5.541733842619626e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002472057458572657</v>
+        <v>0.0002472057458572649</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000400663367006475</v>
+        <v>0.0004006633670063595</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004327754576178221</v>
+        <v>0.00043277545761782</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003586247179200542</v>
+        <v>0.0003586247179200531</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002518056782828952</v>
+        <v>0.0002518056782828943</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004008397698930182</v>
+        <v>0.0004008397698930176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004009049304363066</v>
+        <v>0.0004009049304363054</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004006324052116655</v>
+        <v>0.0004006324052116632</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004009351367579694</v>
+        <v>0.000400935136757969</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002443507045922373</v>
+        <v>0.0002443507045922359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005614565808715359</v>
+        <v>0.0005614565808715341</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001507301711160758</v>
+        <v>0.0001507301711160745</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001906749515015646</v>
+        <v>0.0001906749515015635</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001909474779827864</v>
+        <v>0.0001909474779827851</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002370848608797499</v>
+        <v>0.0002370848608797493</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001906749437518119</v>
+        <v>0.0001906749437518101</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001908823161829174</v>
+        <v>0.0001908823161829153</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000190947476726211</v>
+        <v>0.0001909474767262106</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001906749515015646</v>
+        <v>0.0001906749515015635</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000190947476726211</v>
+        <v>0.0001909474767262106</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001676454124386589</v>
+        <v>0.0001676454124386579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000190947476726211</v>
+        <v>0.0001909474767262106</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.368806920185123e-05</v>
+        <v>2.368806920185117e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.434095800129638e-05</v>
+        <v>2.434095800129608e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.343913791587823e-05</v>
+        <v>2.343913791587795e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.434095800129638e-05</v>
+        <v>2.434095800129608e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.434095800129638e-05</v>
+        <v>2.434095800129608e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.368040103563585e-05</v>
+        <v>2.368040103563579e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.364645208168204e-05</v>
+        <v>2.364645208168211e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.434095800129638e-05</v>
+        <v>2.434095800129608e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.343458488733119e-05</v>
+        <v>2.343458488733095e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.383990698139244e-05</v>
+        <v>2.383990698139218e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.355874903751902e-05</v>
+        <v>2.355874903751882e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.405235675399702e-05</v>
+        <v>2.405235675399683e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.463904052681524e-05</v>
+        <v>2.463904052681484e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.39509985457324e-05</v>
+        <v>2.395099854573206e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.463904052681524e-05</v>
+        <v>2.463904052681484e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.463904052681524e-05</v>
+        <v>2.463904052681484e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.402626039983871e-05</v>
+        <v>2.402626039983858e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.403623260309037e-05</v>
+        <v>2.403623260309023e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.463904052681524e-05</v>
+        <v>2.463904052681484e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.394953280012772e-05</v>
+        <v>2.394953280012734e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.411423669300439e-05</v>
+        <v>2.411423669300416e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.400041770034141e-05</v>
+        <v>2.398631615306486e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001939647785914966</v>
+        <v>0.0001939647785914961</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002152401579876324</v>
+        <v>0.0002152401579876322</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002176632073446963</v>
+        <v>0.0002176632073446982</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002152401579876324</v>
+        <v>0.0002152401579876322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002152401579876324</v>
+        <v>0.0002152401579876322</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002095060531221388</v>
+        <v>0.0002095060531221372</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002545489321098475</v>
+        <v>0.0002545489321098474</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002152401579876324</v>
+        <v>0.0002152401579876322</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000195977410637209</v>
+        <v>0.0001959774106372087</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00020177193858388</v>
+        <v>0.0002017719385838797</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002302449264612332</v>
+        <v>0.0002131527083021825</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.227929983052644e-06</v>
+        <v>7.227929983052669e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.526183011348155e-06</v>
+        <v>6.526183011348196e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.227929983052644e-06</v>
+        <v>7.227929983052669e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.580072048547063e-06</v>
+        <v>6.580072048547266e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.580072048547038e-06</v>
+        <v>6.580072048547265e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.162770235773621e-06</v>
+        <v>7.162770235773614e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.227929983052644e-06</v>
+        <v>7.227929983052669e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.955496219246468e-06</v>
+        <v>6.955496219246557e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.227929983052644e-06</v>
+        <v>7.227929983052669e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.227929983052644e-06</v>
+        <v>7.227929983052669e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.227929983052644e-06</v>
+        <v>7.227929983052669e-06</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.096389913786888e-05</v>
+        <v>3.096389913786886e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.397153422624137e-05</v>
+        <v>1.397153422624127e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.428176428713698e-05</v>
+        <v>1.428172686646854e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.377272253949297e-05</v>
+        <v>1.377272253949293e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.400587286079978e-05</v>
+        <v>1.40058728607998e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.420314896271986e-05</v>
+        <v>3.089873939058986e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.112994694699661e-05</v>
+        <v>3.112994694699633e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.069146537406278e-05</v>
+        <v>3.069146537406273e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.472405663455847e-05</v>
+        <v>1.472405663455848e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.428830192061589e-05</v>
+        <v>1.428830192061573e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.428054234256378e-05</v>
+        <v>1.428054234256367e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.242393790169343e-05</v>
+        <v>5.242393790169327e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.215150413788745e-05</v>
+        <v>5.215150413788711e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.242376280440708e-05</v>
+        <v>5.242376280440691e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.215390006511613e-05</v>
+        <v>5.215390006511594e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.215390006511613e-05</v>
+        <v>5.215390006511594e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.235877815441442e-05</v>
+        <v>5.235877815441421e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.242393790169343e-05</v>
+        <v>5.242393790169327e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.215150413788745e-05</v>
+        <v>5.215150413788711e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.242393790169343e-05</v>
+        <v>5.242393790169327e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.242393790169343e-05</v>
+        <v>5.242393790169327e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.242393790169343e-05</v>
+        <v>5.242393790169327e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002313217140051108</v>
+        <v>0.0002313217140051106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003745347272245285</v>
+        <v>0.0003745347272245281</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004045227067419653</v>
+        <v>0.0004045227067419656</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003352978611104183</v>
+        <v>0.0003352978611104175</v>
       </c>
       <c r="F6" t="n">
         <v>0.000235598107135482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003747112759329242</v>
+        <v>0.0003747112759329232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003747764356801997</v>
+        <v>0.0003747764356801994</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003745040019163966</v>
+        <v>0.0003745040019163965</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003748046286691402</v>
+        <v>0.0003748046286691394</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002286569688981445</v>
+        <v>0.0002286569688981442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005246268879822684</v>
+        <v>0.0005246268879822674</v>
       </c>
     </row>
     <row r="7">
@@ -7843,13 +7843,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001339431641633195</v>
+        <v>0.0001339431641633196</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001691793746685079</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001694518097603185</v>
+        <v>0.0001694518097603184</v>
       </c>
       <c r="E7" t="n">
         <v>0.000210155589140388</v>
@@ -7858,22 +7858,22 @@
         <v>0.0001691793672203965</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001693866486850349</v>
+        <v>0.0001693866486850347</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000169451808432314</v>
+        <v>0.0001694518084323139</v>
       </c>
       <c r="I7" t="n">
         <v>0.0001691793746685079</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000169451808432314</v>
+        <v>0.0001694518084323139</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001247400866828778</v>
+        <v>0.0001488779610482016</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000169451808432314</v>
+        <v>0.0001694518084323139</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.34498189321642e-05</v>
+        <v>2.344981893216415e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.417113083568106e-05</v>
+        <v>2.417113083568102e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.363621254469104e-05</v>
+        <v>2.363621254469096e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.417113083568106e-05</v>
+        <v>2.417113083568102e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.417113083568106e-05</v>
+        <v>2.417113083568102e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.349714120556535e-05</v>
+        <v>2.349714120556524e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.323378783189226e-05</v>
+        <v>2.32337878318922e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.417113083568106e-05</v>
+        <v>2.417113083568102e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.33340452168658e-05</v>
+        <v>2.333404521686576e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.361622265049845e-05</v>
+        <v>2.361622265049838e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.349711598565969e-05</v>
+        <v>2.349711598565961e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.405912063773681e-05</v>
+        <v>2.405912063773677e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.468619020723889e-05</v>
+        <v>2.46861902072388e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.413506699912061e-05</v>
+        <v>2.413506699912057e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.468619020723889e-05</v>
+        <v>2.46861902072388e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.468619020723889e-05</v>
+        <v>2.46861902072388e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.405537752201428e-05</v>
+        <v>2.405537752201422e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.397250906241177e-05</v>
+        <v>2.397250906241172e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.468619020723889e-05</v>
+        <v>2.46861902072388e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.401249175867167e-05</v>
+        <v>2.401249175867162e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.412695446464389e-05</v>
+        <v>2.412695446464384e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.407929847355598e-05</v>
+        <v>2.407929847355593e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen resource use mineral and metals results.xlsx
+++ b/Results/Hydrogen/hydrogen resource use mineral and metals results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,320 +511,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001935735589870775</v>
+        <v>2.428200492307409e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002040040674436358</v>
+        <v>2.483634623640375e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002000800157511695</v>
+        <v>2.429703163951805e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002040040674436358</v>
+        <v>2.483634623640375e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002040040674436358</v>
+        <v>2.483634623640375e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001933283329190875</v>
+        <v>2.424862908393959e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002123147444838256</v>
+        <v>2.429272140858701e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002040040674436358</v>
+        <v>2.483634623640375e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002051859758543324</v>
+        <v>2.429932665501818e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001880522325361664</v>
+        <v>2.428447202503633e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00021891121983768</v>
+        <v>2.427395992501455e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.009195243562171e-06</v>
+        <v>2.424911030700621e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.237164548629586e-06</v>
+        <v>2.481003727343678e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.009195243562171e-06</v>
+        <v>2.424911030700621e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.290240984330907e-06</v>
+        <v>2.481003727343678e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.290240984330907e-06</v>
+        <v>2.481003727343678e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>6.944075853536668e-06</v>
+        <v>2.42103011095322e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.009195243562171e-06</v>
+        <v>2.424911030700621e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.736972321668516e-06</v>
+        <v>2.481003727343678e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.009195243562171e-06</v>
+        <v>2.424911030700621e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.009195243562171e-06</v>
+        <v>2.424911030700621e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.009195243562171e-06</v>
+        <v>2.424911030700621e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.49760438161368e-05</v>
+        <v>0.0001935735589870791</v>
       </c>
       <c r="C4" t="n">
-        <v>1.468345985084654e-05</v>
+        <v>0.0002040040674436362</v>
       </c>
       <c r="D4" t="n">
-        <v>1.501756062443498e-05</v>
+        <v>0.0002000800157511698</v>
       </c>
       <c r="E4" t="n">
-        <v>1.44615006781585e-05</v>
+        <v>0.0002040040674436362</v>
       </c>
       <c r="F4" t="n">
-        <v>1.471482014424998e-05</v>
+        <v>0.0002040040674436362</v>
       </c>
       <c r="G4" t="n">
-        <v>3.374217107488768e-05</v>
+        <v>0.0001933283329190916</v>
       </c>
       <c r="H4" t="n">
-        <v>3.389714753427678e-05</v>
+        <v>0.0002123147444838261</v>
       </c>
       <c r="I4" t="n">
-        <v>3.353506754301951e-05</v>
+        <v>0.0002040040674436362</v>
       </c>
       <c r="J4" t="n">
-        <v>3.389183659218017e-05</v>
+        <v>0.0002051859758543328</v>
       </c>
       <c r="K4" t="n">
-        <v>1.500520413419415e-05</v>
+        <v>0.0001880522325361666</v>
       </c>
       <c r="L4" t="n">
-        <v>1.499162606565577e-05</v>
+        <v>0.0002189112198376809</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.871822997695717e-05</v>
+        <v>7.009195243562158e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.844600705506353e-05</v>
+        <v>6.237164548629632e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.871807095055637e-05</v>
+        <v>7.009195243562158e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.844522827023928e-05</v>
+        <v>6.29024098433087e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.844522827023928e-05</v>
+        <v>6.29024098433086e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.865311058693173e-05</v>
+        <v>6.94407585353672e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.871822997695717e-05</v>
+        <v>7.009195243562158e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.844600705506353e-05</v>
+        <v>6.736972321668442e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.871822997695717e-05</v>
+        <v>7.009195243562158e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.871822997695717e-05</v>
+        <v>7.009195243562158e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.871822997695717e-05</v>
+        <v>7.009195243562158e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002636158199084475</v>
+        <v>1.497604381613681e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004275866290766056</v>
+        <v>1.468345985084648e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004618773946628716</v>
+        <v>1.501756062443502e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003826729381143045</v>
+        <v>1.446150067815847e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002685484716929765</v>
+        <v>1.471482014425001e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004277619938594055</v>
+        <v>3.374217107488771e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004278271132494311</v>
+        <v>3.389714753427684e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004275548903275373</v>
+        <v>3.353506754301947e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004278593855037418</v>
+        <v>3.389183659218022e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002605655108261053</v>
+        <v>1.500520413419424e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005993595402965971</v>
+        <v>1.499162606565574e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001719121541572035</v>
+        <v>5.871822997695735e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002177523652065944</v>
+        <v>5.844600705506354e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002180245894140144</v>
+        <v>5.87180709505563e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002709651271567176</v>
+        <v>5.844522827023934e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002177523569879736</v>
+        <v>5.844522827023934e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002179594687384625</v>
+        <v>5.865311058693177e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002180245881284881</v>
+        <v>5.871822997695735e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002177523652065944</v>
+        <v>5.844600705506354e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002180245881284881</v>
+        <v>5.871822997695735e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001599608023851115</v>
+        <v>5.871822997695735e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002180245881284881</v>
+        <v>5.871822997695735e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.385573862651371e-05</v>
+        <v>0.0002636158199084477</v>
       </c>
       <c r="C8" t="n">
-        <v>2.432162270134165e-05</v>
+        <v>0.000427586629076606</v>
       </c>
       <c r="D8" t="n">
-        <v>2.354132960877245e-05</v>
+        <v>0.0004618773946628725</v>
       </c>
       <c r="E8" t="n">
-        <v>2.432162270134165e-05</v>
+        <v>0.0003826729381143045</v>
       </c>
       <c r="F8" t="n">
-        <v>2.432162270134165e-05</v>
+        <v>0.0002685484716929766</v>
       </c>
       <c r="G8" t="n">
-        <v>2.370689737389595e-05</v>
+        <v>0.0004277619938594063</v>
       </c>
       <c r="H8" t="n">
-        <v>2.364781919033467e-05</v>
+        <v>0.0004278271132494315</v>
       </c>
       <c r="I8" t="n">
-        <v>2.432162270134165e-05</v>
+        <v>0.0004275548903275378</v>
       </c>
       <c r="J8" t="n">
-        <v>2.350067514567034e-05</v>
+        <v>0.0004278593855037423</v>
       </c>
       <c r="K8" t="n">
-        <v>2.380481646432694e-05</v>
+        <v>0.0002605655108261053</v>
       </c>
       <c r="L8" t="n">
-        <v>2.40317474301352e-05</v>
+        <v>0.0005993595402965981</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001719121541572037</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0002177523652065945</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0002180245894140148</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002709651271567177</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.000217752356987974</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0002179594687384628</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0002180245881284884</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0002177523652065945</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0002180245881284884</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001599608023851118</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002180245881284884</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.385573862651369e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.432162270134166e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.354132960877252e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.432162270134166e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.432162270134166e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.370689737389589e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.364781919033466e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.432162270134166e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.35006751456704e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.380481646432696e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.403174743013522e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.410301955484884e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.461411604961558e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.397498916625843e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.461411604961558e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.461411604961558e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.401957877997247e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.401913203430039e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.461411604961558e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.395878627148902e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.408231691073672e-05</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>2.41030195548488e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.461411604961561e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.397498916625837e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.461411604961561e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.461411604961561e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.401957877997253e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.401913203430034e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.461411604961561e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.395878627148903e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.408231691073675e-05</v>
+      </c>
+      <c r="L11" t="n">
         <v>2.400828182235043e-05</v>
       </c>
     </row>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002026894475674553</v>
+        <v>2.463518055125755e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002242094844414574</v>
+        <v>2.52370059098362e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002509936864833095</v>
+        <v>2.467247460615195e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002242094844414574</v>
+        <v>2.52370059098362e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002242094844414574</v>
+        <v>2.52370059098362e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002169713003079398</v>
+        <v>2.460146013921297e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002608802603758058</v>
+        <v>2.466943873293696e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002242094844414574</v>
+        <v>2.52370059098362e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002420478535739984</v>
+        <v>2.4685309328922e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000212773076872718</v>
+        <v>2.462960411366615e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002478418725875169</v>
+        <v>2.466065559150282e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.373115638525164e-06</v>
+        <v>2.457190710970657e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.67419202350897e-06</v>
+        <v>2.518024689264543e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.373115638525164e-06</v>
+        <v>2.457190710970657e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.732292372054242e-06</v>
+        <v>2.518024689264543e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.732292372054168e-06</v>
+        <v>2.518024689264543e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.308014120496081e-06</v>
+        <v>2.453292233301738e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.373115638525164e-06</v>
+        <v>2.457190710970657e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.101096945605109e-06</v>
+        <v>2.518024689264543e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.373115638525164e-06</v>
+        <v>2.457190710970657e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.373115638525164e-06</v>
+        <v>2.457190710970657e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.373115638525164e-06</v>
+        <v>2.457190710970657e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.448684823134626e-05</v>
+        <v>0.0002026894475674547</v>
       </c>
       <c r="C4" t="n">
-        <v>1.419750503446345e-05</v>
+        <v>0.0002242094844414573</v>
       </c>
       <c r="D4" t="n">
-        <v>3.153875109644866e-05</v>
+        <v>0.0002509936864833094</v>
       </c>
       <c r="E4" t="n">
-        <v>1.399370246527444e-05</v>
+        <v>0.0002242094844414573</v>
       </c>
       <c r="F4" t="n">
-        <v>1.422951514774211e-05</v>
+        <v>0.0002242094844414573</v>
       </c>
       <c r="G4" t="n">
-        <v>3.122324091128107e-05</v>
+        <v>0.000216971300307947</v>
       </c>
       <c r="H4" t="n">
-        <v>3.150185212541438e-05</v>
+        <v>0.0002608802603758053</v>
       </c>
       <c r="I4" t="n">
-        <v>1.421482953842628e-05</v>
+        <v>0.0002242094844414573</v>
       </c>
       <c r="J4" t="n">
-        <v>1.496112608407591e-05</v>
+        <v>0.0002420478535739978</v>
       </c>
       <c r="K4" t="n">
-        <v>1.449830216340397e-05</v>
+        <v>0.0002127730768727179</v>
       </c>
       <c r="L4" t="n">
-        <v>1.450863744538362e-05</v>
+        <v>0.0002478418725875169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.264659396673e-05</v>
+        <v>7.373115638524934e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.237457527380983e-05</v>
+        <v>6.674192023508935e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.264641483547737e-05</v>
+        <v>7.373115638524934e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.237887593478675e-05</v>
+        <v>6.732292372054035e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.237887593478676e-05</v>
+        <v>6.732292372054036e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.258149244870092e-05</v>
+        <v>7.308014120495881e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.264659396673e-05</v>
+        <v>7.373115638524934e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.237457527380983e-05</v>
+        <v>7.1010969456049e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.264659396673e-05</v>
+        <v>7.373115638524934e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.264659396673e-05</v>
+        <v>7.373115638524934e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.264659396673e-05</v>
+        <v>7.373115638524934e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002316358188573543</v>
+        <v>1.44868482313462e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003749825714245897</v>
+        <v>1.419750503446338e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004049955411668788</v>
+        <v>3.15387510964486e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003357095489115581</v>
+        <v>1.399370246527439e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002359179330855706</v>
+        <v>1.422951514774202e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003751569076989227</v>
+        <v>3.122324091128096e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003752220092169499</v>
+        <v>3.150185212541404e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003749499905240316</v>
+        <v>1.421482953842616e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003752502280430828</v>
+        <v>1.496112608407585e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002289686316520698</v>
+        <v>1.44983021634039e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005252097915530959</v>
+        <v>1.450863744538355e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001283129392820628</v>
+        <v>5.264659396672998e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001619628525312573</v>
+        <v>5.237457527380991e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001622348725261557</v>
+        <v>5.264641483547734e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002011080342756397</v>
+        <v>5.237887593478675e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001619628448251544</v>
+        <v>5.237887593478675e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000162169769706148</v>
+        <v>5.258149244870087e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001622348712241773</v>
+        <v>5.264659396672998e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001619628525312573</v>
+        <v>5.237457527380991e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001622348712241773</v>
+        <v>5.264659396672998e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000142580371182814</v>
+        <v>5.264659396672998e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001622348712241773</v>
+        <v>5.264659396672998e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.347016982471871e-05</v>
+        <v>0.0002316358188573542</v>
       </c>
       <c r="C8" t="n">
-        <v>2.396737767583463e-05</v>
+        <v>0.0003749825714245897</v>
       </c>
       <c r="D8" t="n">
-        <v>2.268968697791862e-05</v>
+        <v>0.0004049955411668781</v>
       </c>
       <c r="E8" t="n">
-        <v>2.396737767583463e-05</v>
+        <v>0.0003357095489115574</v>
       </c>
       <c r="F8" t="n">
-        <v>2.396737767583463e-05</v>
+        <v>0.0002359179330855699</v>
       </c>
       <c r="G8" t="n">
-        <v>2.332815850080943e-05</v>
+        <v>0.0003751569076989218</v>
       </c>
       <c r="H8" t="n">
-        <v>2.279181874624589e-05</v>
+        <v>0.0003752220092169499</v>
       </c>
       <c r="I8" t="n">
-        <v>2.396737767583463e-05</v>
+        <v>0.0003749499905240309</v>
       </c>
       <c r="J8" t="n">
-        <v>2.243854172357465e-05</v>
+        <v>0.0003752502280430831</v>
       </c>
       <c r="K8" t="n">
-        <v>2.35884397150807e-05</v>
+        <v>0.0002289686316520697</v>
       </c>
       <c r="L8" t="n">
-        <v>2.285449295959973e-05</v>
+        <v>0.0005252097915530953</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001283129392820626</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001619628525312568</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001622348725261559</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002011080342756391</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001619628448251548</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001621697697061479</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001622348712241771</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001619628525312568</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001622348712241771</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001425803711828135</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001622348712241771</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.347016982471876e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.396737767583458e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.268968697791867e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.396737767583458e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.396737767583458e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.332815850080949e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.279181874624596e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.396737767583458e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.243854172357469e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.358843971508075e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.285449295959982e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.413388657555963e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.468514655100243e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.381605844790871e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.468514655100243e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.468514655100243e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.40532887562038e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.385949285475729e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.468514655100243e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.371462127959985e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.418212331498676e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.388461267592059e-05</v>
+      <c r="B11" t="n">
+        <v>2.41338865755597e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.468514655100239e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.381605844790879e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.468514655100239e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.468514655100239e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.405328875620385e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.385949285475737e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.468514655100239e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.371462127959987e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.418212331498677e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.388461267592063e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.48737438463138e-05</v>
+        <v>2.310642257926358e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001837381753976418</v>
+        <v>2.401817330265157e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000210363424579523</v>
+        <v>2.458498313592028e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001996662267368503</v>
+        <v>2.515399072702911e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001996662267368503</v>
+        <v>2.515399072702911e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001950318933652924</v>
+        <v>2.529174824645859e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002488412807092175</v>
+        <v>2.460631617767563e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001996662267368503</v>
+        <v>2.515399072702911e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001804002696949416</v>
+        <v>2.567581527317248e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001857923905799875</v>
+        <v>2.567777667149796e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002059483571032892</v>
+        <v>2.510150451686907e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.772792968808402e-06</v>
+        <v>2.307196488050572e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.717567924689485e-06</v>
+        <v>2.396631152009835e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.772792968808358e-06</v>
+        <v>2.450645020156049e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.012422048455733e-06</v>
+        <v>2.510013168828172e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.012422048455729e-06</v>
+        <v>2.510013168828172e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.706586888089337e-06</v>
+        <v>2.524367354562993e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.772792968808405e-06</v>
+        <v>2.450645020156049e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.494319255459681e-06</v>
+        <v>2.510013168828172e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.772792968808405e-06</v>
+        <v>2.565399075404671e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.772792968808358e-06</v>
+        <v>2.564466200336115e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.772792968808358e-06</v>
+        <v>2.505606821149914e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.297101029389283e-05</v>
+        <v>5.487374384631384e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.460911138497509e-05</v>
+        <v>0.0001837381753976424</v>
       </c>
       <c r="D4" t="n">
-        <v>1.503052610080571e-05</v>
+        <v>0.0002103634245795257</v>
       </c>
       <c r="E4" t="n">
-        <v>1.447375519395879e-05</v>
+        <v>0.0001996662267368518</v>
       </c>
       <c r="F4" t="n">
-        <v>1.472259446570144e-05</v>
+        <v>0.0001996662267368518</v>
       </c>
       <c r="G4" t="n">
-        <v>1.49199316912705e-05</v>
+        <v>0.0001950318933652993</v>
       </c>
       <c r="H4" t="n">
-        <v>3.417369431215769e-05</v>
+        <v>0.0002488412807092226</v>
       </c>
       <c r="I4" t="n">
-        <v>1.470766405864128e-05</v>
+        <v>0.0001996662267368518</v>
       </c>
       <c r="J4" t="n">
-        <v>3.327869733207858e-05</v>
+        <v>0.0001804002696949427</v>
       </c>
       <c r="K4" t="n">
-        <v>1.499690876896669e-05</v>
+        <v>0.0001857923905799879</v>
       </c>
       <c r="L4" t="n">
-        <v>1.499980339580083e-05</v>
+        <v>0.0002059483571032895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.612545906410925e-05</v>
+        <v>7.772792968808234e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.583905353821129e-05</v>
+        <v>6.717567924689599e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.612543033442469e-05</v>
+        <v>7.772792968808234e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.584721932500754e-05</v>
+        <v>7.012422048455716e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.584721932500754e-05</v>
+        <v>7.01242204845574e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.605925298338999e-05</v>
+        <v>7.706586888089017e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.612545906410925e-05</v>
+        <v>7.772792968808234e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.584698535076077e-05</v>
+        <v>7.494319255459711e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.612545906410925e-05</v>
+        <v>7.772792968808234e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.612545906410925e-05</v>
+        <v>7.772792968808234e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.612545906410925e-05</v>
+        <v>7.772792968808234e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457835089929894</v>
+        <v>3.297101029389304e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000398131698576999</v>
+        <v>1.460911138497517e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004300313017741981</v>
+        <v>1.503052610080576e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000356400501888275</v>
+        <v>1.447375519395889e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002503425125749645</v>
+        <v>1.472259446570163e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003983216004685032</v>
+        <v>1.491993169127059e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003983878065492793</v>
+        <v>3.417369431215761e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003981093328358739</v>
+        <v>1.470766405864136e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003984177976934845</v>
+        <v>3.327869733207869e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002429488058164025</v>
+        <v>1.499690876896677e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005577957559360687</v>
+        <v>1.49998033958009e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001504740734113478</v>
+        <v>5.61254590641095e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001902509210503251</v>
+        <v>5.58390535382113e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001905373285113472</v>
+        <v>5.612543033442483e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002364909897675136</v>
+        <v>5.584721932500777e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001902588452478824</v>
+        <v>5.584721932500777e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001904711204955041</v>
+        <v>5.605925298339006e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001905373265762233</v>
+        <v>5.61254590641095e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001902588528628744</v>
+        <v>5.584698535076084e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001905373265762233</v>
+        <v>5.61254590641095e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001673245211658602</v>
+        <v>5.61254590641095e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001905373265762234</v>
+        <v>5.61254590641095e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.247154246741569e-05</v>
+        <v>0.0002457835089929887</v>
       </c>
       <c r="C8" t="n">
-        <v>2.328514793911327e-05</v>
+        <v>0.0003981316985769994</v>
       </c>
       <c r="D8" t="n">
-        <v>2.313359994991288e-05</v>
+        <v>0.0004300313017741979</v>
       </c>
       <c r="E8" t="n">
-        <v>2.399793153413447e-05</v>
+        <v>0.0003564005018882749</v>
       </c>
       <c r="F8" t="n">
-        <v>2.399793153413447e-05</v>
+        <v>0.0002503425125749641</v>
       </c>
       <c r="G8" t="n">
-        <v>2.425962834643521e-05</v>
+        <v>0.0003983216004685029</v>
       </c>
       <c r="H8" t="n">
-        <v>2.272535501200993e-05</v>
+        <v>0.0003983878065492785</v>
       </c>
       <c r="I8" t="n">
-        <v>2.399793153413447e-05</v>
+        <v>0.0003981093328358742</v>
       </c>
       <c r="J8" t="n">
-        <v>2.50991719214955e-05</v>
+        <v>0.0003984177976934833</v>
       </c>
       <c r="K8" t="n">
-        <v>2.485067655947616e-05</v>
+        <v>0.0002429488058164023</v>
       </c>
       <c r="L8" t="n">
-        <v>2.421399040944306e-05</v>
+        <v>0.0005577957559360671</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001504740734113483</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001902509210503255</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001905373285113472</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002364909897675142</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001902588452478832</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001904711204955041</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001905373265762234</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001902588528628751</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001905373265762234</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001673245211658606</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001905373265762234</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.24715424674157e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.328514793911328e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.313359994991286e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.399793153413445e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.399793153413444e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.425962834643503e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.272535501200985e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.399793153413445e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.509917192149575e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.485067655947634e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.42139904094431e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.283322846787495e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.37082417025638e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.396033189640641e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.46524861443886e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.46524861443886e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.484400454485887e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.379591219041641e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.46524861443886e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.542337093625878e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.531651076424873e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.47183564333909e-05</v>
+      <c r="B11" t="n">
+        <v>2.283322846787493e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.370824170256381e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.39603318964064e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.465248614438865e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.465248614438865e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.484400454485889e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.379591219041645e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.465248614438865e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.542337093625881e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.531651076424889e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.471835643339087e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.441859923284899e-05</v>
+        <v>2.321025155870203e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001914971352138085</v>
+        <v>2.413151884422709e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002144240329414866</v>
+        <v>2.480921486734053e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002063480669593083</v>
+        <v>2.534161603726669e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002063480669593083</v>
+        <v>2.534161603726669e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002002365037494212</v>
+        <v>2.53641617096745e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002553818069768233</v>
+        <v>2.483354873310069e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002063480669593083</v>
+        <v>2.534161603726669e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001739040493052596</v>
+        <v>2.589453824741514e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001887912903729795</v>
+        <v>2.576520536350844e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002107352647795446</v>
+        <v>2.522816371161189e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.989837725524054e-06</v>
+        <v>2.316294103783587e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.91670630690138e-06</v>
+        <v>2.406109317616976e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.989837725524049e-06</v>
+        <v>2.471614449477437e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.263185167352276e-06</v>
+        <v>2.527036951925818e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.263185167352275e-06</v>
+        <v>2.527036951925818e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.923530598183078e-06</v>
+        <v>2.529918202014734e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.989837725524049e-06</v>
+        <v>2.471614449477437e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.710885607556821e-06</v>
+        <v>2.527036951925818e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.989837725524054e-06</v>
+        <v>2.587257717671807e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.989837725524049e-06</v>
+        <v>2.571822160364976e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.989837725524049e-06</v>
+        <v>2.516822442421675e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.217663676942667e-05</v>
+        <v>6.441859923284895e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.455718405518796e-05</v>
+        <v>0.0001914971352138084</v>
       </c>
       <c r="D4" t="n">
-        <v>3.273208706570838e-05</v>
+        <v>0.0002144240329414866</v>
       </c>
       <c r="E4" t="n">
-        <v>1.443406995913407e-05</v>
+        <v>0.0002063480669593086</v>
       </c>
       <c r="F4" t="n">
-        <v>1.468164059692747e-05</v>
+        <v>0.0002063480669593086</v>
       </c>
       <c r="G4" t="n">
-        <v>3.211032964208547e-05</v>
+        <v>0.0002002365037494083</v>
       </c>
       <c r="H4" t="n">
-        <v>3.380508330664245e-05</v>
+        <v>0.0002553818069768227</v>
       </c>
       <c r="I4" t="n">
-        <v>1.466442807610779e-05</v>
+        <v>0.0002063480669593086</v>
       </c>
       <c r="J4" t="n">
-        <v>1.540836900313124e-05</v>
+        <v>0.0001739040493052592</v>
       </c>
       <c r="K4" t="n">
-        <v>1.494534434225299e-05</v>
+        <v>0.0001887912903729795</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49559171396643e-05</v>
+        <v>0.0002107352647795445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.385103823788092e-05</v>
+        <v>7.98983772552389e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.35640805319764e-05</v>
+        <v>6.916706306901373e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.385102508882498e-05</v>
+        <v>7.98983772552389e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.357805061668038e-05</v>
+        <v>7.263185167352142e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.357805061668038e-05</v>
+        <v>7.263185167352116e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.378473111053971e-05</v>
+        <v>7.923530598182989e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.385103823788092e-05</v>
+        <v>7.98983772552389e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.35720861199135e-05</v>
+        <v>7.710885607556802e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.385103823788092e-05</v>
+        <v>7.98983772552389e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.385103823788092e-05</v>
+        <v>7.98983772552389e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.385103823788092e-05</v>
+        <v>7.98983772552389e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002337983606782209</v>
+        <v>3.217663676942642e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003783661378741208</v>
+        <v>1.455718405518798e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004086483394083597</v>
+        <v>3.273208706570829e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003387633946298119</v>
+        <v>1.443406995913414e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002381135608550358</v>
+        <v>1.468164059692746e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003785525573901409</v>
+        <v>3.211032964208543e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003786188645176482</v>
+        <v>3.380508330664222e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003783399123995144</v>
+        <v>1.466442807610783e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003786473259211811</v>
+        <v>1.540836900313119e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002311082454662116</v>
+        <v>1.494534434225297e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005298959904951557</v>
+        <v>1.49559171396643e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001358654933365099</v>
+        <v>5.38510382378807e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001715283412897267</v>
+        <v>5.356408053197655e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001718153011602753</v>
+        <v>5.385102508882484e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002130216532042647</v>
+        <v>5.35780506166803e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000171536339596226</v>
+        <v>5.35780506166803e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001717489918682899</v>
+        <v>5.378473111053963e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001718152989956317</v>
+        <v>5.38510382378807e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000171536346877664</v>
+        <v>5.357208611991341e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001718152989956317</v>
+        <v>5.38510382378807e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001509858413213927</v>
+        <v>5.38510382378807e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001718152989956317</v>
+        <v>5.38510382378807e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.228276766715812e-05</v>
+        <v>0.0002337983606782207</v>
       </c>
       <c r="C8" t="n">
-        <v>2.297969864705031e-05</v>
+        <v>0.0003783661378741204</v>
       </c>
       <c r="D8" t="n">
-        <v>2.298817098237012e-05</v>
+        <v>0.0004086483394083596</v>
       </c>
       <c r="E8" t="n">
-        <v>2.376664638398833e-05</v>
+        <v>0.0003387633946298114</v>
       </c>
       <c r="F8" t="n">
-        <v>2.376664638398833e-05</v>
+        <v>0.0002381135608550356</v>
       </c>
       <c r="G8" t="n">
-        <v>2.396246766598478e-05</v>
+        <v>0.0003785525573901402</v>
       </c>
       <c r="H8" t="n">
-        <v>2.252485794675115e-05</v>
+        <v>0.0003786188645176479</v>
       </c>
       <c r="I8" t="n">
-        <v>2.376664638398833e-05</v>
+        <v>0.0003783399123995144</v>
       </c>
       <c r="J8" t="n">
-        <v>2.526185407683776e-05</v>
+        <v>0.0003786473259211816</v>
       </c>
       <c r="K8" t="n">
-        <v>2.462794024727068e-05</v>
+        <v>0.0002311082454662112</v>
       </c>
       <c r="L8" t="n">
-        <v>2.400886845866942e-05</v>
+        <v>0.0005298959904951557</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001358654933365096</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001715283412897272</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001718153011602747</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002130216532042646</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001715363395962257</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001717489918682898</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001718152989956311</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001715363468776641</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001718152989956311</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001509858413213925</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001718152989956311</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.228276766715803e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.297969864705032e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.298817098236999e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.376664638398828e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.376664638398828e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.396246766598504e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.252485794675109e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.376664638398828e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.526185407683758e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.462794024727038e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.400886845866932e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.280976987009756e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.363948088727788e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.402298141247176e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.465741721863756e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.465741721863756e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.475595241867487e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.383650637053431e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.465741721863756e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.561665729071067e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.526912387183572e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.470065305263971e-05</v>
+      <c r="B11" t="n">
+        <v>2.28097698700975e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.363948088727786e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.402298141247161e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.465741721863748e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.465741721863748e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.47559524186747e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.383650637053428e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.465741721863748e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.561665729071064e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.526912387183537e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.470065305263961e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.070180831158737e-05</v>
+        <v>2.332472831534668e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002019928830689154</v>
+        <v>2.426009045561374e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002230597720151986</v>
+        <v>2.507277840389147e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002132652479684896</v>
+        <v>2.553749756413016e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002132652479684896</v>
+        <v>2.553749756413016e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002093530857426979</v>
+        <v>2.544161542713033e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002618203328689711</v>
+        <v>2.509383357018483e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002132652479684896</v>
+        <v>2.553749756413016e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001797530578559327</v>
+        <v>2.624771402266048e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000195360630969196</v>
+        <v>2.5727736591394e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002264338492188939</v>
+        <v>2.54346466282662e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.462572046443045e-06</v>
+        <v>2.327134638300513e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.318217761990365e-06</v>
+        <v>2.4178929936465e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>8.462572046443072e-06</v>
+        <v>2.497304214041381e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.736305826806987e-06</v>
+        <v>2.546065693260332e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.736305826807016e-06</v>
+        <v>2.546065693260332e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.396031998872799e-06</v>
+        <v>2.536671685486691e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.462572046443072e-06</v>
+        <v>2.497304214041381e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.182320976082529e-06</v>
+        <v>2.546065693260332e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.462572046443072e-06</v>
+        <v>2.622409071286757e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.462572046443072e-06</v>
+        <v>2.567177108820663e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.462572046443072e-06</v>
+        <v>2.536098609452301e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.545931168409707e-05</v>
+        <v>7.07018083115875e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.505655270402008e-05</v>
+        <v>0.0002019928830689157</v>
       </c>
       <c r="D4" t="n">
-        <v>1.549389131096212e-05</v>
+        <v>0.0002230597720151989</v>
       </c>
       <c r="E4" t="n">
-        <v>1.493129140382014e-05</v>
+        <v>0.0002132652479684896</v>
       </c>
       <c r="F4" t="n">
-        <v>1.519702450936226e-05</v>
+        <v>0.0002132652479684896</v>
       </c>
       <c r="G4" t="n">
-        <v>3.290339767368999e-05</v>
+        <v>0.0002093530857426957</v>
       </c>
       <c r="H4" t="n">
-        <v>3.507755790383012e-05</v>
+        <v>0.0002618203328689715</v>
       </c>
       <c r="I4" t="n">
-        <v>3.26896866508996e-05</v>
+        <v>0.0002132652479684896</v>
       </c>
       <c r="J4" t="n">
-        <v>3.340316363659413e-05</v>
+        <v>0.0001797530578559327</v>
       </c>
       <c r="K4" t="n">
-        <v>1.545376441671923e-05</v>
+        <v>0.0001953606309691961</v>
       </c>
       <c r="L4" t="n">
-        <v>1.547331314667217e-05</v>
+        <v>0.000226433849218894</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.456736747643024e-05</v>
+        <v>8.462572046443221e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.427978421170289e-05</v>
+        <v>7.318217761990431e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.456735859554189e-05</v>
+        <v>8.462572046443221e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.429756875587578e-05</v>
+        <v>7.736305826807213e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.429756875587578e-05</v>
+        <v>7.736305826807235e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.450082742885987e-05</v>
+        <v>8.396031998872795e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.456736747643024e-05</v>
+        <v>8.462572046443221e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.428711640606956e-05</v>
+        <v>8.182320976082643e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.456736747643024e-05</v>
+        <v>8.462572046443221e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.456736747643024e-05</v>
+        <v>8.462572046443221e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.456736747643024e-05</v>
+        <v>8.462572046443221e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002349019307757334</v>
+        <v>1.54593116840973e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003799725106802214</v>
+        <v>1.505655270402025e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004103544203820692</v>
+        <v>1.549389131096235e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003402321380684156</v>
+        <v>1.493129140382042e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002392343252554359</v>
+        <v>1.519702450936253e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003801549276774692</v>
+        <v>3.290339767369026e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003802214677252964</v>
+        <v>3.507755790383059e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003799412166546787</v>
+        <v>3.268968665090004e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003802500272022768</v>
+        <v>3.340316363659451e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000232202545767428</v>
+        <v>1.545376441671985e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005320198755143483</v>
+        <v>1.547331314667234e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001305205635803972</v>
+        <v>5.456736747643046e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001646166261498888</v>
+        <v>5.427978421170306e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001649042119687618</v>
+        <v>5.456735859554206e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002043019498310498</v>
+        <v>5.429756875587609e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001646239510932787</v>
+        <v>5.429756875587609e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001648376693670456</v>
+        <v>5.450082742886009e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001649042094146162</v>
+        <v>5.456736747643046e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001646239583442553</v>
+        <v>5.428711640606974e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001649042094146162</v>
+        <v>5.456736747643046e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001441739295038859</v>
+        <v>5.456736747643046e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001649042094146162</v>
+        <v>5.456736747643046e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.225131904037644e-05</v>
+        <v>0.0002349019307757341</v>
       </c>
       <c r="C8" t="n">
-        <v>2.285731098958348e-05</v>
+        <v>0.0003799725106802217</v>
       </c>
       <c r="D8" t="n">
-        <v>2.304361864344332e-05</v>
+        <v>0.0004103544203820684</v>
       </c>
       <c r="E8" t="n">
-        <v>2.379901718291017e-05</v>
+        <v>0.0003402321380684161</v>
       </c>
       <c r="F8" t="n">
-        <v>2.379901718291017e-05</v>
+        <v>0.0002392343252554363</v>
       </c>
       <c r="G8" t="n">
-        <v>2.382309349740362e-05</v>
+        <v>0.0003801549276774689</v>
       </c>
       <c r="H8" t="n">
-        <v>2.265147194069716e-05</v>
+        <v>0.0003802214677252958</v>
       </c>
       <c r="I8" t="n">
-        <v>2.379901718291017e-05</v>
+        <v>0.000379941216654679</v>
       </c>
       <c r="J8" t="n">
-        <v>2.548671077331427e-05</v>
+        <v>0.000380250027202277</v>
       </c>
       <c r="K8" t="n">
-        <v>2.443109674420178e-05</v>
+        <v>0.0002322025457674284</v>
       </c>
       <c r="L8" t="n">
-        <v>2.387863418888504e-05</v>
+        <v>0.0005320198755143487</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001305205635803973</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001646166261498893</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001649042119687623</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002043019498310503</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001646239510932792</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001648376693670463</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001649042094146165</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001646239583442559</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001649042094146165</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001441739295038864</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001649042094146165</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.225131904037646e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.285731098958348e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.304361864344333e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.379901718291012e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.379901718291012e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.382309349740368e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.26514719406972e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.379901718291012e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.548671077331438e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.443109674420227e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.387863418888505e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.286061262381633e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.365874962303297e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.419488456406203e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.478144618268809e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.478144618268809e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.473926188024875e-05</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>2.286061262381635e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.3658749623033e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.419488456406205e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.478144618268805e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.478144618268805e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.473926188024877e-05</v>
+      </c>
+      <c r="H11" t="n">
         <v>2.403751173090854e-05</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.478144618268809e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.591220380027324e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.516322581107697e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.476017178722567e-05</v>
+      <c r="I11" t="n">
+        <v>2.478144618268805e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.59122038002733e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.51632258110774e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.476017178722569e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,320 +2891,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.904731031296657e-05</v>
+        <v>2.562924972696415e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001973139772697765</v>
+        <v>2.407218954925474e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002353398729773579</v>
+        <v>2.464935398081488e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002140535341067183</v>
+        <v>2.520158981295615e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002140535341067183</v>
+        <v>2.520158981295615e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002110948963313922</v>
+        <v>2.557057269075948e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000259783094598562</v>
+        <v>2.465398885402933e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002140535341067183</v>
+        <v>2.520158981295615e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002001576616681829</v>
+        <v>2.568183847774085e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001939069554095046</v>
+        <v>2.580623368175374e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002229212460156788</v>
+        <v>2.510984073401764e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.777053384210213e-06</v>
+        <v>2.56193214691031e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.727691656801604e-06</v>
+        <v>2.400620391751927e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.777053384210213e-06</v>
+        <v>2.454373118760783e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.048573225549359e-06</v>
+        <v>2.513238378746494e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.048573225549358e-06</v>
+        <v>2.513238378746494e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.710666395539202e-06</v>
+        <v>2.550925843658944e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.777053384210213e-06</v>
+        <v>2.454373118760783e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.497359736888507e-06</v>
+        <v>2.513238378746494e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.777053384210213e-06</v>
+        <v>2.563879794101123e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.777053384210213e-06</v>
+        <v>2.576597754828066e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.777053384210213e-06</v>
+        <v>2.504769649340271e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.509762386104538e-05</v>
+        <v>6.904731031296664e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.471846729238233e-05</v>
+        <v>0.0001973139772697774</v>
       </c>
       <c r="D4" t="n">
-        <v>1.516197446623038e-05</v>
+        <v>0.000235339872977358</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458637758947248e-05</v>
+        <v>0.0002140535341067216</v>
       </c>
       <c r="F4" t="n">
-        <v>1.48348046167775e-05</v>
+        <v>0.0002140535341067216</v>
       </c>
       <c r="G4" t="n">
-        <v>1.503123687237441e-05</v>
+        <v>0.0002110948963313855</v>
       </c>
       <c r="H4" t="n">
-        <v>3.429843035957232e-05</v>
+        <v>0.0002597830945985645</v>
       </c>
       <c r="I4" t="n">
-        <v>3.282598110545379e-05</v>
+        <v>0.0002140535341067216</v>
       </c>
       <c r="J4" t="n">
-        <v>1.558464458946873e-05</v>
+        <v>0.0002001576616681826</v>
       </c>
       <c r="K4" t="n">
-        <v>1.509310060115633e-05</v>
+        <v>0.0001939069554095051</v>
       </c>
       <c r="L4" t="n">
-        <v>1.511161695920536e-05</v>
+        <v>0.0002229212460156788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.604578562860035e-05</v>
+        <v>7.777053384210239e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.575924644451267e-05</v>
+        <v>6.727691656801602e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.604575559153614e-05</v>
+        <v>7.777053384210239e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.577552232021443e-05</v>
+        <v>7.048573225548975e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.577552232021443e-05</v>
+        <v>7.048573225549027e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.597939863992944e-05</v>
+        <v>7.7106663955391e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.604578562860035e-05</v>
+        <v>7.777053384210239e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.576609198127868e-05</v>
+        <v>7.497359736888504e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.604578562860035e-05</v>
+        <v>7.777053384210239e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.604578562860035e-05</v>
+        <v>7.777053384210239e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.604578562860035e-05</v>
+        <v>7.777053384210239e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457295894786855</v>
+        <v>1.509762386104546e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003980159365110328</v>
+        <v>1.47184672924014e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004298922814344916</v>
+        <v>1.516197446623044e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003563020038142292</v>
+        <v>1.45863775894725e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002502906257109219</v>
+        <v>1.483480461677752e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00039819701479654</v>
+        <v>1.50312368723745e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003982634017852653</v>
+        <v>3.429843035957234e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000397983708137889</v>
+        <v>3.282598110545382e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003982933790771438</v>
+        <v>1.558464458946878e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002428961956017978</v>
+        <v>1.509310060115633e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005575977234348921</v>
+        <v>1.511161695920538e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001508580476521695</v>
+        <v>5.604578562860037e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000190725184149939</v>
+        <v>5.575924644451271e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001910117255375441</v>
+        <v>5.604575559153621e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002370685124299281</v>
+        <v>5.577552232021451e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001907320220146186</v>
+        <v>5.577552232021451e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001909453363453562</v>
+        <v>5.597939863992931e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001910117233340271</v>
+        <v>5.604578562860037e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001907320296867053</v>
+        <v>5.576609198127882e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001910117233340269</v>
+        <v>5.604578562860037e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001677465268750932</v>
+        <v>5.604578562860037e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001910117233340269</v>
+        <v>5.604578562860037e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.470317080570988e-05</v>
+        <v>0.0002457295894786856</v>
       </c>
       <c r="C8" t="n">
-        <v>2.302162718945216e-05</v>
+        <v>0.0003980159365110322</v>
       </c>
       <c r="D8" t="n">
-        <v>2.259543214190583e-05</v>
+        <v>0.000429892281434492</v>
       </c>
       <c r="E8" t="n">
-        <v>2.370279827026803e-05</v>
+        <v>0.0003563020038142289</v>
       </c>
       <c r="F8" t="n">
-        <v>2.370279827026803e-05</v>
+        <v>0.0002502906257109221</v>
       </c>
       <c r="G8" t="n">
-        <v>2.416662044128443e-05</v>
+        <v>0.0003981970147965391</v>
       </c>
       <c r="H8" t="n">
-        <v>2.25412183425902e-05</v>
+        <v>0.0003982634017852648</v>
       </c>
       <c r="I8" t="n">
-        <v>2.370279827026803e-05</v>
+        <v>0.0003979837081378887</v>
       </c>
       <c r="J8" t="n">
-        <v>2.465218969266414e-05</v>
+        <v>0.0003982933790771435</v>
       </c>
       <c r="K8" t="n">
-        <v>2.47870109791e-05</v>
+        <v>0.0002428961956017972</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3868102388617e-05</v>
+        <v>0.0005575977234348918</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001508580476521698</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001907251841499395</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001910117255375448</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002370685124299289</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001907320220146187</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001909453363453564</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001910117233340273</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001907320296867054</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001910117233340273</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001677465268750935</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001910117233340273</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.470317080570992e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.302162718945217e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.259543214190582e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.3702798270268e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.3702798270268e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.416662044128446e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.25412183425902e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3702798270268e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.465218969266421e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.47870109791005e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.386810238861704e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.52123982555213e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.362420400032434e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.376287170615984e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.455112384681282e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.455112384681282e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.495966812416226e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.374283912791651e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.455112384681282e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.52329285806089e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.536080077299487e-05</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>2.521239825552128e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.362420400032436e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.376287170615985e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.455112384681286e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.455112384681286e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.495966812416231e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.374283912791653e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.455112384681286e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.523292858060903e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.536080077299519e-05</v>
+      </c>
+      <c r="L11" t="n">
         <v>2.45731216571968e-05</v>
       </c>
     </row>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.881951424520651e-05</v>
+        <v>2.669315176545916e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002064834359259808</v>
+        <v>2.421223921918647e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002539331552619362</v>
+        <v>2.490378372276161e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000218313219540245</v>
+        <v>2.543122155815005e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000218313219540245</v>
+        <v>2.543122155815005e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002224531614704952</v>
+        <v>2.580638233582388e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002656626302862936</v>
+        <v>2.489287460289548e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000218313219540245</v>
+        <v>2.543122155815005e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002277509741660676</v>
+        <v>2.598844367650898e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001987206311797725</v>
+        <v>2.603707386415959e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002362506963759098</v>
+        <v>2.525886289763787e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.033137865801233e-06</v>
+        <v>2.668444097993102e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.973164309892627e-06</v>
+        <v>2.412558997698303e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>8.033137865801233e-06</v>
+        <v>2.476528166310476e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.320163517487623e-06</v>
+        <v>2.53472516354771e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.320163517487625e-06</v>
+        <v>2.53472516354771e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.966261788552841e-06</v>
+        <v>2.572264125857524e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.033137865801233e-06</v>
+        <v>2.476528166310476e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.750490322694988e-06</v>
+        <v>2.53472516354771e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.033137865801233e-06</v>
+        <v>2.590682184867896e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.033137865801233e-06</v>
+        <v>2.5982518053311e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.033137865801233e-06</v>
+        <v>2.517268936826171e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.511299145321724e-05</v>
+        <v>7.881951424520648e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.471992429430007e-05</v>
+        <v>0.0002064834359259809</v>
       </c>
       <c r="D4" t="n">
-        <v>3.296417044345365e-05</v>
+        <v>0.0002539331552619358</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458577436072936e-05</v>
+        <v>0.0002183132195402453</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484677414433533e-05</v>
+        <v>0.0002183132195402453</v>
       </c>
       <c r="G4" t="n">
-        <v>1.504611537596873e-05</v>
+        <v>0.0002224531614704989</v>
       </c>
       <c r="H4" t="n">
-        <v>3.408614472446397e-05</v>
+        <v>0.0002656626302862934</v>
       </c>
       <c r="I4" t="n">
-        <v>3.211365967384323e-05</v>
+        <v>0.0002183132195402453</v>
       </c>
       <c r="J4" t="n">
-        <v>3.276462268138103e-05</v>
+        <v>0.0002277509741660672</v>
       </c>
       <c r="K4" t="n">
-        <v>1.508972469323927e-05</v>
+        <v>0.0001987206311797729</v>
       </c>
       <c r="L4" t="n">
-        <v>1.512820896449282e-05</v>
+        <v>0.0002362506963759094</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.382360445755503e-05</v>
+        <v>8.033137865801246e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.353618213007926e-05</v>
+        <v>6.973164309892513e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.38235868796305e-05</v>
+        <v>8.033137865801214e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.355339273686704e-05</v>
+        <v>7.320163517487715e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.355339273686704e-05</v>
+        <v>7.320163517487718e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.375672838030652e-05</v>
+        <v>7.966261788552802e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.382360445755503e-05</v>
+        <v>8.033137865801246e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.354095691444891e-05</v>
+        <v>7.750490322695108e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.382360445755503e-05</v>
+        <v>8.033137865801246e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.382360445755503e-05</v>
+        <v>8.033137865801246e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.382360445755503e-05</v>
+        <v>8.033137865801246e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002338352051555598</v>
+        <v>1.511299145321706e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003783777001959718</v>
+        <v>1.471992429430001e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004086477503252024</v>
+        <v>3.296417044345388e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003387795484485674</v>
+        <v>1.458577436072938e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000238149590212423</v>
+        <v>1.484677414433522e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003785578283551015</v>
+        <v>1.504611537596874e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003786247044325315</v>
+        <v>3.40861447244639e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003783420568892431</v>
+        <v>3.211365967384329e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003786531597427001</v>
+        <v>3.276462268138098e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002311456658692289</v>
+        <v>1.508972469323948e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005298694435519203</v>
+        <v>1.512820896449283e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001363623516663553</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001721384588266234</v>
+        <v>5.35361821300791e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001724258838102716</v>
+        <v>5.382358687963063e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002137597751793308</v>
+        <v>5.355339273686704e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001721432262579632</v>
+        <v>5.355339273686704e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001723590050768509</v>
+        <v>5.375672838030642e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001724258811540991</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001721432336109933</v>
+        <v>5.354095691444872e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001724258811540991</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001515305316536636</v>
+        <v>5.382360445755488e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001724258811540991</v>
+        <v>5.382360445755488e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.546633064725677e-05</v>
+        <v>0.0002338352051555596</v>
       </c>
       <c r="C8" t="n">
-        <v>2.269130315789844e-05</v>
+        <v>0.0003783777001959722</v>
       </c>
       <c r="D8" t="n">
-        <v>2.207614686577292e-05</v>
+        <v>0.0004086477503252011</v>
       </c>
       <c r="E8" t="n">
-        <v>2.355728062130836e-05</v>
+        <v>0.0003387795484485675</v>
       </c>
       <c r="F8" t="n">
-        <v>2.355728062130834e-05</v>
+        <v>0.0002381495902124239</v>
       </c>
       <c r="G8" t="n">
-        <v>2.386253545977787e-05</v>
+        <v>0.0003785578283551011</v>
       </c>
       <c r="H8" t="n">
-        <v>2.235532216590441e-05</v>
+        <v>0.000378624704432531</v>
       </c>
       <c r="I8" t="n">
-        <v>2.355728062130836e-05</v>
+        <v>0.0003783420568892434</v>
       </c>
       <c r="J8" t="n">
-        <v>2.405151290430913e-05</v>
+        <v>0.0003786531597427004</v>
       </c>
       <c r="K8" t="n">
-        <v>2.465380968787719e-05</v>
+        <v>0.0002311456658692285</v>
       </c>
       <c r="L8" t="n">
-        <v>2.347767270714294e-05</v>
+        <v>0.0005298694435519203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001363623516663554</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001721384588266237</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001724258838102718</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002137597751793309</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.000172143226257963</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001723590050768509</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001724258811540992</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001721432336109932</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001724258811540992</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001515305316536639</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001724258811540992</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.54663306472568e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.269130315789843e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.207614686577301e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.355728062130831e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.355728062130831e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.386253545977786e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.235532216590437e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.355728062130831e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.405151290430911e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.465380968787729e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.347767270714287e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.613890768220509e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.355963414570202e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.368021882021153e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.461677904240414e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.461677904240414e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.496002826956548e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.379633535158406e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.461677904240414e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.514427219430191e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.543250732354482e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.448762491513117e-05</v>
+      <c r="B11" t="n">
+        <v>2.61389076822051e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.355963414570204e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.368021882021149e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.461677904240411e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.461677904240411e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.49600282695656e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.379633535158405e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.461677904240411e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.514427219430192e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.543250732354496e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.448762491513119e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.406952072551919e-05</v>
+        <v>2.860992983659942e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002181561387013351</v>
+        <v>2.451418638652931e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002567692941055755</v>
+        <v>2.541946251284988e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002208444835713961</v>
+        <v>2.592693727673394e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002208444835713961</v>
+        <v>2.592693727673394e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002296383831922629</v>
+        <v>2.625034933511e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000269144723854974</v>
+        <v>2.540895349474117e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002208444835713961</v>
+        <v>2.592693727673394e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002565380342690679</v>
+        <v>2.686659109886428e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002025748062918029</v>
+        <v>2.626177005525195e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002467231865952739</v>
+        <v>2.56817465100896e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.844923908727514e-06</v>
+        <v>2.862417466415538e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.731690211358097e-06</v>
+        <v>2.441738054721355e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>8.844923908727514e-06</v>
+        <v>2.528435065915103e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.169275209326676e-06</v>
+        <v>2.58464906915191e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.169275209326676e-06</v>
+        <v>2.584649069151913e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.777699753747701e-06</v>
+        <v>2.616393299849325e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.844923908727514e-06</v>
+        <v>2.528435065915103e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.560336297367381e-06</v>
+        <v>2.584649069151913e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.844923908727514e-06</v>
+        <v>2.676486419090515e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.844923908727514e-06</v>
+        <v>2.620478675157485e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.844923908727514e-06</v>
+        <v>2.558988702687969e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.387591770109478e-05</v>
+        <v>8.40695207255191e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.571386848336732e-05</v>
+        <v>0.0002181561387013354</v>
       </c>
       <c r="D4" t="n">
-        <v>1.616283407668198e-05</v>
+        <v>0.0002567692941055754</v>
       </c>
       <c r="E4" t="n">
-        <v>1.553989329305291e-05</v>
+        <v>0.0002208444835713958</v>
       </c>
       <c r="F4" t="n">
-        <v>1.584881477808987e-05</v>
+        <v>0.0002208444835713958</v>
       </c>
       <c r="G4" t="n">
-        <v>3.380869354611537e-05</v>
+        <v>0.0002296383831922666</v>
       </c>
       <c r="H4" t="n">
-        <v>1.614374497408962e-05</v>
+        <v>0.0002691447238549735</v>
       </c>
       <c r="I4" t="n">
-        <v>3.359133008973474e-05</v>
+        <v>0.0002208444835713958</v>
       </c>
       <c r="J4" t="n">
-        <v>1.663509256489162e-05</v>
+        <v>0.0002565380342690679</v>
       </c>
       <c r="K4" t="n">
-        <v>1.608493123911744e-05</v>
+        <v>0.000202574806291803</v>
       </c>
       <c r="L4" t="n">
-        <v>1.613235967535529e-05</v>
+        <v>0.0002467231865952741</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.497429088176302e-05</v>
+        <v>8.84492390872789e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.468607233908111e-05</v>
+        <v>7.731690211357802e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.497426971129081e-05</v>
+        <v>8.84492390872789e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.471905662033061e-05</v>
+        <v>8.169275209326678e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.471905662033061e-05</v>
+        <v>8.169275209326686e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.490706672678285e-05</v>
+        <v>8.777699753748019e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.497429088176302e-05</v>
+        <v>8.84492390872789e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.46897032704024e-05</v>
+        <v>8.560336297367364e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.497429088176302e-05</v>
+        <v>8.844923908727886e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.497429088176302e-05</v>
+        <v>8.84492390872789e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.497429088176302e-05</v>
+        <v>8.84492390872789e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000235545230160202</v>
+        <v>3.38759177010954e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003808961931724022</v>
+        <v>1.571386848336707e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004113151017813704</v>
+        <v>1.616283407668162e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003410782937201317</v>
+        <v>1.553989329305292e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002398929034796563</v>
+        <v>1.584881477808964e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003810604164399557</v>
+        <v>3.380869354611551e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003811276405952123</v>
+        <v>1.614374497408902e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003808430529835748</v>
+        <v>3.359133008973487e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003811562517313241</v>
+        <v>1.663509256489166e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000232840962142253</v>
+        <v>1.608493123911719e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005332006417180838</v>
+        <v>1.613235967535553e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001313973382011602</v>
+        <v>5.497429088176287e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001656717502756634</v>
+        <v>5.468607233908101e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001659599719707258</v>
+        <v>5.497426971129058e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002055599177445456</v>
+        <v>5.471905662033056e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001656753738484256</v>
+        <v>5.471905662033056e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001658927446633651</v>
+        <v>5.490706672678299e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001659599688183448</v>
+        <v>5.497429088176287e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001656753812069845</v>
+        <v>5.468970327040225e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001659599688183448</v>
+        <v>5.497429088176287e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001459342462267001</v>
+        <v>5.497429088176287e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001659599688183448</v>
+        <v>5.497429088176287e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.729465408307202e-05</v>
+        <v>0.0002355452301602023</v>
       </c>
       <c r="C8" t="n">
-        <v>2.27192126286339e-05</v>
+        <v>0.0003808961931724018</v>
       </c>
       <c r="D8" t="n">
-        <v>2.253967266788333e-05</v>
+        <v>0.0004113151017813699</v>
       </c>
       <c r="E8" t="n">
-        <v>2.400887145213546e-05</v>
+        <v>0.0003410782937201313</v>
       </c>
       <c r="F8" t="n">
-        <v>2.400887145213545e-05</v>
+        <v>0.000239892903479656</v>
       </c>
       <c r="G8" t="n">
-        <v>2.414693600219118e-05</v>
+        <v>0.0003810604164399552</v>
       </c>
       <c r="H8" t="n">
-        <v>2.281166190338431e-05</v>
+        <v>0.0003811276405952119</v>
       </c>
       <c r="I8" t="n">
-        <v>2.400887145213545e-05</v>
+        <v>0.0003808430529835745</v>
       </c>
       <c r="J8" t="n">
-        <v>2.425576969182715e-05</v>
+        <v>0.0003811562517313246</v>
       </c>
       <c r="K8" t="n">
-        <v>2.479603920951242e-05</v>
+        <v>0.0002328409621422525</v>
       </c>
       <c r="L8" t="n">
-        <v>2.368597582014191e-05</v>
+        <v>0.0005332006417180829</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001313973382011598</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001656717502756632</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001659599719707257</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002055599177445455</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001656753738484254</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.000165892744663365</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001659599688183452</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001656753812069846</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001659599688183452</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001459342462266997</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001659599688183452</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.729465408307194e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.271921262863382e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.253967266788321e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.400887145213542e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.400887145213542e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.414693600219111e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.281166190338429e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.400887145213542e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.425576969182711e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.479603920951238e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.368597582014178e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.80049937352759e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.374151457183541e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.417062528005332e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.509081466666934e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.509081466666934e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.53326092740045e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.42838722308755e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.509081466666934e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.57249451057741e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.562078543420137e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.481546084361884e-05</v>
+      <c r="B11" t="n">
+        <v>2.800499373527576e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.374151457183539e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.417062528005322e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.509081466666931e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.509081466666931e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.533260927400453e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.428387223087573e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.509081466666931e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.572494510577403e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.562078543420144e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.481546084361882e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.328627833446994e-05</v>
+        <v>2.64974183425188e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002036041184664386</v>
+        <v>2.436803336101043e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002545092525409226</v>
+        <v>2.469940628664373e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002200310953525527</v>
+        <v>2.524809804494693e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002200310953525527</v>
+        <v>2.524809804494693e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002201960300747262</v>
+        <v>2.573151094957415e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002653814320927516</v>
+        <v>2.468844828983437e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002200310953525527</v>
+        <v>2.524809804494693e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002173052489693049</v>
+        <v>2.57201248781004e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001995138663597101</v>
+        <v>2.598164867487486e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002271160688826436</v>
+        <v>2.511820505710487e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.789838540568517e-06</v>
+        <v>2.649653545166473e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.736245506874537e-06</v>
+        <v>2.429973630157361e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.789838540568517e-06</v>
+        <v>2.457296489641247e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.063370770053728e-06</v>
+        <v>2.51728817703439e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.063370770053721e-06</v>
+        <v>2.51728817703439e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.723257471014168e-06</v>
+        <v>2.566268726107627e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.789838540568517e-06</v>
+        <v>2.457296489641247e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.508885500998713e-06</v>
+        <v>2.51728817703439e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.789838540568517e-06</v>
+        <v>2.56591724829603e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.789838540568517e-06</v>
+        <v>2.593778923641988e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.789838540568517e-06</v>
+        <v>2.505192793331867e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.517123323065766e-05</v>
+        <v>7.328627833446985e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.478829632031291e-05</v>
+        <v>0.0002036041184664388</v>
       </c>
       <c r="D4" t="n">
-        <v>1.525871362316244e-05</v>
+        <v>0.0002545092525409223</v>
       </c>
       <c r="E4" t="n">
-        <v>1.465377666915522e-05</v>
+        <v>0.0002200310953525528</v>
       </c>
       <c r="F4" t="n">
-        <v>1.490762093161494e-05</v>
+        <v>0.0002200310953525528</v>
       </c>
       <c r="G4" t="n">
-        <v>1.510465216110341e-05</v>
+        <v>0.0002201960300747269</v>
       </c>
       <c r="H4" t="n">
-        <v>3.43965097604178e-05</v>
+        <v>0.0002653814320927533</v>
       </c>
       <c r="I4" t="n">
-        <v>1.489028019108779e-05</v>
+        <v>0.0002200310953525528</v>
       </c>
       <c r="J4" t="n">
-        <v>1.566454902718263e-05</v>
+        <v>0.0002173052489693052</v>
       </c>
       <c r="K4" t="n">
-        <v>1.516307802128405e-05</v>
+        <v>0.0001995138663597097</v>
       </c>
       <c r="L4" t="n">
-        <v>1.518498600884824e-05</v>
+        <v>0.0002271160688826431</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.602977410080345e-05</v>
+        <v>7.78983854056839e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.574305474822598e-05</v>
+        <v>6.736245506874566e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.602974481955796e-05</v>
+        <v>7.78983854056839e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.575960685324187e-05</v>
+        <v>7.063370770053555e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.575960685324187e-05</v>
+        <v>7.063370770053843e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.596319303124999e-05</v>
+        <v>7.723257471014583e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.602977410080345e-05</v>
+        <v>7.78983854056839e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.574882106123351e-05</v>
+        <v>7.508885500998723e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.602977410080345e-05</v>
+        <v>7.78983854056839e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.602977410080345e-05</v>
+        <v>7.78983854056839e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.602977410080345e-05</v>
+        <v>7.78983854056839e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002457271676430823</v>
+        <v>1.51712332306574e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003979948202728098</v>
+        <v>1.478829632031289e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004298659488839403</v>
+        <v>1.525871362316182e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003562850891434766</v>
+        <v>1.465377666915522e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002502871248636086</v>
+        <v>1.490762093161466e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003981745946924276</v>
+        <v>1.510465216110367e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003982411757620347</v>
+        <v>3.439650976041789e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003979602227224108</v>
+        <v>1.489028019108751e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003982711491617584</v>
+        <v>1.566454902718198e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002428941416391522</v>
+        <v>1.516307802128432e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005575548102816258</v>
+        <v>1.518498600884823e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001510907071096544</v>
+        <v>5.602977410080332e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001910140563179324</v>
+        <v>5.574305474822611e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001913007780769551</v>
+        <v>5.602974481955766e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002374213817254833</v>
+        <v>5.575960685324206e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001910198149438422</v>
+        <v>5.575960685324206e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001912341946009559</v>
+        <v>5.596319303124955e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001913007756705096</v>
+        <v>5.602977410080332e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001910198226309399</v>
+        <v>5.574882106123338e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001913007756705096</v>
+        <v>5.602977410080332e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001680029050413635</v>
+        <v>5.602977410080332e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001913007756705096</v>
+        <v>5.602977410080332e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.54862821657109e-05</v>
+        <v>0.0002457271676430826</v>
       </c>
       <c r="C8" t="n">
-        <v>2.317469698933077e-05</v>
+        <v>0.0003979948202728102</v>
       </c>
       <c r="D8" t="n">
-        <v>2.218259837026108e-05</v>
+        <v>0.0004298659488839416</v>
       </c>
       <c r="E8" t="n">
-        <v>2.360746794667797e-05</v>
+        <v>0.0003562850891434776</v>
       </c>
       <c r="F8" t="n">
-        <v>2.360746794667797e-05</v>
+        <v>0.0002502871248636091</v>
       </c>
       <c r="G8" t="n">
-        <v>2.411681759149591e-05</v>
+        <v>0.0003981745946924275</v>
       </c>
       <c r="H8" t="n">
-        <v>2.245720385274456e-05</v>
+        <v>0.0003982411757620359</v>
       </c>
       <c r="I8" t="n">
-        <v>2.360746794667797e-05</v>
+        <v>0.0003979602227224115</v>
       </c>
       <c r="J8" t="n">
-        <v>2.429724876359951e-05</v>
+        <v>0.0003982711491617584</v>
       </c>
       <c r="K8" t="n">
-        <v>2.483073134134232e-05</v>
+        <v>0.0002428941416391528</v>
       </c>
       <c r="L8" t="n">
-        <v>2.378936984309169e-05</v>
+        <v>0.0005575548102816263</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001510907071096546</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001910140563179325</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001913007780769551</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002374213817254841</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001910198149438426</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001912341946009562</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001913007756705097</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001910198226309401</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001913007756705097</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001680029050413637</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001913007756705097</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.548628216571079e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.317469698933088e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.218259837026116e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.360746794667797e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.360746794667797e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.411681759149578e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.245720385274446e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.360746794667797e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.429724876359968e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.483073134134106e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.37893698430916e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.603774987792383e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.385613688865238e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.361178189959867e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.453582976650106e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.453582976650106e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.502813532352057e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.372577027243514e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.453582976650106e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.510044524559784e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.547793380463136e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.454373710251777e-05</v>
+      <c r="B11" t="n">
+        <v>2.603774987792353e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.385613688865244e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.36117818995988e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.453582976650109e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.453582976650109e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.502813532352068e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.372577027243508e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.453582976650109e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.510044524559791e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.547793380463012e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.454373710251763e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.130342075173966e-05</v>
+        <v>3.524174300757086e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002100005021519489</v>
+        <v>2.471702886276737e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002544506438587369</v>
+        <v>2.487775318207865e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000219037417207612</v>
+        <v>2.560560294406848e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000219037417207612</v>
+        <v>2.560560294406848e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002252313765716168</v>
+        <v>2.671912198333217e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002682880457311471</v>
+        <v>2.486898860488223e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000219037417207612</v>
+        <v>2.560560294406848e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002516273766250272</v>
+        <v>2.600179806406796e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002002517322008379</v>
+        <v>2.678338710321187e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000239579799310945</v>
+        <v>2.524444376387941e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.995810337532046e-06</v>
+        <v>3.536608079050346e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.938021267482627e-06</v>
+        <v>2.463430617338813e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.995810337532046e-06</v>
+        <v>2.473818705561106e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.305761543105625e-06</v>
+        <v>2.552352777913749e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.305761543105625e-06</v>
+        <v>2.552352777913749e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.928428974973408e-06</v>
+        <v>2.664665730950386e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.995810337532046e-06</v>
+        <v>2.473818705561106e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.709788576157046e-06</v>
+        <v>2.552352777913749e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.995810337532046e-06</v>
+        <v>2.589332061892453e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.995810337532046e-06</v>
+        <v>2.673885694743428e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.995810337532046e-06</v>
+        <v>2.515454375369819e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.238138643647917e-05</v>
+        <v>8.130342075173967e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.472260187631284e-05</v>
+        <v>0.0002100005021519481</v>
       </c>
       <c r="D4" t="n">
-        <v>1.51866097489752e-05</v>
+        <v>0.0002544506438587364</v>
       </c>
       <c r="E4" t="n">
-        <v>1.458325299530093e-05</v>
+        <v>0.0002190374172076114</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484572816883849e-05</v>
+        <v>0.0002190374172076114</v>
       </c>
       <c r="G4" t="n">
-        <v>1.504711319788745e-05</v>
+        <v>0.0002252313765716138</v>
       </c>
       <c r="H4" t="n">
-        <v>3.407055765922325e-05</v>
+        <v>0.000268288045731147</v>
       </c>
       <c r="I4" t="n">
-        <v>3.209536467510417e-05</v>
+        <v>0.0002190374172076114</v>
       </c>
       <c r="J4" t="n">
-        <v>1.560129608106891e-05</v>
+        <v>0.0002516273766250264</v>
       </c>
       <c r="K4" t="n">
-        <v>1.509323132178788e-05</v>
+        <v>0.0002002517322008373</v>
       </c>
       <c r="L4" t="n">
-        <v>1.513059265812431e-05</v>
+        <v>0.0002395797993109444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.375492711177868e-05</v>
+        <v>7.995810337532311e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.346748506913875e-05</v>
+        <v>6.938021267482683e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.375491231012456e-05</v>
+        <v>7.995810337532311e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.348924737064407e-05</v>
+        <v>7.305761543105644e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.348924737064407e-05</v>
+        <v>7.305761543105596e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.368754574922007e-05</v>
+        <v>7.928428974973154e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.375492711177868e-05</v>
+        <v>7.995810337532311e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.34689053504037e-05</v>
+        <v>7.709788576156951e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.375492711177868e-05</v>
+        <v>7.995810337532241e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.375492711177868e-05</v>
+        <v>7.995810337532311e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.375492711177868e-05</v>
+        <v>7.995810337532311e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000233744075836577</v>
+        <v>3.238138643647889e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003782395275265686</v>
+        <v>1.472260187631286e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004084907421169311</v>
+        <v>1.518660974897533e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000338652149310088</v>
+        <v>1.458325299530092e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000238058071836977</v>
+        <v>1.484572816883863e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003784116291805861</v>
+        <v>1.50471131978876e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003784790105433296</v>
+        <v>3.407055765922256e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003781929887817695</v>
+        <v>3.209536467510408e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003785074551302379</v>
+        <v>1.560129608106878e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002310555501151225</v>
+        <v>1.509323132178891e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005296667524067481</v>
+        <v>1.513059265812438e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001363727196563696</v>
+        <v>5.375492711177837e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001721531272499293</v>
+        <v>5.346748506913866e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001724405719731027</v>
+        <v>5.375491231012449e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002137760744349914</v>
+        <v>5.348924737064405e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001721545401411415</v>
+        <v>5.348924737064405e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001723731879300105</v>
+        <v>5.368754574921982e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001724405692925692</v>
+        <v>5.375492711177837e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001721545475311942</v>
+        <v>5.346890535040348e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001724405692925692</v>
+        <v>5.375492711177837e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001270247078174702</v>
+        <v>5.375492711177837e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001724405692925692</v>
+        <v>5.375492711177837e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.40891569064389e-05</v>
+        <v>0.0002337440758365762</v>
       </c>
       <c r="C8" t="n">
-        <v>2.311646418492916e-05</v>
+        <v>0.0003782395275265681</v>
       </c>
       <c r="D8" t="n">
-        <v>2.203630813717976e-05</v>
+        <v>0.0004084907421169306</v>
       </c>
       <c r="E8" t="n">
-        <v>2.371586882829572e-05</v>
+        <v>0.0003386521493100873</v>
       </c>
       <c r="F8" t="n">
-        <v>2.371586882829572e-05</v>
+        <v>0.0002380580718369767</v>
       </c>
       <c r="G8" t="n">
-        <v>2.47206328204338e-05</v>
+        <v>0.0003784116291805856</v>
       </c>
       <c r="H8" t="n">
-        <v>2.227163155913214e-05</v>
+        <v>0.0003784790105433288</v>
       </c>
       <c r="I8" t="n">
-        <v>2.371586882829572e-05</v>
+        <v>0.000378192988781769</v>
       </c>
       <c r="J8" t="n">
-        <v>2.348483332122417e-05</v>
+        <v>0.0003785074551302374</v>
       </c>
       <c r="K8" t="n">
-        <v>2.537283058851712e-05</v>
+        <v>0.0002310555501151221</v>
       </c>
       <c r="L8" t="n">
-        <v>2.338920927478316e-05</v>
+        <v>0.0005296667524067483</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001363727196563689</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001721531272499288</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001724405719731023</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002137760744349905</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001721545401411414</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001723731879300103</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.000172440569292569</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001721545475311941</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.000172440569292569</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001270247078174697</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.000172440569292569</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.408915690643887e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.311646418492912e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.203630813717963e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.371586882829566e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.371586882829566e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.472063282043363e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.227163155913215e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.371586882829566e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.348483332122418e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.537283058851717e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.338920927478323e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3.466073857100708e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.402640592094314e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.364838966381521e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.478311236076824e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.478311236076824e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.584277470292961e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.374669799353837e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.478311236076824e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.490592866822068e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.616184075663674e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.444121095018595e-05</v>
+      <c r="B11" t="n">
+        <v>3.466073857100655e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.402640592094311e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.364838966381512e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.478311236076819e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.478311236076819e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.584277470292947e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.374669799353823e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.478311236076819e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.490592866822059e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.616184075663662e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.444121095018571e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.332251137702226e-05</v>
+        <v>5.900988575900245e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002166425821214574</v>
+        <v>2.511818099209114e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002529389665772096</v>
+        <v>2.524239139595295e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002208035569144127</v>
+        <v>2.584813542129415e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002208035569144127</v>
+        <v>2.584813542129415e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002285210671437047</v>
+        <v>2.903106295919303e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000269625502566337</v>
+        <v>2.523683850226002e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002208035569144127</v>
+        <v>2.584813542129415e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000260988249786803</v>
+        <v>2.660926191023925e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002018301883058992</v>
+        <v>2.658561014398307e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002450931595243695</v>
+        <v>2.55585249617785e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.652889781204233e-06</v>
+        <v>5.950872515269265e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.541272952922017e-06</v>
+        <v>2.503301592383475e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>8.652889781204233e-06</v>
+        <v>2.510927838325187e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.037877665053792e-06</v>
+        <v>2.576672770433591e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.037877665053797e-06</v>
+        <v>2.576672770433591e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.584017443728453e-06</v>
+        <v>2.899043106267608e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.652889781204233e-06</v>
+        <v>2.510927838325187e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.357184892460705e-06</v>
+        <v>2.576672770433591e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.652889781204233e-06</v>
+        <v>2.649869097319274e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.652889781204233e-06</v>
+        <v>2.653493777252149e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.652889781204233e-06</v>
+        <v>2.546669273808332e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.350351614749699e-05</v>
+        <v>8.332251137702236e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.546936716645214e-05</v>
+        <v>0.0002166425821214573</v>
       </c>
       <c r="D4" t="n">
-        <v>1.591784233642247e-05</v>
+        <v>0.0002529389665772102</v>
       </c>
       <c r="E4" t="n">
-        <v>1.531264576805759e-05</v>
+        <v>0.0002208035569144127</v>
       </c>
       <c r="F4" t="n">
-        <v>1.559879347164544e-05</v>
+        <v>0.0002208035569144127</v>
       </c>
       <c r="G4" t="n">
-        <v>1.580256616989101e-05</v>
+        <v>0.0002285210671437089</v>
       </c>
       <c r="H4" t="n">
-        <v>3.571442451420041e-05</v>
+        <v>0.0002696255025663369</v>
       </c>
       <c r="I4" t="n">
-        <v>1.557573361862332e-05</v>
+        <v>0.0002208035569144127</v>
       </c>
       <c r="J4" t="n">
-        <v>3.396743988476388e-05</v>
+        <v>0.0002609882497868037</v>
       </c>
       <c r="K4" t="n">
-        <v>1.583971009124308e-05</v>
+        <v>0.0002018301883058992</v>
       </c>
       <c r="L4" t="n">
-        <v>1.589470405404849e-05</v>
+        <v>0.0002450931595243697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.467543576404718e-05</v>
+        <v>8.652889781204228e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.438732066557262e-05</v>
+        <v>7.54127295292205e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.467541786412435e-05</v>
+        <v>8.652889781204228e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.442942967777285e-05</v>
+        <v>8.03787766505374e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.442942967777285e-05</v>
+        <v>8.03787766505374e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.460656342657137e-05</v>
+        <v>8.584017443728427e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.467543576404718e-05</v>
+        <v>8.652889781204228e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.437973087530362e-05</v>
+        <v>8.357184892460595e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.467543576404718e-05</v>
+        <v>8.652889781204228e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.467543576404718e-05</v>
+        <v>8.652889781204228e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.467543576404718e-05</v>
+        <v>8.652889781204228e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002351283661971102</v>
+        <v>3.350351614749702e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003802726428217748</v>
+        <v>1.546936716645215e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004106251501429643</v>
+        <v>1.591784233642243e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003405033341964531</v>
+        <v>1.531264576805754e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002394698875762123</v>
+        <v>1.559879347164545e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003804157178513604</v>
+        <v>1.580256616989108e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003804845901891084</v>
+        <v>3.57144245142005e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003801888853000922</v>
+        <v>1.557573361862331e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003805131568746453</v>
+        <v>3.396743988476386e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002324282997083074</v>
+        <v>1.583971009124313e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005323213206603242</v>
+        <v>1.589470405404857e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001311341385605494</v>
+        <v>5.467543576404723e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001653527023763693</v>
+        <v>5.438732066557267e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001656408205248487</v>
+        <v>5.467541786412444e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000205165081978641</v>
+        <v>5.442942967777296e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001653451052485768</v>
+        <v>5.442942967777296e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001655719451373677</v>
+        <v>5.460656342657144e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001656408174748437</v>
+        <v>5.467543576404723e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001653451125860998</v>
+        <v>5.437973087530372e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001656408174748437</v>
+        <v>5.467543576404723e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001448363597542567</v>
+        <v>5.467543576404723e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001656408174748437</v>
+        <v>5.467543576404723e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.819510156487284e-05</v>
+        <v>0.0002351283661971102</v>
       </c>
       <c r="C8" t="n">
-        <v>2.336888899278676e-05</v>
+        <v>0.000380272642821775</v>
       </c>
       <c r="D8" t="n">
-        <v>2.245606209053387e-05</v>
+        <v>0.0004106251501429645</v>
       </c>
       <c r="E8" t="n">
-        <v>2.392785032007179e-05</v>
+        <v>0.0003405033341964535</v>
       </c>
       <c r="F8" t="n">
-        <v>2.392785032007179e-05</v>
+        <v>0.0002394698875762121</v>
       </c>
       <c r="G8" t="n">
-        <v>2.699791675638971e-05</v>
+        <v>0.0003804157178513604</v>
       </c>
       <c r="H8" t="n">
-        <v>2.262445179547969e-05</v>
+        <v>0.0003804845901891087</v>
       </c>
       <c r="I8" t="n">
-        <v>2.392785032007179e-05</v>
+        <v>0.0003801888853000927</v>
       </c>
       <c r="J8" t="n">
-        <v>2.388460434260808e-05</v>
+        <v>0.0003805131568746456</v>
       </c>
       <c r="K8" t="n">
-        <v>2.514229361618212e-05</v>
+        <v>0.0002324282997083076</v>
       </c>
       <c r="L8" t="n">
-        <v>2.359539754712568e-05</v>
+        <v>0.0005323213206603249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001311341385605499</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001653527023763694</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.000165640820524849</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.000205165081978642</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001653451052485772</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001655719451373683</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001656408174748442</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001653451125861006</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001656408174748442</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001448363597542571</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001656408174748442</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.819510156487283e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.336888899278677e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.245606209053396e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.392785032007185e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.392785032007185e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.699791675638972e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.262445179547969e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.392785032007185e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.388460434260813e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.514229361618212e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.359539754712577e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.841218284027443e-05</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>5.841218284027446e-05</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.436099793520642e-05</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.403516952746754e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.501144035129942e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.501144035129942e-05</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="D11" t="n">
+        <v>2.403516952746762e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.501144035129949e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.501144035129949e-05</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.812446260006638e-05</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.410623448615109e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.501144035129942e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.541984416272337e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.595195261475496e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.470707968642883e-05</v>
+      <c r="H11" t="n">
+        <v>2.410623448615118e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.501144035129949e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.541984416272343e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.595195261475506e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.470707968642884e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00018835854164686</v>
+        <v>2.43237917065067e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000207818894269702</v>
+        <v>2.486836329562783e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001966769740404309</v>
+        <v>2.433864175426089e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000207818894269702</v>
+        <v>2.486836329562783e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000207818894269702</v>
+        <v>2.486836329562783e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001888222617823272</v>
+        <v>2.428889163417846e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002038699187735649</v>
+        <v>2.433150107643231e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000207818894269702</v>
+        <v>2.486836329562783e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001973971314192439</v>
+        <v>2.43409274556656e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001834198150645251</v>
+        <v>2.432607215135675e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001920505311137785</v>
+        <v>2.433056139475439e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.027221813380257e-06</v>
+        <v>2.428594104223455e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.291283185805561e-06</v>
+        <v>2.484185661681383e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.027221813380257e-06</v>
+        <v>2.428594104223455e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.339469236671698e-06</v>
+        <v>2.484185661681383e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.339469236671699e-06</v>
+        <v>2.484185661681383e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>6.962028001241259e-06</v>
+        <v>2.424657574194453e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.027221813380257e-06</v>
+        <v>2.428594104223455e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.754487183324734e-06</v>
+        <v>2.484185661681383e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.027221813380257e-06</v>
+        <v>2.428594104223455e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.027221813380257e-06</v>
+        <v>2.428594104223455e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.027221813380257e-06</v>
+        <v>2.428594104223455e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.450540011019829e-05</v>
+        <v>0.0001883585416468634</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420733772466935e-05</v>
+        <v>0.0002078188942697025</v>
       </c>
       <c r="D4" t="n">
-        <v>1.455096025756212e-05</v>
+        <v>0.0001966769740404304</v>
       </c>
       <c r="E4" t="n">
-        <v>1.399782032069919e-05</v>
+        <v>0.0002078188942697025</v>
       </c>
       <c r="F4" t="n">
-        <v>1.424180826159976e-05</v>
+        <v>0.0002078188942697025</v>
       </c>
       <c r="G4" t="n">
-        <v>1.444020629805927e-05</v>
+        <v>0.0001888222617823286</v>
       </c>
       <c r="H4" t="n">
-        <v>3.227888246084649e-05</v>
+        <v>0.0002038699187735641</v>
       </c>
       <c r="I4" t="n">
-        <v>3.192659425124946e-05</v>
+        <v>0.0002078188942697025</v>
       </c>
       <c r="J4" t="n">
-        <v>1.498879124756719e-05</v>
+        <v>0.0001973971314192456</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453375791672653e-05</v>
+        <v>0.0001834198150645267</v>
       </c>
       <c r="L4" t="n">
-        <v>1.452068547462676e-05</v>
+        <v>0.0001920505311137775</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.542088017586323e-05</v>
+        <v>7.027221813380506e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.51481455458077e-05</v>
+        <v>6.291283185805516e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.542070969737263e-05</v>
+        <v>7.027221813380506e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.514696499143909e-05</v>
+        <v>6.339469236671549e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.514696499143909e-05</v>
+        <v>6.339469236671566e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.535568636372423e-05</v>
+        <v>6.962028001241547e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.542088017586323e-05</v>
+        <v>7.027221813380506e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.51481455458077e-05</v>
+        <v>6.754487183324813e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.542088017586323e-05</v>
+        <v>7.027221813380506e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.542088017586323e-05</v>
+        <v>7.027221813380506e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.542088017586323e-05</v>
+        <v>7.027221813380506e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002472157093151749</v>
+        <v>1.450540011019828e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004006838452642411</v>
+        <v>1.420733772466926e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004328003668881066</v>
+        <v>1.455096025756212e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003586419868442881</v>
+        <v>1.399782032069917e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002518147913271921</v>
+        <v>1.424180826159965e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004008620790374244</v>
+        <v>1.444020629805931e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004009272728495579</v>
+        <v>3.227888246084649e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004006545382195073</v>
+        <v>3.192659425124916e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004009574816040658</v>
+        <v>1.498879124756721e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002443604381046927</v>
+        <v>1.453375791672653e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005614918541387786</v>
+        <v>1.452068547462675e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001507563243906442</v>
+        <v>5.542088017586312e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001907107607462869</v>
+        <v>5.514814554580763e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001909834966176943</v>
+        <v>5.542070969737257e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002371320544751099</v>
+        <v>5.514696499143905e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001907107529406782</v>
+        <v>5.514696499143905e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001909183015642033</v>
+        <v>5.535568636372416e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001909834953763427</v>
+        <v>5.542088017586312e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001907107607462869</v>
+        <v>5.514814554580763e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001909834953763427</v>
+        <v>5.542088017586312e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001676757150450422</v>
+        <v>5.542088017586312e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001909834953763427</v>
+        <v>5.542088017586312e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.377994250782085e-05</v>
+        <v>0.0002472157093151746</v>
       </c>
       <c r="C8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>0.0004006838452642397</v>
       </c>
       <c r="D8" t="n">
-        <v>2.34692970621196e-05</v>
+        <v>0.0004328003668881067</v>
       </c>
       <c r="E8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>0.0003586419868442876</v>
       </c>
       <c r="F8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>0.0002518147913271916</v>
       </c>
       <c r="G8" t="n">
-        <v>2.365129209309335e-05</v>
+        <v>0.0004008620790374245</v>
       </c>
       <c r="H8" t="n">
-        <v>2.363600253402212e-05</v>
+        <v>0.000400927272849558</v>
       </c>
       <c r="I8" t="n">
-        <v>2.434165951225634e-05</v>
+        <v>0.0004006545382195065</v>
       </c>
       <c r="J8" t="n">
-        <v>2.34296400675481e-05</v>
+        <v>0.0004009574816040655</v>
       </c>
       <c r="K8" t="n">
-        <v>2.373305316759395e-05</v>
+        <v>0.0002443604381046931</v>
       </c>
       <c r="L8" t="n">
-        <v>2.365195157613799e-05</v>
+        <v>0.0005614918541387772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001507563243906441</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001907107607462867</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001909834966176941</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002371320544751096</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001907107529406779</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001909183015642033</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001909834953763423</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001907107607462867</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001909834953763423</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001676757150450419</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001909834953763423</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.377994250782071e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.434165951225637e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.346929706211965e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.434165951225637e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.434165951225637e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.36512920930934e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.363600253402213e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.434165951225637e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.342964006754813e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.373305316759402e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.365195157613796e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>2.409356076082678e-05</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>2.464077201902055e-05</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.396706614081864e-05</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>2.396706614081862e-05</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.464077201902055e-05</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>2.464077201902055e-05</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.401803567689476e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.40357769839645e-05</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>2.401803567689474e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.403577698396454e-05</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.464077201902055e-05</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.395130778331396e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.407450640644616e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.400056174947372e-05</v>
+      <c r="J11" t="n">
+        <v>2.395130778331393e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.407450640644621e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.400056174947371e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001769823896620232</v>
+        <v>2.445176981426534e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002031011974385333</v>
+        <v>2.500689462443337e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001932936259765656</v>
+        <v>2.446261405020874e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002031011974385333</v>
+        <v>2.500689462443337e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002031011974385333</v>
+        <v>2.500689462443337e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001857118367455416</v>
+        <v>2.441456941949898e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001973220518100461</v>
+        <v>2.445994338979062e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002031011974385333</v>
+        <v>2.500689462443337e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001934830844920071</v>
+        <v>2.447147514646152e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001943370070901187</v>
+        <v>2.44545487420898e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001937831456065301</v>
+        <v>2.446189727786456e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.160532067840128e-06</v>
+        <v>2.440757806617447e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.457559465456773e-06</v>
+        <v>2.497676163429667e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.160532067840135e-06</v>
+        <v>2.440757806617447e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.510570331122788e-06</v>
+        <v>2.497676163429667e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.510570331122795e-06</v>
+        <v>2.497676163429667e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.095333875101822e-06</v>
+        <v>2.436790724532058e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.160532067840135e-06</v>
+        <v>2.440757806617447e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.887841151501242e-06</v>
+        <v>2.497676163429667e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.160532067840135e-06</v>
+        <v>2.440757806617447e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.160532067840135e-06</v>
+        <v>2.440757806617447e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.160532067840135e-06</v>
+        <v>2.440757806617447e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.415600176696668e-05</v>
+        <v>0.0001769823896620255</v>
       </c>
       <c r="C4" t="n">
-        <v>1.38535901914158e-05</v>
+        <v>0.0002031011974385335</v>
       </c>
       <c r="D4" t="n">
-        <v>1.419130254736109e-05</v>
+        <v>0.0001932936259765701</v>
       </c>
       <c r="E4" t="n">
-        <v>1.365727355497414e-05</v>
+        <v>0.0002031011974385335</v>
       </c>
       <c r="F4" t="n">
-        <v>1.389086690497243e-05</v>
+        <v>0.0002031011974385335</v>
       </c>
       <c r="G4" t="n">
-        <v>1.409080357422838e-05</v>
+        <v>0.0001857118367455416</v>
       </c>
       <c r="H4" t="n">
-        <v>3.095652515952458e-05</v>
+        <v>0.0001973220518100478</v>
       </c>
       <c r="I4" t="n">
-        <v>3.052647997872832e-05</v>
+        <v>0.0002031011974385335</v>
       </c>
       <c r="J4" t="n">
-        <v>1.460977605701403e-05</v>
+        <v>0.0001934830844920071</v>
       </c>
       <c r="K4" t="n">
-        <v>1.418096107857257e-05</v>
+        <v>0.0001943370070901188</v>
       </c>
       <c r="L4" t="n">
-        <v>1.416814816998973e-05</v>
+        <v>0.00019378314560653</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.232244614639465e-05</v>
+        <v>7.160532067840102e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.204975523005561e-05</v>
+        <v>6.457559465456753e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.232227192376702e-05</v>
+        <v>7.160532067840091e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.205205719597781e-05</v>
+        <v>6.510570331122779e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.205205719597781e-05</v>
+        <v>6.510570331122899e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.225724795365626e-05</v>
+        <v>7.095333875101756e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.232244614639463e-05</v>
+        <v>7.160532067840091e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.204975523005561e-05</v>
+        <v>6.887841151501088e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.232244614639463e-05</v>
+        <v>7.160532067840091e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.232244614639463e-05</v>
+        <v>7.160532067840091e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.232244614639463e-05</v>
+        <v>7.160532067840091e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002311890709617557</v>
+        <v>1.41560017669667e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003743518455065346</v>
+        <v>1.385359019141583e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004043298397938347</v>
+        <v>1.419130254736102e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003351286322283222</v>
+        <v>1.365727355497414e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002354635692210609</v>
+        <v>1.389086690497243e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003745287136474568</v>
+        <v>1.40908035742284e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003745939118401909</v>
+        <v>3.09565251595249e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003743212209238561</v>
+        <v>3.052647997872864e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003746220950262004</v>
+        <v>1.460977605701405e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002285252524161888</v>
+        <v>1.418096107857264e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000524392259479262</v>
+        <v>1.416814816998982e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001336424445790533</v>
+        <v>5.232244614639467e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001688102047834622</v>
+        <v>5.204975523005578e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001690828969612104</v>
+        <v>5.232227192376725e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002097077258719471</v>
+        <v>5.205205719597807e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001688101974345138</v>
+        <v>5.205205719597807e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001690176975070627</v>
+        <v>5.225724795365641e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001690828956998013</v>
+        <v>5.23224461463947e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001688102047834622</v>
+        <v>5.204975523005578e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001690828956998013</v>
+        <v>5.23224461463947e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000148548559665589</v>
+        <v>5.23224461463947e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001690828956998013</v>
+        <v>5.23224461463947e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.374143038804893e-05</v>
+        <v>0.0002311890709617559</v>
       </c>
       <c r="C8" t="n">
-        <v>2.436881977115282e-05</v>
+        <v>0.0003743518455065349</v>
       </c>
       <c r="D8" t="n">
-        <v>2.351478981936115e-05</v>
+        <v>0.0004043298397938352</v>
       </c>
       <c r="E8" t="n">
-        <v>2.436881977115282e-05</v>
+        <v>0.0003351286322283223</v>
       </c>
       <c r="F8" t="n">
-        <v>2.436881977115282e-05</v>
+        <v>0.0002354635692210611</v>
       </c>
       <c r="G8" t="n">
-        <v>2.365486621689064e-05</v>
+        <v>0.0003745287136474571</v>
       </c>
       <c r="H8" t="n">
-        <v>2.359101326876283e-05</v>
+        <v>0.0003745939118401913</v>
       </c>
       <c r="I8" t="n">
-        <v>2.436881977115282e-05</v>
+        <v>0.0003743212209238565</v>
       </c>
       <c r="J8" t="n">
-        <v>2.333896735554543e-05</v>
+        <v>0.0003746220950262004</v>
       </c>
       <c r="K8" t="n">
-        <v>2.368428180520962e-05</v>
+        <v>0.0002285252524161888</v>
       </c>
       <c r="L8" t="n">
-        <v>2.354661189659894e-05</v>
+        <v>0.0005243922594792629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001336424445790536</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001688102047834629</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001690828969612113</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002097077258719479</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001688101974345143</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001690176975070633</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001690828956998013</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001688102047834629</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001690828956998013</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001485485596655892</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001690828956998013</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.374143038804889e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.436881977115286e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.351478981936107e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.436881977115286e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.436881977115286e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.365486621689066e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.359101326876286e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.436881977115286e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.333896735554545e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.368428180520965e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.354661189659893e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.414867049783151e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.473027913930716e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.405639255276145e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.473027913930716e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.473027913930716e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.409013347923643e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.408840380473071e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.473027913930716e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.398525386766504e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.412544663834238e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.407970398860816e-05</v>
+      <c r="B11" t="n">
+        <v>2.414867049783154e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.473027913930718e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.405639255276131e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.473027913930718e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.473027913930718e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.409013347923647e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.408840380473075e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.473027913930718e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.398525386766502e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.412544663834237e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.407970398860818e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001875187311682294</v>
+        <v>2.451902834668326e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002103420983600297</v>
+        <v>2.508920502597743e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002095211526585468</v>
+        <v>2.453262336874757e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002103420983600297</v>
+        <v>2.508920502597743e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002103420983600297</v>
+        <v>2.508920502597743e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001969439593866454</v>
+        <v>2.448450531944189e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002169173070727707</v>
+        <v>2.452921202606285e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002103420983600297</v>
+        <v>2.508920502597743e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002032072541323314</v>
+        <v>2.454894225733873e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002091621389990633</v>
+        <v>2.452304487542454e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002236116655485306</v>
+        <v>2.453205024025099e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.278144634662158e-06</v>
+        <v>2.447426749366349e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.587564831986071e-06</v>
+        <v>2.505462988726309e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.278144634662144e-06</v>
+        <v>2.447426749366349e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.643798311945052e-06</v>
+        <v>2.505462988726309e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.643798311945045e-06</v>
+        <v>2.505462988726309e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.213022719382576e-06</v>
+        <v>2.443479289854796e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.278144634662144e-06</v>
+        <v>2.447426749366349e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.005982378390288e-06</v>
+        <v>2.505462988726309e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.278144634662146e-06</v>
+        <v>2.447426749366349e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.278144634662144e-06</v>
+        <v>2.447426749366349e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.278144634662144e-06</v>
+        <v>2.447426749366349e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.429832519501606e-05</v>
+        <v>0.0001875187311682295</v>
       </c>
       <c r="C4" t="n">
-        <v>1.399977456230687e-05</v>
+        <v>0.0002103420983600298</v>
       </c>
       <c r="D4" t="n">
-        <v>1.433321669576721e-05</v>
+        <v>0.000209521152658547</v>
       </c>
       <c r="E4" t="n">
-        <v>1.380154244048294e-05</v>
+        <v>0.0002103420983600298</v>
       </c>
       <c r="F4" t="n">
-        <v>1.403569339300025e-05</v>
+        <v>0.0002103420983600298</v>
       </c>
       <c r="G4" t="n">
-        <v>3.094435457882189e-05</v>
+        <v>0.0001969439593866416</v>
       </c>
       <c r="H4" t="n">
-        <v>3.120534232563558e-05</v>
+        <v>0.0002169173070727711</v>
       </c>
       <c r="I4" t="n">
-        <v>1.402616293874423e-05</v>
+        <v>0.0002103420983600298</v>
       </c>
       <c r="J4" t="n">
-        <v>3.106393348250758e-05</v>
+        <v>0.0002032072541323312</v>
       </c>
       <c r="K4" t="n">
-        <v>1.431987370730711e-05</v>
+        <v>0.0002091621389990634</v>
       </c>
       <c r="L4" t="n">
-        <v>1.431092933768302e-05</v>
+        <v>0.0002236116655485304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.247847414475686e-05</v>
+        <v>7.278144634662136e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.220631188848479e-05</v>
+        <v>6.587564831986038e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.247829459734169e-05</v>
+        <v>7.27814463466214e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.22132691480787e-05</v>
+        <v>6.643798311944964e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.22132691480787e-05</v>
+        <v>6.643798311944962e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.241335222947718e-05</v>
+        <v>7.213022719382591e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.247847414475679e-05</v>
+        <v>7.27814463466214e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.220631188848479e-05</v>
+        <v>7.005982378390159e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.247847414475679e-05</v>
+        <v>7.27814463466214e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.247847414475679e-05</v>
+        <v>7.27814463466214e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.247847414475679e-05</v>
+        <v>7.27814463466214e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002314051199201439</v>
+        <v>1.429832519501616e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003746528531887104</v>
+        <v>1.399977456230684e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004046424197640256</v>
+        <v>1.433321669576728e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003354072938079209</v>
+        <v>1.380154244048289e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002356854614913177</v>
+        <v>1.403569339300026e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003748247912508598</v>
+        <v>3.094435457882186e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003748899131661372</v>
+        <v>3.120534232563541e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003746177509098673</v>
+        <v>1.402616293874417e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003749181120649048</v>
+        <v>3.106393348250773e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002287398162182957</v>
+        <v>1.431987370730717e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005247717777385041</v>
+        <v>1.431092933768308e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001277850236746304</v>
+        <v>5.247847414475695e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001613084630656731</v>
+        <v>5.220631188848494e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001615806266853018</v>
+        <v>5.247829459734176e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002003078628505597</v>
+        <v>5.221326914807875e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001613084557328385</v>
+        <v>5.221326914807875e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001615155034066649</v>
+        <v>5.24133522294773e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001615806253219447</v>
+        <v>5.247847414475693e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001613084630656731</v>
+        <v>5.220631188848494e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001615806253219447</v>
+        <v>5.247847414475693e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001419993215753409</v>
+        <v>5.247847414475693e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001615806253219447</v>
+        <v>5.247847414475693e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.378134424077038e-05</v>
+        <v>0.0002314051199201445</v>
       </c>
       <c r="C8" t="n">
-        <v>2.433543666092167e-05</v>
+        <v>0.0003746528531887101</v>
       </c>
       <c r="D8" t="n">
-        <v>2.349709368491921e-05</v>
+        <v>0.0004046424197640261</v>
       </c>
       <c r="E8" t="n">
-        <v>2.433543666092167e-05</v>
+        <v>0.000335407293807921</v>
       </c>
       <c r="F8" t="n">
-        <v>2.433543666092167e-05</v>
+        <v>0.0002356854614913178</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36433578603692e-05</v>
+        <v>0.0003748247912508596</v>
       </c>
       <c r="H8" t="n">
-        <v>2.359011445215191e-05</v>
+        <v>0.0003748899131661372</v>
       </c>
       <c r="I8" t="n">
-        <v>2.433543666092167e-05</v>
+        <v>0.0003746177509098675</v>
       </c>
       <c r="J8" t="n">
-        <v>2.316681789934239e-05</v>
+        <v>0.0003749181120649051</v>
       </c>
       <c r="K8" t="n">
-        <v>2.369831376118085e-05</v>
+        <v>0.0002287398162182956</v>
       </c>
       <c r="L8" t="n">
-        <v>2.35273447174366e-05</v>
+        <v>0.0005247717777385049</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001277850236746303</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001613084630656727</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001615806266853015</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002003078628505591</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001613084557328382</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001615155034066649</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001615806253219445</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001613084630656727</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001615806253219445</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001419993215753409</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001615806253219445</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.378134424077034e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.433543666092165e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.349709368491919e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.433543666092165e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.433543666092165e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.364335786036911e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.359011445215182e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.433543666092165e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.31668178993424e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.369831376118086e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.352734471743658e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.420374605840146e-05</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>2.420374605840149e-05</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.476196981605928e-05</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.408800617170076e-05</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>2.408800617170075e-05</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.476196981605928e-05</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>2.476196981605928e-05</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.412439985491677e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.412691957454649e-05</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>2.412439985491667e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.412691957454651e-05</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.476196981605928e-05</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.395404852532796e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.416998345432704e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.410119735940385e-05</v>
+      <c r="J11" t="n">
+        <v>2.395404852532799e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.416998345432708e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.410119735940392e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002059799261726977</v>
+        <v>2.437763572598015e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002147577044985776</v>
+        <v>2.49159314579299e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000245941553619526</v>
+        <v>2.438621440075752e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002147577044985776</v>
+        <v>2.49159314579299e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002147577044985776</v>
+        <v>2.49159314579299e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002150067804600814</v>
+        <v>2.433121385454496e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002484737562262976</v>
+        <v>2.436990219223481e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002147577044985776</v>
+        <v>2.49159314579299e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002041997700276915</v>
+        <v>2.438581775737151e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002069988347007254</v>
+        <v>2.436986622902126e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002226371960876411</v>
+        <v>2.440168088250373e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.081121922712115e-06</v>
+        <v>2.432439715276769e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.35865074572002e-06</v>
+        <v>2.488433567595217e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.081121922712115e-06</v>
+        <v>2.432439715276769e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.406716003312364e-06</v>
+        <v>2.488433567595217e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.406716003312399e-06</v>
+        <v>2.488433567595217e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.015925385950733e-06</v>
+        <v>2.428530324418108e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.081121922712115e-06</v>
+        <v>2.432439715276769e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.808369922625261e-06</v>
+        <v>2.488433567595217e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.081121922712115e-06</v>
+        <v>2.432439715276769e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.081121922712115e-06</v>
+        <v>2.432439715276769e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.081121922712115e-06</v>
+        <v>2.432439715276769e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.231718868826488e-05</v>
+        <v>0.0002059799261726921</v>
       </c>
       <c r="C4" t="n">
-        <v>1.429555773216019e-05</v>
+        <v>0.0002147577044985772</v>
       </c>
       <c r="D4" t="n">
-        <v>3.25837604923856e-05</v>
+        <v>0.0002459415536195257</v>
       </c>
       <c r="E4" t="n">
-        <v>1.408346985017964e-05</v>
+        <v>0.0002147577044985772</v>
       </c>
       <c r="F4" t="n">
-        <v>1.432727088908611e-05</v>
+        <v>0.0002147577044985772</v>
       </c>
       <c r="G4" t="n">
-        <v>3.225199215150372e-05</v>
+        <v>0.0002150067804600826</v>
       </c>
       <c r="H4" t="n">
-        <v>1.460235949990754e-05</v>
+        <v>0.0002484737562262966</v>
       </c>
       <c r="I4" t="n">
-        <v>3.204443668817792e-05</v>
+        <v>0.0002147577044985772</v>
       </c>
       <c r="J4" t="n">
-        <v>3.238419514004916e-05</v>
+        <v>0.0002041997700276934</v>
       </c>
       <c r="K4" t="n">
-        <v>1.462092085779149e-05</v>
+        <v>0.0002069988347007242</v>
       </c>
       <c r="L4" t="n">
-        <v>1.460387346918924e-05</v>
+        <v>0.0002226371960876405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.549103134688987e-05</v>
+        <v>7.081121922711778e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.521827934680301e-05</v>
+        <v>6.358650745720057e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.549085703340252e-05</v>
+        <v>7.081121922711778e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.522069083747753e-05</v>
+        <v>6.406716003312484e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.522069083747753e-05</v>
+        <v>6.406716003312484e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.542583481012866e-05</v>
+        <v>7.015925385950676e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.549103134688987e-05</v>
+        <v>7.081121922711827e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.521827934680301e-05</v>
+        <v>6.808369922624981e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.549103134688987e-05</v>
+        <v>7.08112192271178e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.549103134688987e-05</v>
+        <v>7.081121922711778e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.549103134688987e-05</v>
+        <v>7.081121922711778e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002473043513569891</v>
+        <v>3.231718868826476e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004008052549601681</v>
+        <v>1.429555773216014e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004329244316843057</v>
+        <v>3.258376049238535e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003587550054673494</v>
+        <v>1.408346985017962e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002519064911202299</v>
+        <v>1.432727088908613e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004009800574553467</v>
+        <v>3.225199215150359e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004010452539921022</v>
+        <v>1.460235949990754e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004007725019920214</v>
+        <v>3.204443668817787e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004010754685124515</v>
+        <v>3.238419514004883e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002444485351576618</v>
+        <v>1.462092085779146e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005616404824252042</v>
+        <v>1.460387346918925e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001509415492429223</v>
+        <v>5.549103134688991e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001909354484193558</v>
+        <v>5.521827934680299e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001912082018844754</v>
+        <v>5.549085703340254e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002374023018279716</v>
+        <v>5.522069083747749e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000190935440753344</v>
+        <v>5.522069083747748e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001911430038826816</v>
+        <v>5.54258348101287e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001912082004194428</v>
+        <v>5.549103134688991e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001909354484193558</v>
+        <v>5.521827934680299e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001912082004194428</v>
+        <v>5.549103134688991e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001678775452046084</v>
+        <v>5.549103134688991e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001912082004194428</v>
+        <v>5.549103134688991e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.348737806551969e-05</v>
+        <v>0.0002473043513569889</v>
       </c>
       <c r="C8" t="n">
-        <v>2.426811836871284e-05</v>
+        <v>0.0004008052549601671</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3308292602153e-05</v>
+        <v>0.0004329244316843051</v>
       </c>
       <c r="E8" t="n">
-        <v>2.426811836871284e-05</v>
+        <v>0.0003587550054673491</v>
       </c>
       <c r="F8" t="n">
-        <v>2.426811836871284e-05</v>
+        <v>0.0002519064911202298</v>
       </c>
       <c r="G8" t="n">
-        <v>2.360659860230855e-05</v>
+        <v>0.0004009800574553464</v>
       </c>
       <c r="H8" t="n">
-        <v>2.366726461418194e-05</v>
+        <v>0.0004010452539921023</v>
       </c>
       <c r="I8" t="n">
-        <v>2.426811836871284e-05</v>
+        <v>0.0004007725019920208</v>
       </c>
       <c r="J8" t="n">
-        <v>2.332588443982115e-05</v>
+        <v>0.0004010754685124521</v>
       </c>
       <c r="K8" t="n">
-        <v>2.365127055339232e-05</v>
+        <v>0.000244448535157662</v>
       </c>
       <c r="L8" t="n">
-        <v>2.35404872178309e-05</v>
+        <v>0.0005616404824252033</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001509415492429221</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001909354484193557</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001912082018844752</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002374023018279718</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001909354407533439</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001911430038826813</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001912082004194425</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001909354484193557</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001912082004194425</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001678775452046083</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001912082004194425</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.348737806551982e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.426811836871306e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.330829260215311e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.426811836871306e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.426811836871306e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.360659860230868e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.366726461418205e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.426811836871306e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.33258844398212e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.365127055339253e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.354048721783101e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.399678937386069e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.463555061936786e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.392388359209467e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.463555061936786e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.463555061936786e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.402240107958956e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.407090479302106e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.463555061936786e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.39314912909095e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.406359148117819e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.401920055386602e-05</v>
+      <c r="B11" t="n">
+        <v>2.39967893738608e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.463555061936805e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.392388359209482e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.463555061936805e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.463555061936805e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.402240107958969e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.40709047930212e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.463555061936805e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.393149129090963e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.406359148117835e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.401920055386617e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001987491412224537</v>
+        <v>2.456961477784311e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002227191136293556</v>
+        <v>2.512860364562358e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002554590075368718</v>
+        <v>2.458542997210832e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002227191136293556</v>
+        <v>2.512860364562358e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002227191136293556</v>
+        <v>2.512860364562358e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002251723243846819</v>
+        <v>2.452829031271318e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002889923943542668</v>
+        <v>2.459016254906053e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002227191136293556</v>
+        <v>2.512860364562358e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002278130299220598</v>
+        <v>2.458025027301308e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002102787211528063</v>
+        <v>2.456605674199915e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002551110262605922</v>
+        <v>2.459728519876418e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.279474135045375e-06</v>
+        <v>2.450464693267925e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.573903097556324e-06</v>
+        <v>2.508276753923131e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.279474135045375e-06</v>
+        <v>2.450464693267925e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.628991184744278e-06</v>
+        <v>2.508276753923131e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.628991184744326e-06</v>
+        <v>2.508276753923131e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.214156936741529e-06</v>
+        <v>2.446477895065908e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.279474135045375e-06</v>
+        <v>2.450464693267925e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.006038458320472e-06</v>
+        <v>2.508276753923131e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.279474135045375e-06</v>
+        <v>2.450464693267925e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.279474135045375e-06</v>
+        <v>2.450464693267925e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.279474135045375e-06</v>
+        <v>2.450464693267925e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.109797354749381e-05</v>
+        <v>0.0001987491412224539</v>
       </c>
       <c r="C4" t="n">
-        <v>1.405190883629871e-05</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="D4" t="n">
-        <v>1.440708235690887e-05</v>
+        <v>0.0002554590075368718</v>
       </c>
       <c r="E4" t="n">
-        <v>1.385059418522502e-05</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="F4" t="n">
-        <v>1.409093083040994e-05</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="G4" t="n">
-        <v>3.103265634918993e-05</v>
+        <v>0.0002251723243846814</v>
       </c>
       <c r="H4" t="n">
-        <v>3.127522604542043e-05</v>
+        <v>0.0002889923943542674</v>
       </c>
       <c r="I4" t="n">
-        <v>3.082453787076889e-05</v>
+        <v>0.0002227191136293556</v>
       </c>
       <c r="J4" t="n">
-        <v>1.481447539709815e-05</v>
+        <v>0.0002278130299220599</v>
       </c>
       <c r="K4" t="n">
-        <v>1.438175797693084e-05</v>
+        <v>0.0002102787211528069</v>
       </c>
       <c r="L4" t="n">
-        <v>1.437015888756138e-05</v>
+        <v>0.0002551110262605923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.250914009457199e-05</v>
+        <v>7.279474135045398e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.22357044178471e-05</v>
+        <v>6.573903097556303e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.250896465970457e-05</v>
+        <v>7.279474135045398e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.223813132282308e-05</v>
+        <v>6.628991184744273e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.223813132282308e-05</v>
+        <v>6.628991184744297e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.244382289626825e-05</v>
+        <v>7.21415693674152e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.250914009457199e-05</v>
+        <v>7.279474135045398e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.22357044178471e-05</v>
+        <v>7.006038458320407e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.250914009457199e-05</v>
+        <v>7.279474135045398e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.250914009457199e-05</v>
+        <v>7.279474135045398e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.250914009457199e-05</v>
+        <v>7.279474135045398e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002314339200373251</v>
+        <v>3.10979735474933e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003746945045769128</v>
+        <v>1.405190883629859e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004046935100844329</v>
+        <v>1.440708235690885e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003354443606037287</v>
+        <v>1.385059418522498e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002357108683748788</v>
+        <v>1.409093083040983e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003748718580744687</v>
+        <v>3.103265634918963e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003749371752727702</v>
+        <v>3.127522604542041e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003746637395960474</v>
+        <v>3.082453787076858e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003749653777998353</v>
+        <v>1.481447539709802e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002287682733945688</v>
+        <v>1.438175797693083e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005248383249368346</v>
+        <v>1.437015888756134e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001341714599003598</v>
+        <v>5.250914009457213e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001694598980339356</v>
+        <v>5.223570441784712e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001697333350993637</v>
+        <v>5.25089646597047e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002104975381624633</v>
+        <v>5.223813132282301e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001694598904576305</v>
+        <v>5.223813132282301e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001696680165123567</v>
+        <v>5.244382289626818e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001697333337106603</v>
+        <v>5.250914009457213e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001694598980339356</v>
+        <v>5.223570441784712e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001697333337106603</v>
+        <v>5.250914009457213e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001491286449467973</v>
+        <v>5.250914009457213e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001697333337106603</v>
+        <v>5.250914009457213e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3382254926467e-05</v>
+        <v>0.0002314339200373251</v>
       </c>
       <c r="C8" t="n">
-        <v>2.412234434175238e-05</v>
+        <v>0.0003746945045769137</v>
       </c>
       <c r="D8" t="n">
-        <v>2.305173380891997e-05</v>
+        <v>0.0004046935100844338</v>
       </c>
       <c r="E8" t="n">
-        <v>2.412234434175238e-05</v>
+        <v>0.0003354443606037294</v>
       </c>
       <c r="F8" t="n">
-        <v>2.412234434175238e-05</v>
+        <v>0.0002357108683748787</v>
       </c>
       <c r="G8" t="n">
-        <v>2.337964143763238e-05</v>
+        <v>0.0003748718580744688</v>
       </c>
       <c r="H8" t="n">
-        <v>2.298617065890879e-05</v>
+        <v>0.0003749371752727701</v>
       </c>
       <c r="I8" t="n">
-        <v>2.412234434175238e-05</v>
+        <v>0.0003746637395960471</v>
       </c>
       <c r="J8" t="n">
-        <v>2.317200899818132e-05</v>
+        <v>0.0003749653777998354</v>
       </c>
       <c r="K8" t="n">
-        <v>2.34582884871474e-05</v>
+        <v>0.0002287682733945688</v>
       </c>
       <c r="L8" t="n">
-        <v>2.283242600165165e-05</v>
+        <v>0.0005248383249368349</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001341714599003594</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001694598980339348</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001697333350993635</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002104975381624626</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001694598904576301</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001696680165123561</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001697333337106601</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001694598980339348</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001697333337106601</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001491286449467965</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001697333337106601</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.338225492646697e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.412234434175237e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.305173380892001e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.412234434175237e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.412234434175237e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.337964143763234e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.298617065890884e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.412234434175237e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.317200899818135e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.345828848714738e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.283242600165167e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.405892283816537e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.469160803008357e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.392434987063851e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.469160803008357e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.469160803008357e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.403454928615798e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.389925100539816e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.469160803008357e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.397389576595141e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.408996031473563e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.383641934609479e-05</v>
+      <c r="B11" t="n">
+        <v>2.405892283816532e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.469160803008353e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.39243498706385e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.469160803008353e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.469160803008353e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.403454928615796e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.389925100539821e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.469160803008353e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.39738957659514e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.408996031473564e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.383641934609475e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002109417920603678</v>
+        <v>2.469624888017246e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002232854615972502</v>
+        <v>2.527460649890541e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002821104540841528</v>
+        <v>2.475927065117328e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002232854615972502</v>
+        <v>2.527460649890541e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002232854615972502</v>
+        <v>2.527460649890541e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002280311471395341</v>
+        <v>2.465832314904224e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002755624199005057</v>
+        <v>2.472541124041138e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002232854615972502</v>
+        <v>2.527460649890541e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002845800397415786</v>
+        <v>2.47701618612128e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002192191650576918</v>
+        <v>2.468680839795277e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002466414804392448</v>
+        <v>2.471167681587479e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.39358450232895e-06</v>
+        <v>2.462096403111445e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.676497434442079e-06</v>
+        <v>2.521750861073348e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.39358450232895e-06</v>
+        <v>2.462096403111445e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.736537705793609e-06</v>
+        <v>2.521750861073348e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.736537705793608e-06</v>
+        <v>2.521750861073348e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.328138993006462e-06</v>
+        <v>2.458051206985923e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.39358450232895e-06</v>
+        <v>2.462096403111445e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.119380466463827e-06</v>
+        <v>2.521750861073348e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.39358450232895e-06</v>
+        <v>2.462096403111445e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.39358450232895e-06</v>
+        <v>2.462096403111445e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.39358450232895e-06</v>
+        <v>2.462096403111445e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.454998115619957e-05</v>
+        <v>0.0002109417920603682</v>
       </c>
       <c r="C4" t="n">
-        <v>1.423956261786171e-05</v>
+        <v>0.0002232854615972499</v>
       </c>
       <c r="D4" t="n">
-        <v>1.467559677310181e-05</v>
+        <v>0.0002821104540841523</v>
       </c>
       <c r="E4" t="n">
-        <v>1.403309862828418e-05</v>
+        <v>0.0002232854615972499</v>
       </c>
       <c r="F4" t="n">
-        <v>1.428357621643298e-05</v>
+        <v>0.0002232854615972499</v>
       </c>
       <c r="G4" t="n">
-        <v>1.448453564687712e-05</v>
+        <v>0.0002280311471395391</v>
       </c>
       <c r="H4" t="n">
-        <v>3.161441313198264e-05</v>
+        <v>0.0002755624199005065</v>
       </c>
       <c r="I4" t="n">
-        <v>1.427577712033446e-05</v>
+        <v>0.0002232854615972499</v>
       </c>
       <c r="J4" t="n">
-        <v>1.503205648362078e-05</v>
+        <v>0.0002845800397415795</v>
       </c>
       <c r="K4" t="n">
-        <v>1.456049373315226e-05</v>
+        <v>0.0002192191650576931</v>
       </c>
       <c r="L4" t="n">
-        <v>1.456357398606307e-05</v>
+        <v>0.0002466414804392449</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.270305999474899e-05</v>
+        <v>7.393584502328887e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.242885595888386e-05</v>
+        <v>6.676497434442049e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.270288271180765e-05</v>
+        <v>7.393584502328887e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.243049922432716e-05</v>
+        <v>6.736537705793589e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.243049922432716e-05</v>
+        <v>6.736537705793587e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.263761448542658e-05</v>
+        <v>7.328138993006325e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.270305999474899e-05</v>
+        <v>7.393584502328887e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.242885595888386e-05</v>
+        <v>7.119380466463661e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.270305999474899e-05</v>
+        <v>7.393584502328887e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.270305999474899e-05</v>
+        <v>7.393584502328887e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.270305999474899e-05</v>
+        <v>7.393584502328887e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002317233213183929</v>
+        <v>1.454998115619958e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003751183883304083</v>
+        <v>1.423956261786163e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004051470734119369</v>
+        <v>1.467559677310185e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003358311312829354</v>
+        <v>1.403309862828401e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002360033449011114</v>
+        <v>1.42835762164329e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003752970992067671</v>
+        <v>1.448453564687709e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003753625447160912</v>
+        <v>3.161441313198262e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003750883406802243</v>
+        <v>1.427577712033441e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003753907739646344</v>
+        <v>1.503205648362065e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002290551489972081</v>
+        <v>1.456049373315219e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005254057244949862</v>
+        <v>1.456357398606313e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001285084775402477</v>
+        <v>5.27030599947491e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001622091658750606</v>
+        <v>5.242885595888399e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001624833714509851</v>
+        <v>5.270288271180774e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002014154630012761</v>
+        <v>5.243049922432703e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001622091581329532</v>
+        <v>5.243049922432703e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001624179244016031</v>
+        <v>5.263761448542677e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001624833699109258</v>
+        <v>5.27030599947491e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001622091658750606</v>
+        <v>5.242885595888399e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001624833699109258</v>
+        <v>5.27030599947491e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000141999531588252</v>
+        <v>5.27030599947491e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001624833699109258</v>
+        <v>5.27030599947491e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.325590875566804e-05</v>
+        <v>0.0002317233213183931</v>
       </c>
       <c r="C8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>0.0003751183883304091</v>
       </c>
       <c r="D8" t="n">
-        <v>2.19366148198526e-05</v>
+        <v>0.0004051470734119368</v>
       </c>
       <c r="E8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>0.0003358311312829365</v>
       </c>
       <c r="F8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>0.0002360033449011116</v>
       </c>
       <c r="G8" t="n">
-        <v>2.317083691564488e-05</v>
+        <v>0.0003752970992067671</v>
       </c>
       <c r="H8" t="n">
-        <v>2.268736317151919e-05</v>
+        <v>0.0003753625447160901</v>
       </c>
       <c r="I8" t="n">
-        <v>2.398838601472786e-05</v>
+        <v>0.0003750883406802255</v>
       </c>
       <c r="J8" t="n">
-        <v>2.173180408810706e-05</v>
+        <v>0.0003753907739646352</v>
       </c>
       <c r="K8" t="n">
-        <v>2.345537167565301e-05</v>
+        <v>0.0002290551489972082</v>
       </c>
       <c r="L8" t="n">
-        <v>2.309814273171538e-05</v>
+        <v>0.0005254057244949853</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.000128508477540248</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001622091658750609</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001624833714509854</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002014154630012764</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001622091581329536</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001624179244016033</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001624833699109256</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001622091658750609</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001624833699109256</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001419995315882525</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001624833699109256</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.325590875566809e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.398838601472794e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.193661481985267e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.398838601472794e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.398838601472794e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.317083691564488e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.268736317151924e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.398838601472794e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.173180408810713e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.34553716756531e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.309814273171543e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.407514437967129e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.471535180074149e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.353788320553581e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.471535180074149e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.471535180074149e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.401691646150654e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.384561668727516e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.471535180074149e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.345558487993805e-05</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>2.407514437967133e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.471535180074154e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.353788320553584e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.471535180074154e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.471535180074154e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.401691646150656e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.384561668727519e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.471535180074154e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.345558487993798e-05</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.415646016169546e-05</v>
       </c>
-      <c r="L9" t="n">
-        <v>2.401222727292481e-05</v>
+      <c r="L11" t="n">
+        <v>2.401222727292479e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000194173971169578</v>
+        <v>2.432141330146728e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002095333304772803</v>
+        <v>2.486580798552344e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002171313206726944</v>
+        <v>2.433331962161755e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002095333304772803</v>
+        <v>2.486580798552344e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002095333304772803</v>
+        <v>2.486580798552344e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000198474572537036</v>
+        <v>2.428101884063129e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002385427550627798</v>
+        <v>2.432422507286397e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002095333304772803</v>
+        <v>2.486580798552344e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001970365957671459</v>
+        <v>2.433392551851143e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001860683099611692</v>
+        <v>2.431420656690568e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001979557948330319</v>
+        <v>2.43283153347023e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.034867640172722e-06</v>
+        <v>2.427939813155932e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.306450807556842e-06</v>
+        <v>2.483934452974641e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.03486764017272e-06</v>
+        <v>2.427939813155932e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.354210223090525e-06</v>
+        <v>2.483934452974641e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.354210223090423e-06</v>
+        <v>2.483934452974641e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>6.96970709687929e-06</v>
+        <v>2.424030577515629e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.034867640172722e-06</v>
+        <v>2.427939813155932e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.762342415526493e-06</v>
+        <v>2.483934452974641e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.03486764017272e-06</v>
+        <v>2.427939813155932e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.03486764017272e-06</v>
+        <v>2.427939813155932e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.03486764017272e-06</v>
+        <v>2.427939813155932e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.451204694894525e-05</v>
+        <v>0.0001941739711695789</v>
       </c>
       <c r="C4" t="n">
-        <v>1.421790622804391e-05</v>
+        <v>0.0002095333304772695</v>
       </c>
       <c r="D4" t="n">
-        <v>1.456235704194518e-05</v>
+        <v>0.0002171313206726982</v>
       </c>
       <c r="E4" t="n">
-        <v>1.400809477566735e-05</v>
+        <v>0.0002095333304772695</v>
       </c>
       <c r="F4" t="n">
-        <v>1.42493040274319e-05</v>
+        <v>0.0002095333304772695</v>
       </c>
       <c r="G4" t="n">
-        <v>3.213478570967854e-05</v>
+        <v>0.0001984745725370521</v>
       </c>
       <c r="H4" t="n">
-        <v>3.228223280406536e-05</v>
+        <v>0.0002385427550628068</v>
       </c>
       <c r="I4" t="n">
-        <v>3.192742102832557e-05</v>
+        <v>0.0002095333304772695</v>
       </c>
       <c r="J4" t="n">
-        <v>3.226999623467888e-05</v>
+        <v>0.000197036595767146</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453319126251813e-05</v>
+        <v>0.000186068309961169</v>
       </c>
       <c r="L4" t="n">
-        <v>1.452711215492475e-05</v>
+        <v>0.0001979557948330557</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.541733842619626e-05</v>
+        <v>7.034867640172391e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.514481320155009e-05</v>
+        <v>6.306450807556668e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.541716642826073e-05</v>
+        <v>7.034867640172391e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.514536342928333e-05</v>
+        <v>6.354210223090558e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.514536342928333e-05</v>
+        <v>6.354210223090615e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.535217788290285e-05</v>
+        <v>6.969707096879505e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.541733842619626e-05</v>
+        <v>7.034867640172391e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.514481320155009e-05</v>
+        <v>6.762342415526033e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.541733842619626e-05</v>
+        <v>7.034867640172391e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.541733842619626e-05</v>
+        <v>7.034867640172391e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.541733842619626e-05</v>
+        <v>7.034867640172391e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002472057458572649</v>
+        <v>1.451204694894526e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004006633670063595</v>
+        <v>1.421790622804362e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00043277545761782</v>
+        <v>1.456235704194532e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003586247179200531</v>
+        <v>1.400809477566744e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002518056782828943</v>
+        <v>1.424930402743178e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004008397698930176</v>
+        <v>3.21347857096785e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004009049304363054</v>
+        <v>3.228223280406523e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004006324052116632</v>
+        <v>3.192742102832562e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000400935136757969</v>
+        <v>3.226999623467883e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002443507045922359</v>
+        <v>1.453319126251805e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005614565808715341</v>
+        <v>1.452711215492472e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001507301711160745</v>
+        <v>5.541733842619641e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001906749515015635</v>
+        <v>5.514481320155006e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001909474779827851</v>
+        <v>5.541716642826106e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002370848608797493</v>
+        <v>5.514536342928402e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001906749437518101</v>
+        <v>5.514536342928402e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001908823161829153</v>
+        <v>5.535217788290312e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001909474767262106</v>
+        <v>5.541733842619641e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001906749515015635</v>
+        <v>5.514481320155006e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001909474767262106</v>
+        <v>5.541733842619641e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001676454124386579</v>
+        <v>5.541733842619641e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001909474767262106</v>
+        <v>5.541733842619641e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.368806920185117e-05</v>
+        <v>0.0002472057458572652</v>
       </c>
       <c r="C8" t="n">
-        <v>2.434095800129608e-05</v>
+        <v>0.0004006633670063599</v>
       </c>
       <c r="D8" t="n">
-        <v>2.343913791587795e-05</v>
+        <v>0.0004327754576178206</v>
       </c>
       <c r="E8" t="n">
-        <v>2.434095800129608e-05</v>
+        <v>0.0003586247179200531</v>
       </c>
       <c r="F8" t="n">
-        <v>2.434095800129608e-05</v>
+        <v>0.0002518056782828944</v>
       </c>
       <c r="G8" t="n">
-        <v>2.368040103563579e-05</v>
+        <v>0.000400839769893017</v>
       </c>
       <c r="H8" t="n">
-        <v>2.364645208168211e-05</v>
+        <v>0.0004009049304363055</v>
       </c>
       <c r="I8" t="n">
-        <v>2.434095800129608e-05</v>
+        <v>0.000400632405211664</v>
       </c>
       <c r="J8" t="n">
-        <v>2.343458488733095e-05</v>
+        <v>0.0004009351367579681</v>
       </c>
       <c r="K8" t="n">
-        <v>2.383990698139218e-05</v>
+        <v>0.0002443507045922364</v>
       </c>
       <c r="L8" t="n">
-        <v>2.355874903751882e-05</v>
+        <v>0.0005614565808715351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001507301711160754</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001906749515015644</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001909474779827859</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002370848608797493</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001906749437518115</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001908823161829169</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001909474767262107</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001906749515015644</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001909474767262107</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001676454124386586</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001909474767262107</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.368806920185072e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.434095800129603e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.343913791587769e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.434095800129603e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.434095800129603e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.368040103563544e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.364645208168181e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.434095800129603e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.343458488733116e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.383990698139219e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.355874903751865e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.405235675399683e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.463904052681484e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.395099854573206e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.463904052681484e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.463904052681484e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.402626039983858e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.403623260309023e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.463904052681484e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.394953280012734e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.411423669300416e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.398631615306486e-05</v>
+      <c r="B11" t="n">
+        <v>2.405235675399663e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.463904052681472e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.395099854573224e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.463904052681472e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.463904052681472e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.402626039983857e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.403623260309034e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.463904052681472e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.394953280012738e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.411423669300408e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.398631615306468e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001939647785914961</v>
+        <v>2.451771478183332e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002152401579876322</v>
+        <v>2.508121832928438e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002176632073446982</v>
+        <v>2.450885145551621e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002152401579876322</v>
+        <v>2.508121832928438e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002152401579876322</v>
+        <v>2.508121832928438e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002095060531221372</v>
+        <v>2.447455360959287e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002545489321098474</v>
+        <v>2.452939804558223e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002152401579876322</v>
+        <v>2.508121832928438e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001959774106372087</v>
+        <v>2.452376331217786e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002017719385838797</v>
+        <v>2.450983438660111e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002131527083021825</v>
+        <v>2.454029652958144e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.227929983052669e-06</v>
+        <v>2.445771109070207e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.526183011348196e-06</v>
+        <v>2.503931842973776e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.227929983052669e-06</v>
+        <v>2.445771109070207e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.580072048547266e-06</v>
+        <v>2.503931842973776e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.580072048547265e-06</v>
+        <v>2.503931842973776e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.162770235773614e-06</v>
+        <v>2.441840087962731e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.227929983052669e-06</v>
+        <v>2.445771109070207e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.955496219246557e-06</v>
+        <v>2.503931842973776e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.227929983052669e-06</v>
+        <v>2.445771109070207e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.227929983052669e-06</v>
+        <v>2.445771109070207e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.227929983052669e-06</v>
+        <v>2.445771109070207e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.096389913786886e-05</v>
+        <v>0.0001939647785914963</v>
       </c>
       <c r="C4" t="n">
-        <v>1.397153422624127e-05</v>
+        <v>0.0002152401579876325</v>
       </c>
       <c r="D4" t="n">
-        <v>1.428172686646854e-05</v>
+        <v>0.0002176632073446975</v>
       </c>
       <c r="E4" t="n">
-        <v>1.377272253949293e-05</v>
+        <v>0.0002152401579876325</v>
       </c>
       <c r="F4" t="n">
-        <v>1.40058728607998e-05</v>
+        <v>0.0002152401579876325</v>
       </c>
       <c r="G4" t="n">
-        <v>3.089873939058986e-05</v>
+        <v>0.0002095060531221382</v>
       </c>
       <c r="H4" t="n">
-        <v>3.112994694699633e-05</v>
+        <v>0.0002545489321098479</v>
       </c>
       <c r="I4" t="n">
-        <v>3.069146537406273e-05</v>
+        <v>0.0002152401579876325</v>
       </c>
       <c r="J4" t="n">
-        <v>1.472405663455848e-05</v>
+        <v>0.0001959774106372078</v>
       </c>
       <c r="K4" t="n">
-        <v>1.428830192061573e-05</v>
+        <v>0.0002017719385838792</v>
       </c>
       <c r="L4" t="n">
-        <v>1.428054234256367e-05</v>
+        <v>0.0002131527083021826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.242393790169327e-05</v>
+        <v>7.227929983052624e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>5.215150413788711e-05</v>
+        <v>6.526183011348337e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>5.242376280440691e-05</v>
+        <v>7.227929983052624e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>5.215390006511594e-05</v>
+        <v>6.580072048547269e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>5.215390006511594e-05</v>
+        <v>6.580072048547321e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.235877815441421e-05</v>
+        <v>7.162770235773588e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>5.242393790169327e-05</v>
+        <v>7.227929983052624e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>5.215150413788711e-05</v>
+        <v>6.955496219246553e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.242393790169327e-05</v>
+        <v>7.227929983052624e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.242393790169327e-05</v>
+        <v>7.227929983052624e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>5.242393790169327e-05</v>
+        <v>7.227929983052624e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002313217140051106</v>
+        <v>3.096389913786886e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003745347272245281</v>
+        <v>1.397153422624129e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004045227067419656</v>
+        <v>1.428172686646854e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003352978611104175</v>
+        <v>1.377272253949297e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000235598107135482</v>
+        <v>1.400587286079988e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003747112759329232</v>
+        <v>3.089873939058985e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003747764356801994</v>
+        <v>3.112994694699708e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003745040019163965</v>
+        <v>3.06914653740629e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003748046286691394</v>
+        <v>1.472405663455852e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002286569688981442</v>
+        <v>1.42883019206158e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005246268879822674</v>
+        <v>1.428054234256369e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001339431641633196</v>
+        <v>5.242393790169331e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001691793746685079</v>
+        <v>5.215150413788713e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001694518097603184</v>
+        <v>5.242376280440696e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000210155589140388</v>
+        <v>5.215390006511618e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001691793672203965</v>
+        <v>5.215390006511618e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001693866486850347</v>
+        <v>5.235877815441431e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001694518084323139</v>
+        <v>5.242393790169331e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001691793746685079</v>
+        <v>5.215150413788713e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001694518084323139</v>
+        <v>5.242393790169331e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001488779610482016</v>
+        <v>5.242393790169331e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001694518084323139</v>
+        <v>5.242393790169331e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.344981893216415e-05</v>
+        <v>0.000231321714005112</v>
       </c>
       <c r="C8" t="n">
-        <v>2.417113083568102e-05</v>
+        <v>0.0003745347272245303</v>
       </c>
       <c r="D8" t="n">
-        <v>2.363621254469096e-05</v>
+        <v>0.0004045227067419684</v>
       </c>
       <c r="E8" t="n">
-        <v>2.417113083568102e-05</v>
+        <v>0.0003352978611104198</v>
       </c>
       <c r="F8" t="n">
-        <v>2.417113083568102e-05</v>
+        <v>0.0002355981071354837</v>
       </c>
       <c r="G8" t="n">
-        <v>2.349714120556524e-05</v>
+        <v>0.0003747112759329257</v>
       </c>
       <c r="H8" t="n">
-        <v>2.32337878318922e-05</v>
+        <v>0.0003747764356802017</v>
       </c>
       <c r="I8" t="n">
-        <v>2.417113083568102e-05</v>
+        <v>0.0003745040019163987</v>
       </c>
       <c r="J8" t="n">
-        <v>2.333404521686576e-05</v>
+        <v>0.0003748046286691417</v>
       </c>
       <c r="K8" t="n">
-        <v>2.361622265049838e-05</v>
+        <v>0.0002286569688981454</v>
       </c>
       <c r="L8" t="n">
-        <v>2.349711598565961e-05</v>
+        <v>0.0005246268879822708</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001339431641633194</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001691793746685078</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001694518097603181</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002101555891403877</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001691793672203962</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.000169386648685035</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001694518084323138</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001691793746685078</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001694518084323138</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.000148877961048202</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001694518084323138</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.34498189321642e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.417113083568105e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.3636212544691e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.417113083568105e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.417113083568105e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.349714120556544e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.323378783189227e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.417113083568105e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.33340452168658e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.361622265049848e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.349711598565966e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.405912063773677e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.46861902072388e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.413506699912057e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.46861902072388e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.46861902072388e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.405537752201422e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.397250906241172e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.46861902072388e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.401249175867162e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.412695446464384e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.407929847355593e-05</v>
+      <c r="B11" t="n">
+        <v>2.405912063773683e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.468619020723888e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.413506699912067e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.468619020723888e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.468619020723888e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.405537752201429e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.397250906241178e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.468619020723888e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.40124917586717e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.412695446464388e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.407929847355599e-05</v>
       </c>
     </row>
   </sheetData>
